--- a/skeleton-cc.xlsx
+++ b/skeleton-cc.xlsx
@@ -40,7 +40,7 @@
     <definedName name="Z_D6DF09BD_97F5_4B8B_B461_A7BC9875A0D8_.wvu.Rows" localSheetId="0" hidden="1">'FACE SHEET'!$20:$20</definedName>
     <definedName name="Z_D6DF09BD_97F5_4B8B_B461_A7BC9875A0D8_.wvu.Rows" localSheetId="2" hidden="1">Measurement!$22:$24</definedName>
   </definedNames>
-  <calcPr calcId="152511" fullCalcOnLoad="1"/>
+  <calcPr calcId="152511"/>
   <customWorkbookViews>
     <customWorkbookView name="Admin - Personal View" guid="{D6DF09BD-97F5-4B8B-B461-A7BC9875A0D8}" mergeInterval="0" personalView="1" maximized="1" xWindow="-9" yWindow="-9" windowWidth="1938" windowHeight="1048" activeSheetId="1"/>
   </customWorkbookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="151">
   <si>
     <t xml:space="preserve">Estimate checked by:  </t>
   </si>
@@ -219,9 +219,6 @@
   </si>
   <si>
     <t>For remaining lead  Total lead above 50 up to 100</t>
-  </si>
-  <si>
-    <t>Estimated framed in the office of the Taluka Development Officer, Taluka Panchyat, Thasra for the expenses that will be incurred in the Work Of</t>
   </si>
   <si>
     <t>PLAN</t>
@@ -243,15 +240,9 @@
     <t>GENERAL DESCRIPTION</t>
   </si>
   <si>
-    <t>R &amp; B (P) KDP NADIAD</t>
-  </si>
-  <si>
     <t>Soft Murum</t>
   </si>
   <si>
-    <t>R &amp; B (P) SUB DIVI  DAKOR/ DEE ATVT PRANT OFFICE THASRA</t>
-  </si>
-  <si>
     <t>ABSTRACT SHEET</t>
   </si>
   <si>
@@ -297,9 +288,6 @@
     <t>X</t>
   </si>
   <si>
-    <t>VF SFD p5ZMST IMHGF C[9/ D\H]Z YI[, K[P VF V\NFH5+SDF\ AMS; S8L\U4 AL8L D[8, $_ YL &amp;# DLDL 4 D]ZD 4 ;LP ;LP !oZo$4  8|LDLS;4 ZM,L\U4 TSTLGL VF.8[DGM ;DFJ[X SZL JQF" Z_Z!vZZ GF DFU"" VG[ DSFGGF V[;PVMPVFZ EFJ ,. V\NFH T{IFZ SZ[, K[P</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -411,60 +399,6 @@
     <t>AS PER SCHEDULE OF TESTING</t>
   </si>
   <si>
-    <t>CUBE</t>
-  </si>
-  <si>
-    <t>CEMENT</t>
-  </si>
-  <si>
-    <t>SAND</t>
-  </si>
-  <si>
-    <t>KAPACHI</t>
-  </si>
-  <si>
-    <t>METAL</t>
-  </si>
-  <si>
-    <t>CC ROAD</t>
-  </si>
-  <si>
-    <t>(I)</t>
-  </si>
-  <si>
-    <t>Cost of material</t>
-  </si>
-  <si>
-    <t>Rs</t>
-  </si>
-  <si>
-    <t>R&amp;B sor 2024-25 Item Code 26012A Item Code 26.50 Page -163</t>
-  </si>
-  <si>
-    <t>(ii)</t>
-  </si>
-  <si>
-    <t>Conveyance from</t>
-  </si>
-  <si>
-    <t>0 to 5.00 KM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">( as per statement No:- 05 </t>
-  </si>
-  <si>
-    <t>(iii)</t>
-  </si>
-  <si>
-    <t>5 to 50 km</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
     <t xml:space="preserve">Item No.2 :- Supplying of crsuhed stone aggregate,chipping etc. of hard stones of following nominal size free of disintegrated pieces deletarious and organic mater </t>
   </si>
   <si>
@@ -495,9 +429,6 @@
     <t xml:space="preserve">મુકામે </t>
   </si>
   <si>
-    <t xml:space="preserve">તા. ઠાસરા </t>
-  </si>
-  <si>
     <t>ADD 18% GST</t>
   </si>
   <si>
@@ -508,12 +439,6 @@
   </si>
   <si>
     <t>જઅમ/ધા.ફં/પ્રા.મં/૬(૧)/૨૫-૨૬/વશી/૨૧૭-૧૯/૨૫. તા. ૧૭/૦૭/૨૦૨૫.</t>
-  </si>
-  <si>
-    <t>ABSTRACT</t>
-  </si>
-  <si>
-    <t>SS</t>
   </si>
   <si>
     <t xml:space="preserve">ગોળજ ગામે ઉનાળીયા ચેરમેનના ઘર થી ખૂટતા સી.સી. રસ્તાનું કામ . </t>
@@ -584,10 +509,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="4">
-    <numFmt numFmtId="171" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="199" formatCode="0.000"/>
-    <numFmt numFmtId="207" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="208" formatCode="[$-7000447]0"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="[$-7000447]0"/>
   </numFmts>
   <fonts count="57">
     <font>
@@ -1336,11 +1261,11 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="417">
+  <cellXfs count="416">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1437,12 +1362,8 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="208" fontId="34" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="34" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1503,11 +1424,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="20" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1515,7 +1436,7 @@
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1523,7 +1444,7 @@
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="20" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1547,22 +1468,22 @@
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="22" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="22" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1573,7 +1494,7 @@
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1581,15 +1502,15 @@
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="23" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="22" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="22" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1597,7 +1518,7 @@
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1605,7 +1526,7 @@
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1613,14 +1534,14 @@
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -1628,11 +1549,11 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -1640,18 +1561,18 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyProtection="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="35" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="35" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="36" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1666,7 +1587,7 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="38" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1694,7 +1615,7 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="199" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1709,7 +1630,7 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="207" fontId="20" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -1727,17 +1648,17 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="2" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="199" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
@@ -1761,7 +1682,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="199" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1801,7 +1722,7 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="199" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
@@ -1823,7 +1744,7 @@
     <xf numFmtId="2" fontId="21" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="199" fontId="21" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
@@ -1835,16 +1756,16 @@
     <xf numFmtId="2" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="199" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="199" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="199" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="2" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1871,7 +1792,7 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="207" fontId="40" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="40" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -1904,7 +1825,7 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="199" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1922,7 +1843,7 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="38" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="33" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
@@ -2123,18 +2044,18 @@
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="171" fontId="42" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="2" fontId="42" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="42" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="42" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2151,6 +2072,156 @@
     <xf numFmtId="2" fontId="36" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="31" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="34" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2159,166 +2230,13 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="20" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="31" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="208" fontId="34" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="40" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="38" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="38" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2366,6 +2284,9 @@
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2454,10 +2375,10 @@
     <xf numFmtId="0" fontId="50" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="199" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="199" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
@@ -2545,92 +2466,92 @@
     <xf numFmtId="0" fontId="50" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="52" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="42" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="42" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="52" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="36" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="42" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="42" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="171" fontId="42" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3198,17 +3119,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="30.75" customHeight="1" thickBot="1">
-      <c r="A1" s="282" t="s">
-        <v>157</v>
-      </c>
-      <c r="B1" s="283"/>
-      <c r="C1" s="283"/>
-      <c r="D1" s="283"/>
-      <c r="E1" s="283"/>
-      <c r="F1" s="283"/>
-      <c r="G1" s="283"/>
-      <c r="H1" s="283"/>
-      <c r="I1" s="284"/>
+      <c r="A1" s="279" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" s="280"/>
+      <c r="C1" s="280"/>
+      <c r="D1" s="280"/>
+      <c r="E1" s="280"/>
+      <c r="F1" s="280"/>
+      <c r="G1" s="280"/>
+      <c r="H1" s="280"/>
+      <c r="I1" s="281"/>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="4"/>
@@ -3222,32 +3143,30 @@
       <c r="I2" s="6"/>
     </row>
     <row r="3" spans="1:15" ht="15">
-      <c r="A3" s="276" t="s">
+      <c r="A3" s="273" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="277"/>
-      <c r="C3" s="277"/>
+      <c r="B3" s="274"/>
+      <c r="C3" s="274"/>
       <c r="D3" s="23" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="E3" s="24"/>
       <c r="F3" s="31" t="s">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="G3" s="31" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="H3" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="J3" s="278" t="s">
-        <v>64</v>
-      </c>
-      <c r="K3" s="278"/>
-      <c r="L3" s="278"/>
-      <c r="M3" s="278"/>
-      <c r="N3" s="278"/>
-      <c r="O3" s="279"/>
+        <v>136</v>
+      </c>
+      <c r="J3" s="275"/>
+      <c r="K3" s="275"/>
+      <c r="L3" s="275"/>
+      <c r="M3" s="275"/>
+      <c r="N3" s="275"/>
+      <c r="O3" s="276"/>
     </row>
     <row r="4" spans="1:15" ht="15">
       <c r="A4" s="21"/>
@@ -3261,39 +3180,37 @@
       <c r="I4" s="8"/>
     </row>
     <row r="5" spans="1:15" ht="15">
-      <c r="A5" s="276" t="s">
+      <c r="A5" s="273" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="277"/>
-      <c r="C5" s="277"/>
+      <c r="B5" s="274"/>
+      <c r="C5" s="274"/>
       <c r="D5" s="23" t="s">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="E5" s="24"/>
       <c r="F5" s="31" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="I5" s="31" t="s">
-        <v>163</v>
-      </c>
-      <c r="J5" s="274" t="s">
-        <v>66</v>
-      </c>
-      <c r="K5" s="274"/>
-      <c r="L5" s="274"/>
-      <c r="M5" s="274"/>
-      <c r="N5" s="274"/>
-      <c r="O5" s="275"/>
+        <v>138</v>
+      </c>
+      <c r="J5" s="271"/>
+      <c r="K5" s="271"/>
+      <c r="L5" s="271"/>
+      <c r="M5" s="271"/>
+      <c r="N5" s="271"/>
+      <c r="O5" s="272"/>
     </row>
     <row r="6" spans="1:15" ht="15">
       <c r="A6" s="21"/>
       <c r="B6" s="22"/>
       <c r="C6" s="22"/>
       <c r="D6" s="23" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="E6" s="26"/>
       <c r="F6" s="7"/>
@@ -3302,11 +3219,11 @@
       <c r="I6" s="8"/>
     </row>
     <row r="7" spans="1:15" ht="15">
-      <c r="A7" s="276" t="s">
+      <c r="A7" s="273" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="277"/>
-      <c r="C7" s="277"/>
+      <c r="B7" s="274"/>
+      <c r="C7" s="274"/>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
@@ -3326,19 +3243,19 @@
       <c r="I8" s="8"/>
     </row>
     <row r="9" spans="1:15" ht="20.399999999999999">
-      <c r="A9" s="276" t="s">
+      <c r="A9" s="273" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="277"/>
-      <c r="C9" s="277"/>
-      <c r="D9" s="280" t="s">
-        <v>150</v>
-      </c>
-      <c r="E9" s="280"/>
-      <c r="F9" s="280"/>
-      <c r="G9" s="280"/>
-      <c r="H9" s="280"/>
-      <c r="I9" s="281"/>
+      <c r="B9" s="274"/>
+      <c r="C9" s="274"/>
+      <c r="D9" s="277" t="s">
+        <v>127</v>
+      </c>
+      <c r="E9" s="277"/>
+      <c r="F9" s="277"/>
+      <c r="G9" s="277"/>
+      <c r="H9" s="277"/>
+      <c r="I9" s="278"/>
       <c r="J9" s="9"/>
     </row>
     <row r="10" spans="1:15" ht="15">
@@ -3353,11 +3270,11 @@
       <c r="I10" s="8"/>
     </row>
     <row r="11" spans="1:15" ht="15">
-      <c r="A11" s="276" t="s">
+      <c r="A11" s="273" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="277"/>
-      <c r="C11" s="277"/>
+      <c r="B11" s="274"/>
+      <c r="C11" s="274"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
@@ -3377,11 +3294,11 @@
       <c r="I12" s="8"/>
     </row>
     <row r="13" spans="1:15" ht="15">
-      <c r="A13" s="276" t="s">
+      <c r="A13" s="273" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="277"/>
-      <c r="C13" s="277"/>
+      <c r="B13" s="274"/>
+      <c r="C13" s="274"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
@@ -3401,11 +3318,11 @@
       <c r="I14" s="8"/>
     </row>
     <row r="15" spans="1:15" ht="15">
-      <c r="A15" s="276" t="s">
+      <c r="A15" s="273" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="277"/>
-      <c r="C15" s="277"/>
+      <c r="B15" s="274"/>
+      <c r="C15" s="274"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
@@ -3425,11 +3342,11 @@
       <c r="I16" s="8"/>
     </row>
     <row r="17" spans="1:19" ht="15">
-      <c r="A17" s="276" t="s">
+      <c r="A17" s="273" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="277"/>
-      <c r="C17" s="277"/>
+      <c r="B17" s="274"/>
+      <c r="C17" s="274"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
@@ -3448,82 +3365,80 @@
       <c r="H18" s="7"/>
       <c r="I18" s="8"/>
     </row>
-    <row r="19" spans="1:19" s="35" customFormat="1" ht="15" customHeight="1">
-      <c r="A19" s="285" t="s">
-        <v>169</v>
-      </c>
-      <c r="B19" s="285"/>
-      <c r="C19" s="285"/>
-      <c r="D19" s="285"/>
-      <c r="E19" s="285"/>
-      <c r="F19" s="285"/>
-      <c r="G19" s="285"/>
-      <c r="H19" s="289" t="s">
-        <v>168</v>
-      </c>
-      <c r="I19" s="290"/>
-      <c r="J19" s="272" t="s">
-        <v>57</v>
-      </c>
-      <c r="K19" s="273"/>
-      <c r="L19" s="273"/>
-      <c r="M19" s="273"/>
-      <c r="N19" s="273"/>
-      <c r="O19" s="273"/>
-      <c r="P19" s="273"/>
-      <c r="Q19" s="273"/>
-      <c r="R19" s="273"/>
-    </row>
-    <row r="20" spans="1:19" s="36" customFormat="1" ht="28.8" customHeight="1">
-      <c r="A20" s="285" t="s">
-        <v>170</v>
-      </c>
-      <c r="B20" s="285"/>
-      <c r="C20" s="285"/>
-      <c r="D20" s="285"/>
-      <c r="E20" s="285"/>
-      <c r="F20" s="285"/>
-      <c r="G20" s="285"/>
-      <c r="H20" s="285"/>
-      <c r="I20" s="286"/>
-      <c r="J20" s="272"/>
-      <c r="K20" s="273"/>
-      <c r="L20" s="273"/>
-      <c r="M20" s="273"/>
-      <c r="N20" s="273"/>
-      <c r="O20" s="273"/>
-      <c r="P20" s="273"/>
-      <c r="Q20" s="273"/>
-      <c r="R20" s="273"/>
+    <row r="19" spans="1:19" s="34" customFormat="1" ht="15" customHeight="1">
+      <c r="A19" s="282" t="s">
+        <v>144</v>
+      </c>
+      <c r="B19" s="282"/>
+      <c r="C19" s="282"/>
+      <c r="D19" s="282"/>
+      <c r="E19" s="282"/>
+      <c r="F19" s="282"/>
+      <c r="G19" s="282"/>
+      <c r="H19" s="286" t="s">
+        <v>143</v>
+      </c>
+      <c r="I19" s="287"/>
+      <c r="J19" s="314"/>
+      <c r="K19" s="315"/>
+      <c r="L19" s="315"/>
+      <c r="M19" s="315"/>
+      <c r="N19" s="315"/>
+      <c r="O19" s="315"/>
+      <c r="P19" s="315"/>
+      <c r="Q19" s="315"/>
+      <c r="R19" s="315"/>
+    </row>
+    <row r="20" spans="1:19" s="35" customFormat="1" ht="28.8" customHeight="1">
+      <c r="A20" s="282" t="s">
+        <v>145</v>
+      </c>
+      <c r="B20" s="282"/>
+      <c r="C20" s="282"/>
+      <c r="D20" s="282"/>
+      <c r="E20" s="282"/>
+      <c r="F20" s="282"/>
+      <c r="G20" s="282"/>
+      <c r="H20" s="282"/>
+      <c r="I20" s="283"/>
+      <c r="J20" s="314"/>
+      <c r="K20" s="315"/>
+      <c r="L20" s="315"/>
+      <c r="M20" s="315"/>
+      <c r="N20" s="315"/>
+      <c r="O20" s="315"/>
+      <c r="P20" s="315"/>
+      <c r="Q20" s="315"/>
+      <c r="R20" s="315"/>
     </row>
     <row r="21" spans="1:19" ht="45" customHeight="1">
-      <c r="A21" s="287" t="s">
-        <v>90</v>
-      </c>
-      <c r="B21" s="288"/>
-      <c r="C21" s="315" t="s">
-        <v>155</v>
-      </c>
-      <c r="D21" s="315"/>
-      <c r="E21" s="315"/>
-      <c r="F21" s="315"/>
-      <c r="G21" s="315"/>
-      <c r="H21" s="315"/>
-      <c r="I21" s="316"/>
+      <c r="A21" s="284" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" s="285"/>
+      <c r="C21" s="311" t="s">
+        <v>130</v>
+      </c>
+      <c r="D21" s="311"/>
+      <c r="E21" s="311"/>
+      <c r="F21" s="311"/>
+      <c r="G21" s="311"/>
+      <c r="H21" s="311"/>
+      <c r="I21" s="312"/>
     </row>
     <row r="22" spans="1:19" ht="17.25" customHeight="1">
-      <c r="A22" s="308" t="s">
+      <c r="A22" s="304" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="309"/>
-      <c r="C22" s="309"/>
-      <c r="D22" s="309"/>
-      <c r="E22" s="309"/>
-      <c r="F22" s="309"/>
-      <c r="G22" s="298">
+      <c r="B22" s="305"/>
+      <c r="C22" s="305"/>
+      <c r="D22" s="305"/>
+      <c r="E22" s="305"/>
+      <c r="F22" s="305"/>
+      <c r="G22" s="313">
         <v>100000</v>
       </c>
-      <c r="H22" s="298"/>
+      <c r="H22" s="313"/>
       <c r="I22" s="12"/>
     </row>
     <row r="23" spans="1:19" ht="15">
@@ -3590,19 +3505,19 @@
       <c r="I27" s="8"/>
     </row>
     <row r="28" spans="1:19" ht="15">
-      <c r="A28" s="296" t="s">
+      <c r="A28" s="293" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="297"/>
-      <c r="C28" s="297"/>
-      <c r="D28" s="294" t="s">
-        <v>151</v>
-      </c>
-      <c r="E28" s="294"/>
-      <c r="F28" s="294"/>
-      <c r="G28" s="294"/>
-      <c r="H28" s="294"/>
-      <c r="I28" s="295"/>
+      <c r="B28" s="294"/>
+      <c r="C28" s="294"/>
+      <c r="D28" s="291" t="s">
+        <v>128</v>
+      </c>
+      <c r="E28" s="291"/>
+      <c r="F28" s="291"/>
+      <c r="G28" s="291"/>
+      <c r="H28" s="291"/>
+      <c r="I28" s="292"/>
     </row>
     <row r="29" spans="1:19" ht="15">
       <c r="A29" s="27"/>
@@ -3616,20 +3531,20 @@
       <c r="I29" s="8"/>
     </row>
     <row r="30" spans="1:19" ht="15">
-      <c r="A30" s="296" t="s">
+      <c r="A30" s="293" t="s">
         <v>0</v>
       </c>
-      <c r="B30" s="297"/>
-      <c r="C30" s="297"/>
-      <c r="D30" s="294" t="str">
+      <c r="B30" s="294"/>
+      <c r="C30" s="294"/>
+      <c r="D30" s="291" t="str">
         <f>D28</f>
         <v>MR.V.A.THAKOR. A.A.E.</v>
       </c>
-      <c r="E30" s="294"/>
-      <c r="F30" s="294"/>
-      <c r="G30" s="294"/>
-      <c r="H30" s="294"/>
-      <c r="I30" s="295"/>
+      <c r="E30" s="291"/>
+      <c r="F30" s="291"/>
+      <c r="G30" s="291"/>
+      <c r="H30" s="291"/>
+      <c r="I30" s="292"/>
     </row>
     <row r="31" spans="1:19" ht="17.399999999999999" customHeight="1">
       <c r="A31" s="27"/>
@@ -3641,140 +3556,136 @@
       <c r="G31" s="7"/>
       <c r="H31" s="7"/>
       <c r="I31" s="8"/>
-      <c r="K31" s="304" t="s">
-        <v>82</v>
-      </c>
-      <c r="L31" s="304"/>
-      <c r="M31" s="304"/>
-      <c r="N31" s="304"/>
-      <c r="O31" s="304"/>
-      <c r="P31" s="304"/>
-      <c r="Q31" s="304"/>
-      <c r="R31" s="304"/>
-      <c r="S31" s="304"/>
+      <c r="K31" s="300"/>
+      <c r="L31" s="300"/>
+      <c r="M31" s="300"/>
+      <c r="N31" s="300"/>
+      <c r="O31" s="300"/>
+      <c r="P31" s="300"/>
+      <c r="Q31" s="300"/>
+      <c r="R31" s="300"/>
+      <c r="S31" s="300"/>
     </row>
     <row r="32" spans="1:19" ht="15">
-      <c r="A32" s="310" t="s">
+      <c r="A32" s="306" t="s">
         <v>18</v>
       </c>
-      <c r="B32" s="311"/>
-      <c r="C32" s="311"/>
-      <c r="D32" s="292"/>
-      <c r="E32" s="292"/>
-      <c r="F32" s="292"/>
-      <c r="G32" s="292"/>
-      <c r="H32" s="292"/>
-      <c r="I32" s="293"/>
-      <c r="K32" s="305"/>
-      <c r="L32" s="305"/>
-      <c r="M32" s="305"/>
-      <c r="N32" s="305"/>
-      <c r="O32" s="305"/>
-      <c r="P32" s="305"/>
-      <c r="Q32" s="305"/>
-      <c r="R32" s="305"/>
-      <c r="S32" s="305"/>
+      <c r="B32" s="307"/>
+      <c r="C32" s="307"/>
+      <c r="D32" s="289"/>
+      <c r="E32" s="289"/>
+      <c r="F32" s="289"/>
+      <c r="G32" s="289"/>
+      <c r="H32" s="289"/>
+      <c r="I32" s="290"/>
+      <c r="K32" s="301"/>
+      <c r="L32" s="301"/>
+      <c r="M32" s="301"/>
+      <c r="N32" s="301"/>
+      <c r="O32" s="301"/>
+      <c r="P32" s="301"/>
+      <c r="Q32" s="301"/>
+      <c r="R32" s="301"/>
+      <c r="S32" s="301"/>
     </row>
     <row r="33" spans="1:19" ht="25.5" customHeight="1">
-      <c r="A33" s="300" t="s">
-        <v>63</v>
-      </c>
-      <c r="B33" s="301"/>
-      <c r="C33" s="301"/>
-      <c r="D33" s="301"/>
-      <c r="E33" s="301"/>
-      <c r="F33" s="301"/>
-      <c r="G33" s="301"/>
-      <c r="H33" s="301"/>
-      <c r="I33" s="302"/>
-      <c r="K33" s="305"/>
-      <c r="L33" s="305"/>
-      <c r="M33" s="305"/>
-      <c r="N33" s="305"/>
-      <c r="O33" s="305"/>
-      <c r="P33" s="305"/>
-      <c r="Q33" s="305"/>
-      <c r="R33" s="305"/>
-      <c r="S33" s="305"/>
+      <c r="A33" s="296" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" s="297"/>
+      <c r="C33" s="297"/>
+      <c r="D33" s="297"/>
+      <c r="E33" s="297"/>
+      <c r="F33" s="297"/>
+      <c r="G33" s="297"/>
+      <c r="H33" s="297"/>
+      <c r="I33" s="298"/>
+      <c r="K33" s="301"/>
+      <c r="L33" s="301"/>
+      <c r="M33" s="301"/>
+      <c r="N33" s="301"/>
+      <c r="O33" s="301"/>
+      <c r="P33" s="301"/>
+      <c r="Q33" s="301"/>
+      <c r="R33" s="301"/>
+      <c r="S33" s="301"/>
     </row>
     <row r="34" spans="1:19" ht="42" customHeight="1">
       <c r="A34" s="29" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B34" s="33">
         <v>6</v>
       </c>
-      <c r="C34" s="306" t="s">
-        <v>152</v>
-      </c>
-      <c r="D34" s="306"/>
-      <c r="E34" s="306"/>
-      <c r="F34" s="306"/>
-      <c r="G34" s="306"/>
-      <c r="H34" s="306"/>
-      <c r="I34" s="307"/>
-      <c r="K34" s="305"/>
-      <c r="L34" s="305"/>
-      <c r="M34" s="305"/>
-      <c r="N34" s="305"/>
-      <c r="O34" s="305"/>
-      <c r="P34" s="305"/>
-      <c r="Q34" s="305"/>
-      <c r="R34" s="305"/>
-      <c r="S34" s="305"/>
+      <c r="C34" s="302" t="s">
+        <v>129</v>
+      </c>
+      <c r="D34" s="302"/>
+      <c r="E34" s="302"/>
+      <c r="F34" s="302"/>
+      <c r="G34" s="302"/>
+      <c r="H34" s="302"/>
+      <c r="I34" s="303"/>
+      <c r="K34" s="301"/>
+      <c r="L34" s="301"/>
+      <c r="M34" s="301"/>
+      <c r="N34" s="301"/>
+      <c r="O34" s="301"/>
+      <c r="P34" s="301"/>
+      <c r="Q34" s="301"/>
+      <c r="R34" s="301"/>
+      <c r="S34" s="301"/>
     </row>
     <row r="35" spans="1:19" ht="42" customHeight="1">
       <c r="A35" s="29" t="s">
-        <v>146</v>
-      </c>
-      <c r="B35" s="303" t="s">
-        <v>156</v>
-      </c>
-      <c r="C35" s="303"/>
-      <c r="D35" s="34" t="s">
-        <v>148</v>
-      </c>
-      <c r="E35" s="38" t="s">
-        <v>147</v>
-      </c>
-      <c r="F35" s="306" t="str">
+        <v>124</v>
+      </c>
+      <c r="B35" s="299" t="s">
+        <v>131</v>
+      </c>
+      <c r="C35" s="299"/>
+      <c r="D35" s="299"/>
+      <c r="E35" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="F35" s="302" t="str">
         <f>D9</f>
         <v>ધારા ફંડ વર્ષ ૨૦૨૫-૨૬.</v>
       </c>
-      <c r="G35" s="306"/>
-      <c r="H35" s="306"/>
-      <c r="I35" s="307"/>
-      <c r="K35" s="305"/>
-      <c r="L35" s="305"/>
-      <c r="M35" s="305"/>
-      <c r="N35" s="305"/>
-      <c r="O35" s="305"/>
-      <c r="P35" s="305"/>
-      <c r="Q35" s="305"/>
-      <c r="R35" s="305"/>
-      <c r="S35" s="305"/>
+      <c r="G35" s="302"/>
+      <c r="H35" s="302"/>
+      <c r="I35" s="303"/>
+      <c r="K35" s="301"/>
+      <c r="L35" s="301"/>
+      <c r="M35" s="301"/>
+      <c r="N35" s="301"/>
+      <c r="O35" s="301"/>
+      <c r="P35" s="301"/>
+      <c r="Q35" s="301"/>
+      <c r="R35" s="301"/>
+      <c r="S35" s="301"/>
     </row>
     <row r="36" spans="1:19" ht="91.5" customHeight="1">
-      <c r="A36" s="312" t="s">
-        <v>166</v>
-      </c>
-      <c r="B36" s="313"/>
-      <c r="C36" s="313"/>
-      <c r="D36" s="313"/>
-      <c r="E36" s="313"/>
-      <c r="F36" s="313"/>
-      <c r="G36" s="313"/>
-      <c r="H36" s="313"/>
-      <c r="I36" s="314"/>
-      <c r="K36" s="305"/>
-      <c r="L36" s="305"/>
-      <c r="M36" s="305"/>
-      <c r="N36" s="305"/>
-      <c r="O36" s="305"/>
-      <c r="P36" s="305"/>
-      <c r="Q36" s="305"/>
-      <c r="R36" s="305"/>
-      <c r="S36" s="305"/>
+      <c r="A36" s="308" t="s">
+        <v>141</v>
+      </c>
+      <c r="B36" s="309"/>
+      <c r="C36" s="309"/>
+      <c r="D36" s="309"/>
+      <c r="E36" s="309"/>
+      <c r="F36" s="309"/>
+      <c r="G36" s="309"/>
+      <c r="H36" s="309"/>
+      <c r="I36" s="310"/>
+      <c r="K36" s="301"/>
+      <c r="L36" s="301"/>
+      <c r="M36" s="301"/>
+      <c r="N36" s="301"/>
+      <c r="O36" s="301"/>
+      <c r="P36" s="301"/>
+      <c r="Q36" s="301"/>
+      <c r="R36" s="301"/>
+      <c r="S36" s="301"/>
     </row>
     <row r="37" spans="1:19" ht="23.4" customHeight="1">
       <c r="A37" s="13"/>
@@ -3793,11 +3704,11 @@
       <c r="C38" s="5"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
-      <c r="F38" s="299" t="s">
-        <v>76</v>
-      </c>
-      <c r="G38" s="299"/>
-      <c r="H38" s="299"/>
+      <c r="F38" s="295" t="s">
+        <v>73</v>
+      </c>
+      <c r="G38" s="295"/>
+      <c r="H38" s="295"/>
       <c r="I38" s="15"/>
     </row>
     <row r="39" spans="1:19" ht="15.6">
@@ -3807,10 +3718,10 @@
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
       <c r="F39" s="30" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="G39" s="30"/>
-      <c r="H39" s="37" t="str">
+      <c r="H39" s="36" t="str">
         <f>H19</f>
         <v>Thasra</v>
       </c>
@@ -3822,9 +3733,9 @@
       <c r="C40" s="17"/>
       <c r="D40" s="18"/>
       <c r="E40" s="18"/>
-      <c r="F40" s="291"/>
-      <c r="G40" s="291"/>
-      <c r="H40" s="291"/>
+      <c r="F40" s="288"/>
+      <c r="G40" s="288"/>
+      <c r="H40" s="288"/>
       <c r="I40" s="19"/>
     </row>
     <row r="41" spans="1:19">
@@ -3884,23 +3795,23 @@
     <mergeCell ref="C21:I21"/>
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="F35:I35"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="J19:R20"/>
+    <mergeCell ref="B35:D35"/>
     <mergeCell ref="F40:H40"/>
     <mergeCell ref="D32:I32"/>
     <mergeCell ref="D30:I30"/>
     <mergeCell ref="D28:I28"/>
     <mergeCell ref="A30:C30"/>
-    <mergeCell ref="G22:H22"/>
     <mergeCell ref="F38:H38"/>
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A33:I33"/>
-    <mergeCell ref="B35:C35"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A20:I20"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="H19:I19"/>
-    <mergeCell ref="J19:R20"/>
     <mergeCell ref="J5:O5"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="J3:O3"/>
@@ -3920,112 +3831,87 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:M167"/>
+  <dimension ref="A1:I167"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="83" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.44140625" style="86" customWidth="1"/>
-    <col min="3" max="3" width="58.5546875" style="40" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" style="86" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.33203125" style="40" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" style="86" customWidth="1"/>
-    <col min="7" max="7" width="12.88671875" style="40" customWidth="1"/>
-    <col min="8" max="9" width="9.109375" style="40"/>
-    <col min="10" max="10" width="12.88671875" style="40" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" style="40" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.88671875" style="40" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.109375" style="40"/>
+    <col min="1" max="1" width="14.6640625" style="82" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" style="85" customWidth="1"/>
+    <col min="3" max="3" width="58.5546875" style="39" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" style="85" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.33203125" style="39" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" style="85" customWidth="1"/>
+    <col min="7" max="7" width="12.88671875" style="39" customWidth="1"/>
+    <col min="8" max="9" width="9.109375" style="39"/>
+    <col min="10" max="10" width="12.88671875" style="39" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" style="39" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.88671875" style="39" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.109375" style="39"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="45" customHeight="1" thickBot="1">
-      <c r="A1" s="320" t="s">
-        <v>67</v>
-      </c>
-      <c r="B1" s="320"/>
-      <c r="C1" s="320"/>
-      <c r="D1" s="320"/>
-      <c r="E1" s="320"/>
-      <c r="F1" s="320"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="40">
-        <v>60.39</v>
-      </c>
-      <c r="K1" s="40">
-        <v>104.2</v>
-      </c>
-      <c r="L1" s="40">
-        <f>J1*K1</f>
-        <v>6292.6379999999999</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="35.4" thickBot="1">
-      <c r="A2" s="89" t="str">
+    <row r="1" spans="1:9" ht="45" customHeight="1" thickBot="1">
+      <c r="A1" s="318" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="318"/>
+      <c r="C1" s="318"/>
+      <c r="D1" s="318"/>
+      <c r="E1" s="318"/>
+      <c r="F1" s="318"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+    </row>
+    <row r="2" spans="1:9" ht="35.4" thickBot="1">
+      <c r="A2" s="88" t="str">
         <f>'FACE SHEET'!A21</f>
         <v>કામ નું નામ :</v>
       </c>
-      <c r="B2" s="333" t="str">
+      <c r="B2" s="332" t="str">
         <f>'FACE SHEET'!C21</f>
         <v xml:space="preserve">ગોળજ ગામે ઉનાળીયા ચેરમેનના ઘર થી ખૂટતા સી.સી. રસ્તાનું કામ . </v>
       </c>
-      <c r="C2" s="333"/>
-      <c r="D2" s="333"/>
-      <c r="E2" s="333"/>
-      <c r="F2" s="334"/>
-      <c r="J2" s="40">
-        <f>J1</f>
-        <v>60.39</v>
-      </c>
-      <c r="K2" s="40">
-        <v>156.56</v>
-      </c>
-      <c r="L2" s="40">
-        <f>J2*K2</f>
-        <v>9454.6584000000003</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" s="2" customFormat="1" ht="61.2" customHeight="1">
-      <c r="A3" s="90" t="s">
+      <c r="C2" s="332"/>
+      <c r="D2" s="332"/>
+      <c r="E2" s="332"/>
+      <c r="F2" s="333"/>
+    </row>
+    <row r="3" spans="1:9" s="2" customFormat="1" ht="61.2" customHeight="1">
+      <c r="A3" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="91" t="s">
+      <c r="B3" s="90" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="91" t="s">
+      <c r="C3" s="90" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="92" t="s">
+      <c r="D3" s="91" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="91" t="s">
+      <c r="E3" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="91" t="s">
+      <c r="F3" s="90" t="s">
         <v>4</v>
       </c>
       <c r="G3" s="1"/>
-      <c r="L3" s="2">
-        <f>L1-L2</f>
-        <v>-3162.0204000000003</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" s="41" customFormat="1" ht="70.95" customHeight="1">
-      <c r="A4" s="325">
+    </row>
+    <row r="4" spans="1:9" s="40" customFormat="1" ht="70.95" customHeight="1">
+      <c r="A4" s="323">
         <f>Measurement!K6</f>
         <v>36</v>
       </c>
-      <c r="B4" s="318" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" s="93" t="str">
+      <c r="B4" s="331" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="92" t="str">
         <f>Measurement!A5</f>
         <v xml:space="preserve">Item No.1 :- Box cutting the road surface to proper slope and camber for making a base for road work including removing the excavated stuff and depositing on the road side slope as deirected up to 50 m. lead. </v>
       </c>
-      <c r="D4" s="94">
+      <c r="D4" s="93">
         <v>156.56</v>
       </c>
-      <c r="E4" s="319" t="str">
+      <c r="E4" s="316" t="str">
         <f>B4</f>
         <v>Cmt</v>
       </c>
@@ -4033,66 +3919,40 @@
         <f>A4*D5</f>
         <v>5692.32</v>
       </c>
-      <c r="H4" s="41">
-        <v>1</v>
-      </c>
-      <c r="I4" s="42">
-        <f>Measurement!K6</f>
-        <v>36</v>
-      </c>
-      <c r="J4" s="41">
-        <v>150.84</v>
-      </c>
-      <c r="K4" s="41">
-        <f t="shared" ref="K4:K12" si="0">I4*J4</f>
-        <v>5430.24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" s="41" customFormat="1">
-      <c r="A5" s="325"/>
-      <c r="B5" s="318"/>
-      <c r="C5" s="95" t="s">
-        <v>145</v>
-      </c>
-      <c r="D5" s="94">
+      <c r="I4" s="41"/>
+    </row>
+    <row r="5" spans="1:9" s="40" customFormat="1">
+      <c r="A5" s="323"/>
+      <c r="B5" s="331"/>
+      <c r="C5" s="94" t="s">
+        <v>123</v>
+      </c>
+      <c r="D5" s="93">
         <f>TRUNC((D4*1.01),2)</f>
         <v>158.12</v>
       </c>
-      <c r="E5" s="319"/>
+      <c r="E5" s="316"/>
       <c r="F5" s="317"/>
-      <c r="H5" s="41">
-        <v>2</v>
-      </c>
-      <c r="I5" s="42">
+      <c r="I5" s="41"/>
+    </row>
+    <row r="6" spans="1:9" s="40" customFormat="1" ht="48.6" customHeight="1">
+      <c r="A6" s="323">
         <f>Measurement!K11</f>
         <v>16.559999999999999</v>
       </c>
-      <c r="J5" s="41">
-        <v>662.8</v>
-      </c>
-      <c r="K5" s="41">
-        <f t="shared" si="0"/>
-        <v>10975.967999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" s="41" customFormat="1" ht="48.6" customHeight="1">
-      <c r="A6" s="325">
-        <f>Measurement!K11</f>
-        <v>16.559999999999999</v>
-      </c>
-      <c r="B6" s="318" t="str">
+      <c r="B6" s="331" t="str">
         <f>Measurement!L11</f>
         <v>Cmt</v>
       </c>
-      <c r="C6" s="93" t="str">
+      <c r="C6" s="92" t="str">
         <f>Measurement!A8</f>
         <v xml:space="preserve">Item No.2 :- Supplying of crsuhed stone aggregate,chipping etc. of hard stones of following nominal size free of disintegrated pieces deletarious and organic mater </v>
       </c>
-      <c r="D6" s="94">
+      <c r="D6" s="93">
         <f>Schedule!I4</f>
         <v>677.82999999999993</v>
       </c>
-      <c r="E6" s="319" t="str">
+      <c r="E6" s="316" t="str">
         <f>B6</f>
         <v>Cmt</v>
       </c>
@@ -4100,65 +3960,39 @@
         <f>A6*D7</f>
         <v>11336.975999999999</v>
       </c>
-      <c r="H6" s="41">
-        <v>3</v>
-      </c>
-      <c r="I6" s="43">
+      <c r="I6" s="42"/>
+    </row>
+    <row r="7" spans="1:9" s="40" customFormat="1">
+      <c r="A7" s="323"/>
+      <c r="B7" s="331"/>
+      <c r="C7" s="94" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="93">
+        <f>TRUNC((D6*1.01),2)</f>
+        <v>684.6</v>
+      </c>
+      <c r="E7" s="316"/>
+      <c r="F7" s="317"/>
+      <c r="I7" s="42"/>
+    </row>
+    <row r="8" spans="1:9" s="40" customFormat="1" ht="48" customHeight="1">
+      <c r="A8" s="323">
         <f>Measurement!K14</f>
         <v>4.1399999999999997</v>
       </c>
-      <c r="J6" s="41">
-        <v>64.64</v>
-      </c>
-      <c r="K6" s="41">
-        <f t="shared" si="0"/>
-        <v>267.6096</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" s="41" customFormat="1">
-      <c r="A7" s="325"/>
-      <c r="B7" s="318"/>
-      <c r="C7" s="95" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7" s="94">
-        <f>TRUNC((D6*1.01),2)</f>
-        <v>684.6</v>
-      </c>
-      <c r="E7" s="319"/>
-      <c r="F7" s="317"/>
-      <c r="H7" s="41">
-        <v>4</v>
-      </c>
-      <c r="I7" s="43">
-        <f>Abstract!I5</f>
-        <v>16.559999999999999</v>
-      </c>
-      <c r="J7" s="41">
-        <v>166.5</v>
-      </c>
-      <c r="K7" s="41">
-        <f t="shared" si="0"/>
-        <v>2757.24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" s="41" customFormat="1" ht="48" customHeight="1">
-      <c r="A8" s="325">
-        <f>Measurement!K14</f>
-        <v>4.1399999999999997</v>
-      </c>
-      <c r="B8" s="318" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" s="93" t="str">
+      <c r="B8" s="331" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="92" t="str">
         <f>Measurement!A13</f>
         <v xml:space="preserve">Item No.3 :-  Supplying of crsuhed stone aggregate,chipping etc. of hard stones of following nominal size free of disintegrated pieces deletarious and organic mater </v>
       </c>
-      <c r="D8" s="94">
+      <c r="D8" s="93">
         <f>Schedule!I5</f>
         <v>171.8</v>
       </c>
-      <c r="E8" s="319" t="str">
+      <c r="E8" s="316" t="str">
         <f>B8</f>
         <v>Cmt</v>
       </c>
@@ -4166,67 +4000,38 @@
         <f>A8*D9</f>
         <v>718.33139999999992</v>
       </c>
-      <c r="H8" s="41">
-        <v>5</v>
-      </c>
-      <c r="I8" s="43">
-        <f>I6</f>
-        <v>4.1399999999999997</v>
-      </c>
-      <c r="J8" s="41">
-        <v>98.31</v>
-      </c>
-      <c r="K8" s="41">
-        <f t="shared" si="0"/>
-        <v>407.0034</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" s="41" customFormat="1">
-      <c r="A9" s="325"/>
-      <c r="B9" s="318"/>
-      <c r="C9" s="95" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="94">
+      <c r="I8" s="42"/>
+    </row>
+    <row r="9" spans="1:9" s="40" customFormat="1">
+      <c r="A9" s="323"/>
+      <c r="B9" s="331"/>
+      <c r="C9" s="94" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="93">
         <f>TRUNC((D8*1.01),2)</f>
         <v>173.51</v>
       </c>
-      <c r="E9" s="319"/>
+      <c r="E9" s="316"/>
       <c r="F9" s="317"/>
-      <c r="H9" s="41">
-        <v>6</v>
-      </c>
-      <c r="I9" s="43">
-        <f>Measurement!K4</f>
-        <v>120</v>
-      </c>
-      <c r="J9" s="41">
-        <v>17.93</v>
-      </c>
-      <c r="K9" s="41">
-        <f t="shared" si="0"/>
-        <v>2151.6</v>
-      </c>
-      <c r="M9" s="41">
-        <v>90103</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" s="41" customFormat="1" ht="78.599999999999994" customHeight="1">
-      <c r="A10" s="325">
+      <c r="I9" s="42"/>
+    </row>
+    <row r="10" spans="1:9" s="40" customFormat="1" ht="78.599999999999994" customHeight="1">
+      <c r="A10" s="323">
         <f>Measurement!K17</f>
         <v>16.559999999999999</v>
       </c>
-      <c r="B10" s="318" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" s="93" t="str">
+      <c r="B10" s="331" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" s="92" t="str">
         <f>Measurement!A16</f>
         <v xml:space="preserve">Item No. :- 4 Spreading the stone aggregates for soiling and W. B. M. including filling the inter stices forming the surface to required camber and gradient (excluding spreading of blindage) (ii) 40 mm to 63 mm size aggreates (HB) </v>
       </c>
-      <c r="D10" s="94">
+      <c r="D10" s="93">
         <v>247.28</v>
       </c>
-      <c r="E10" s="319" t="str">
+      <c r="E10" s="316" t="str">
         <f>B10</f>
         <v>Cmt</v>
       </c>
@@ -4234,66 +4039,37 @@
         <f>A10*D11</f>
         <v>4135.8599999999997</v>
       </c>
-      <c r="H10" s="41">
-        <v>7</v>
-      </c>
-      <c r="I10" s="43">
-        <f>Measurement!K26</f>
-        <v>12</v>
-      </c>
-      <c r="J10" s="41">
-        <v>4744.37</v>
-      </c>
-      <c r="K10" s="41">
-        <f t="shared" si="0"/>
-        <v>56932.44</v>
-      </c>
-      <c r="M10" s="41">
-        <v>9063</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" s="41" customFormat="1">
-      <c r="A11" s="325"/>
-      <c r="B11" s="318"/>
-      <c r="C11" s="95" t="s">
-        <v>142</v>
-      </c>
-      <c r="D11" s="94">
+      <c r="I10" s="42"/>
+    </row>
+    <row r="11" spans="1:9" s="40" customFormat="1">
+      <c r="A11" s="323"/>
+      <c r="B11" s="331"/>
+      <c r="C11" s="94" t="s">
+        <v>120</v>
+      </c>
+      <c r="D11" s="93">
         <f>TRUNC((D10*1.01),2)</f>
         <v>249.75</v>
       </c>
-      <c r="E11" s="319"/>
+      <c r="E11" s="316"/>
       <c r="F11" s="317"/>
-      <c r="H11" s="41">
-        <v>8</v>
-      </c>
-      <c r="I11" s="41">
-        <v>1</v>
-      </c>
-      <c r="J11" s="41">
-        <v>2656</v>
-      </c>
-      <c r="K11" s="41">
-        <f t="shared" si="0"/>
-        <v>2656</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" s="41" customFormat="1" ht="49.95" customHeight="1">
-      <c r="A12" s="325">
+    </row>
+    <row r="12" spans="1:9" s="40" customFormat="1" ht="49.95" customHeight="1">
+      <c r="A12" s="323">
         <f>Measurement!K20</f>
         <v>4.1399999999999997</v>
       </c>
-      <c r="B12" s="318" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" s="93" t="str">
+      <c r="B12" s="331" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="92" t="str">
         <f>Measurement!A19</f>
         <v>Item No. 5 :-  Spreading blindage or road crust filling the  gaps in metal and levelling to gradient  and camber as directed (i) Murrum</v>
       </c>
-      <c r="D12" s="94">
+      <c r="D12" s="93">
         <v>146.01</v>
       </c>
-      <c r="E12" s="319" t="str">
+      <c r="E12" s="316" t="str">
         <f>B12</f>
         <v>Cmt</v>
       </c>
@@ -4301,52 +4077,35 @@
         <f>A12*D13</f>
         <v>610.5258</v>
       </c>
-      <c r="H12" s="41">
-        <v>9</v>
-      </c>
-      <c r="I12" s="41">
-        <v>1</v>
-      </c>
-      <c r="J12" s="41">
-        <v>312.85000000000002</v>
-      </c>
-      <c r="K12" s="41">
-        <f t="shared" si="0"/>
-        <v>312.85000000000002</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" s="41" customFormat="1">
-      <c r="A13" s="325"/>
-      <c r="B13" s="318"/>
-      <c r="C13" s="95" t="s">
-        <v>143</v>
-      </c>
-      <c r="D13" s="94">
+    </row>
+    <row r="13" spans="1:9" s="40" customFormat="1">
+      <c r="A13" s="323"/>
+      <c r="B13" s="331"/>
+      <c r="C13" s="94" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" s="93">
         <f>TRUNC((D12*1.01),2)</f>
         <v>147.47</v>
       </c>
-      <c r="E13" s="319"/>
+      <c r="E13" s="316"/>
       <c r="F13" s="317"/>
-      <c r="K13" s="41">
-        <f>SUM(K4:K12)</f>
-        <v>81890.951000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" s="41" customFormat="1" ht="96.6" hidden="1" customHeight="1">
-      <c r="A14" s="325">
+    </row>
+    <row r="14" spans="1:9" s="40" customFormat="1" ht="96.6" hidden="1" customHeight="1">
+      <c r="A14" s="323">
         <v>0</v>
       </c>
-      <c r="B14" s="318" t="s">
+      <c r="B14" s="331" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="93" t="str">
+      <c r="C14" s="92" t="str">
         <f>Measurement!A22</f>
         <v xml:space="preserve">Item No. 6 :- Rolling and consolidation water bound macadam (Except laterite and kankar) including watering not excceding 150 mm thickness ( main layer including binding  matenals) including filling in  depressions which occurs during the process (B) With power roller excceding 8 tonne and not excecding 12 tonne. </v>
       </c>
-      <c r="D14" s="94">
+      <c r="D14" s="93">
         <v>17.75</v>
       </c>
-      <c r="E14" s="319" t="str">
+      <c r="E14" s="316" t="str">
         <f>B14</f>
         <v>Smt</v>
       </c>
@@ -4355,36 +4114,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" s="41" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1">
-      <c r="A15" s="325"/>
-      <c r="B15" s="318"/>
-      <c r="C15" s="95" t="s">
-        <v>74</v>
-      </c>
-      <c r="D15" s="94">
+    <row r="15" spans="1:9" s="40" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1">
+      <c r="A15" s="323"/>
+      <c r="B15" s="331"/>
+      <c r="C15" s="94" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="93">
         <f>TRUNC((D14*1.01),2)</f>
         <v>17.920000000000002</v>
       </c>
-      <c r="E15" s="319"/>
+      <c r="E15" s="316"/>
       <c r="F15" s="317"/>
     </row>
-    <row r="16" spans="1:13" s="41" customFormat="1" ht="64.2" customHeight="1">
-      <c r="A16" s="325">
+    <row r="16" spans="1:9" s="40" customFormat="1" ht="64.2" customHeight="1">
+      <c r="A16" s="323">
         <f>Measurement!K26</f>
         <v>12</v>
       </c>
-      <c r="B16" s="318" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" s="93" t="str">
+      <c r="B16" s="331" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="92" t="str">
         <f>Measurement!A25</f>
         <v xml:space="preserve">Item No. :- 6 Providing and Laying Ordinary Ciment Concrete 1:2:4 exposed work with  Curing etc. Complete including compacting with surface mechanical vibrator,mechanical loater, channaling, from work, grooving, excluding cost of reinforcement for R.C.C work  . </v>
       </c>
-      <c r="D16" s="94">
+      <c r="D16" s="93">
         <f>RA!G14</f>
         <v>4866.3500000000004</v>
       </c>
-      <c r="E16" s="319" t="str">
+      <c r="E16" s="316" t="str">
         <f>B16</f>
         <v>Cmt</v>
       </c>
@@ -4393,34 +4152,34 @@
         <v>58980.12</v>
       </c>
     </row>
-    <row r="17" spans="1:8" s="41" customFormat="1">
-      <c r="A17" s="325"/>
-      <c r="B17" s="318"/>
-      <c r="C17" s="95" t="s">
-        <v>94</v>
-      </c>
-      <c r="D17" s="94">
+    <row r="17" spans="1:8" s="40" customFormat="1">
+      <c r="A17" s="323"/>
+      <c r="B17" s="331"/>
+      <c r="C17" s="94" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="93">
         <f>TRUNC((D16*1.01),2)</f>
         <v>4915.01</v>
       </c>
-      <c r="E17" s="319"/>
+      <c r="E17" s="316"/>
       <c r="F17" s="317"/>
     </row>
-    <row r="18" spans="1:8" s="41" customFormat="1" ht="45">
-      <c r="A18" s="325">
+    <row r="18" spans="1:8" s="40" customFormat="1" ht="45">
+      <c r="A18" s="323">
         <v>1</v>
       </c>
-      <c r="B18" s="318" t="s">
+      <c r="B18" s="331" t="s">
         <v>50</v>
       </c>
-      <c r="C18" s="93" t="s">
-        <v>118</v>
-      </c>
-      <c r="D18" s="94">
+      <c r="C18" s="92" t="s">
+        <v>114</v>
+      </c>
+      <c r="D18" s="93">
         <f>RA!G28</f>
         <v>2656</v>
       </c>
-      <c r="E18" s="319" t="str">
+      <c r="E18" s="316" t="str">
         <f>B18</f>
         <v>No</v>
       </c>
@@ -4429,32 +4188,32 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="19" spans="1:8" s="41" customFormat="1">
-      <c r="A19" s="325"/>
-      <c r="B19" s="318"/>
-      <c r="C19" s="95" t="s">
-        <v>119</v>
-      </c>
-      <c r="D19" s="94"/>
-      <c r="E19" s="319"/>
+    <row r="19" spans="1:8" s="40" customFormat="1">
+      <c r="A19" s="323"/>
+      <c r="B19" s="331"/>
+      <c r="C19" s="94" t="s">
+        <v>115</v>
+      </c>
+      <c r="D19" s="93"/>
+      <c r="E19" s="316"/>
       <c r="F19" s="317"/>
     </row>
-    <row r="20" spans="1:8" s="41" customFormat="1" ht="51" customHeight="1">
-      <c r="A20" s="325">
+    <row r="20" spans="1:8" s="40" customFormat="1" ht="51" customHeight="1">
+      <c r="A20" s="323">
         <f>Measurement!K29</f>
         <v>1</v>
       </c>
-      <c r="B20" s="318" t="s">
+      <c r="B20" s="331" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="93" t="str">
+      <c r="C20" s="92" t="str">
         <f>Measurement!A28</f>
         <v xml:space="preserve">Item No :- 7 Providing and fixing number plate of marble stone of required size set in C. M. 1 : 4 including finishing and engraving letters etc. complete.                </v>
       </c>
-      <c r="D20" s="94">
+      <c r="D20" s="93">
         <v>303.11</v>
       </c>
-      <c r="E20" s="319" t="str">
+      <c r="E20" s="316" t="str">
         <f>B20</f>
         <v>No</v>
       </c>
@@ -4463,1074 +4222,1074 @@
         <v>306.14</v>
       </c>
     </row>
-    <row r="21" spans="1:8" s="41" customFormat="1">
-      <c r="A21" s="325"/>
-      <c r="B21" s="318"/>
-      <c r="C21" s="95" t="s">
-        <v>144</v>
-      </c>
-      <c r="D21" s="94">
+    <row r="21" spans="1:8" s="40" customFormat="1">
+      <c r="A21" s="323"/>
+      <c r="B21" s="331"/>
+      <c r="C21" s="94" t="s">
+        <v>122</v>
+      </c>
+      <c r="D21" s="93">
         <f>TRUNC((D20*1.01),2)</f>
         <v>306.14</v>
       </c>
-      <c r="E21" s="319"/>
+      <c r="E21" s="316"/>
       <c r="F21" s="317"/>
     </row>
-    <row r="22" spans="1:8" s="44" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A22" s="323" t="s">
+    <row r="22" spans="1:8" s="43" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A22" s="321" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="324"/>
-      <c r="C22" s="324"/>
-      <c r="D22" s="324"/>
-      <c r="E22" s="324"/>
-      <c r="F22" s="96">
+      <c r="B22" s="322"/>
+      <c r="C22" s="322"/>
+      <c r="D22" s="322"/>
+      <c r="E22" s="322"/>
+      <c r="F22" s="95">
         <f>SUM(F4:F21)</f>
         <v>84436.273199999996</v>
       </c>
     </row>
-    <row r="23" spans="1:8" s="44" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A23" s="327" t="s">
-        <v>149</v>
-      </c>
-      <c r="B23" s="328"/>
-      <c r="C23" s="328"/>
-      <c r="D23" s="328"/>
-      <c r="E23" s="328"/>
-      <c r="F23" s="97">
+    <row r="23" spans="1:8" s="43" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A23" s="325" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="326"/>
+      <c r="C23" s="326"/>
+      <c r="D23" s="326"/>
+      <c r="E23" s="326"/>
+      <c r="F23" s="96">
         <f>F22*18%</f>
         <v>15198.529175999998</v>
       </c>
     </row>
-    <row r="24" spans="1:8" s="44" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A24" s="323" t="s">
+    <row r="24" spans="1:8" s="43" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A24" s="321" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="324"/>
-      <c r="C24" s="324"/>
-      <c r="D24" s="324"/>
-      <c r="E24" s="324"/>
-      <c r="F24" s="96">
+      <c r="B24" s="322"/>
+      <c r="C24" s="322"/>
+      <c r="D24" s="322"/>
+      <c r="E24" s="322"/>
+      <c r="F24" s="95">
         <f>F22+F23</f>
         <v>99634.802375999992</v>
       </c>
     </row>
-    <row r="25" spans="1:8" s="47" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A25" s="327" t="s">
-        <v>68</v>
-      </c>
-      <c r="B25" s="328"/>
-      <c r="C25" s="328"/>
-      <c r="D25" s="328"/>
-      <c r="E25" s="328"/>
-      <c r="F25" s="97">
+    <row r="25" spans="1:8" s="46" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A25" s="325" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" s="326"/>
+      <c r="C25" s="326"/>
+      <c r="D25" s="326"/>
+      <c r="E25" s="326"/>
+      <c r="F25" s="96">
         <f>'FACE SHEET'!G22</f>
         <v>100000</v>
       </c>
     </row>
-    <row r="26" spans="1:8" s="47" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A26" s="321"/>
-      <c r="B26" s="322"/>
-      <c r="C26" s="322"/>
-      <c r="D26" s="322"/>
-      <c r="E26" s="322"/>
-      <c r="F26" s="48" t="s">
+    <row r="26" spans="1:8" s="46" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A26" s="319"/>
+      <c r="B26" s="320"/>
+      <c r="C26" s="320"/>
+      <c r="D26" s="320"/>
+      <c r="E26" s="320"/>
+      <c r="F26" s="47" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" s="46" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A27" s="319"/>
+      <c r="B27" s="320"/>
+      <c r="C27" s="320"/>
+      <c r="D27" s="320"/>
+      <c r="E27" s="320"/>
+      <c r="F27" s="45"/>
+    </row>
+    <row r="28" spans="1:8" s="46" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A28" s="48"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="44"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="45"/>
+    </row>
+    <row r="29" spans="1:8" s="55" customFormat="1">
+      <c r="A29" s="49"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="51"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="54"/>
+    </row>
+    <row r="30" spans="1:8" s="55" customFormat="1">
+      <c r="A30" s="97" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" s="86"/>
+      <c r="C30" s="87"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="58"/>
+      <c r="H30" s="58"/>
+    </row>
+    <row r="31" spans="1:8" s="55" customFormat="1">
+      <c r="A31" s="98" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" s="47" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A27" s="321"/>
-      <c r="B27" s="322"/>
-      <c r="C27" s="322"/>
-      <c r="D27" s="322"/>
-      <c r="E27" s="322"/>
-      <c r="F27" s="46"/>
-    </row>
-    <row r="28" spans="1:8" s="47" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A28" s="49"/>
-      <c r="B28" s="45"/>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="46"/>
-    </row>
-    <row r="29" spans="1:8" s="56" customFormat="1">
-      <c r="A29" s="50"/>
-      <c r="B29" s="51"/>
-      <c r="C29" s="52"/>
-      <c r="D29" s="53"/>
-      <c r="E29" s="54"/>
-      <c r="F29" s="55"/>
-    </row>
-    <row r="30" spans="1:8" s="56" customFormat="1">
-      <c r="A30" s="98" t="s">
-        <v>86</v>
-      </c>
-      <c r="B30" s="87"/>
-      <c r="C30" s="88"/>
-      <c r="D30" s="57"/>
-      <c r="E30" s="57"/>
-      <c r="F30" s="58"/>
-      <c r="G30" s="59"/>
-      <c r="H30" s="59"/>
-    </row>
-    <row r="31" spans="1:8" s="56" customFormat="1">
-      <c r="A31" s="99" t="s">
-        <v>87</v>
-      </c>
-      <c r="B31" s="87"/>
-      <c r="C31" s="88"/>
-      <c r="D31" s="57"/>
-      <c r="E31" s="57"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="326"/>
-      <c r="H31" s="326"/>
-    </row>
-    <row r="32" spans="1:8" s="56" customFormat="1">
-      <c r="A32" s="329" t="s">
-        <v>88</v>
-      </c>
-      <c r="B32" s="330"/>
-      <c r="C32" s="60"/>
-      <c r="D32" s="57"/>
-      <c r="E32" s="57"/>
-      <c r="F32" s="58"/>
-      <c r="G32" s="326"/>
-      <c r="H32" s="326"/>
-    </row>
-    <row r="33" spans="1:8" s="56" customFormat="1" ht="17.399999999999999">
-      <c r="A33" s="61"/>
-      <c r="B33" s="62"/>
-      <c r="C33" s="63"/>
-      <c r="D33" s="64"/>
-      <c r="E33" s="63"/>
-      <c r="F33" s="65"/>
-      <c r="G33" s="66"/>
-      <c r="H33" s="40"/>
-    </row>
-    <row r="34" spans="1:8" s="56" customFormat="1">
-      <c r="A34" s="61"/>
-      <c r="B34" s="62"/>
-      <c r="C34" s="67"/>
-      <c r="D34" s="68"/>
-      <c r="E34" s="69"/>
-      <c r="F34" s="70"/>
-    </row>
-    <row r="35" spans="1:8" s="56" customFormat="1">
-      <c r="A35" s="61"/>
-      <c r="B35" s="62"/>
-      <c r="C35" s="67"/>
-      <c r="D35" s="68"/>
-      <c r="E35" s="69"/>
-      <c r="F35" s="70"/>
-    </row>
-    <row r="36" spans="1:8" s="56" customFormat="1">
-      <c r="A36" s="71"/>
-      <c r="B36" s="72"/>
-      <c r="C36" s="73"/>
-      <c r="D36" s="331"/>
-      <c r="E36" s="331"/>
-      <c r="F36" s="332"/>
-    </row>
-    <row r="37" spans="1:8" s="56" customFormat="1">
-      <c r="A37" s="74"/>
-      <c r="B37" s="74"/>
-      <c r="C37" s="75"/>
-      <c r="D37" s="76"/>
-      <c r="E37" s="77"/>
-      <c r="F37" s="76"/>
-    </row>
-    <row r="38" spans="1:8" s="56" customFormat="1">
-      <c r="A38" s="74"/>
-      <c r="B38" s="74"/>
-      <c r="C38" s="75"/>
-      <c r="D38" s="76"/>
-      <c r="E38" s="77"/>
-      <c r="F38" s="76"/>
-    </row>
-    <row r="39" spans="1:8" s="56" customFormat="1">
-      <c r="A39" s="74"/>
-      <c r="B39" s="74"/>
-      <c r="C39" s="75"/>
-      <c r="D39" s="76"/>
-      <c r="E39" s="77"/>
-      <c r="F39" s="76"/>
-    </row>
-    <row r="40" spans="1:8" s="56" customFormat="1">
-      <c r="A40" s="74"/>
-      <c r="B40" s="74"/>
-      <c r="C40" s="75"/>
-      <c r="D40" s="76"/>
-      <c r="E40" s="77"/>
-      <c r="F40" s="76"/>
-    </row>
-    <row r="41" spans="1:8" s="56" customFormat="1">
-      <c r="A41" s="74"/>
-      <c r="B41" s="74"/>
-      <c r="C41" s="75"/>
-      <c r="D41" s="76"/>
-      <c r="E41" s="77"/>
-      <c r="F41" s="76"/>
-    </row>
-    <row r="42" spans="1:8" s="56" customFormat="1">
-      <c r="A42" s="74"/>
-      <c r="B42" s="74"/>
-      <c r="C42" s="75"/>
-      <c r="D42" s="76"/>
-      <c r="E42" s="77"/>
-      <c r="F42" s="76"/>
-    </row>
-    <row r="43" spans="1:8" s="56" customFormat="1">
-      <c r="A43" s="74"/>
-      <c r="B43" s="74"/>
-      <c r="C43" s="75"/>
-      <c r="D43" s="76"/>
-      <c r="E43" s="77"/>
-      <c r="F43" s="76"/>
-    </row>
-    <row r="44" spans="1:8" s="56" customFormat="1">
-      <c r="A44" s="74"/>
-      <c r="B44" s="74"/>
-      <c r="C44" s="75"/>
-      <c r="D44" s="76"/>
-      <c r="E44" s="77"/>
-      <c r="F44" s="76"/>
-    </row>
-    <row r="45" spans="1:8" s="56" customFormat="1">
-      <c r="A45" s="74"/>
-      <c r="B45" s="74"/>
-      <c r="C45" s="75"/>
-      <c r="D45" s="76"/>
-      <c r="E45" s="77"/>
-      <c r="F45" s="76"/>
-    </row>
-    <row r="46" spans="1:8" s="56" customFormat="1">
-      <c r="A46" s="74"/>
-      <c r="B46" s="74"/>
-      <c r="C46" s="75"/>
-      <c r="D46" s="76"/>
-      <c r="E46" s="77"/>
-      <c r="F46" s="76"/>
+      <c r="B31" s="86"/>
+      <c r="C31" s="87"/>
+      <c r="D31" s="56"/>
+      <c r="E31" s="56"/>
+      <c r="F31" s="57"/>
+      <c r="G31" s="324"/>
+      <c r="H31" s="324"/>
+    </row>
+    <row r="32" spans="1:8" s="55" customFormat="1">
+      <c r="A32" s="327" t="s">
+        <v>84</v>
+      </c>
+      <c r="B32" s="328"/>
+      <c r="C32" s="59"/>
+      <c r="D32" s="56"/>
+      <c r="E32" s="56"/>
+      <c r="F32" s="57"/>
+      <c r="G32" s="324"/>
+      <c r="H32" s="324"/>
+    </row>
+    <row r="33" spans="1:8" s="55" customFormat="1" ht="17.399999999999999">
+      <c r="A33" s="60"/>
+      <c r="B33" s="61"/>
+      <c r="C33" s="62"/>
+      <c r="D33" s="63"/>
+      <c r="E33" s="62"/>
+      <c r="F33" s="64"/>
+      <c r="G33" s="65"/>
+      <c r="H33" s="39"/>
+    </row>
+    <row r="34" spans="1:8" s="55" customFormat="1">
+      <c r="A34" s="60"/>
+      <c r="B34" s="61"/>
+      <c r="C34" s="66"/>
+      <c r="D34" s="67"/>
+      <c r="E34" s="68"/>
+      <c r="F34" s="69"/>
+    </row>
+    <row r="35" spans="1:8" s="55" customFormat="1">
+      <c r="A35" s="60"/>
+      <c r="B35" s="61"/>
+      <c r="C35" s="66"/>
+      <c r="D35" s="67"/>
+      <c r="E35" s="68"/>
+      <c r="F35" s="69"/>
+    </row>
+    <row r="36" spans="1:8" s="55" customFormat="1">
+      <c r="A36" s="70"/>
+      <c r="B36" s="71"/>
+      <c r="C36" s="72"/>
+      <c r="D36" s="329"/>
+      <c r="E36" s="329"/>
+      <c r="F36" s="330"/>
+    </row>
+    <row r="37" spans="1:8" s="55" customFormat="1">
+      <c r="A37" s="73"/>
+      <c r="B37" s="73"/>
+      <c r="C37" s="74"/>
+      <c r="D37" s="75"/>
+      <c r="E37" s="76"/>
+      <c r="F37" s="75"/>
+    </row>
+    <row r="38" spans="1:8" s="55" customFormat="1">
+      <c r="A38" s="73"/>
+      <c r="B38" s="73"/>
+      <c r="C38" s="74"/>
+      <c r="D38" s="75"/>
+      <c r="E38" s="76"/>
+      <c r="F38" s="75"/>
+    </row>
+    <row r="39" spans="1:8" s="55" customFormat="1">
+      <c r="A39" s="73"/>
+      <c r="B39" s="73"/>
+      <c r="C39" s="74"/>
+      <c r="D39" s="75"/>
+      <c r="E39" s="76"/>
+      <c r="F39" s="75"/>
+    </row>
+    <row r="40" spans="1:8" s="55" customFormat="1">
+      <c r="A40" s="73"/>
+      <c r="B40" s="73"/>
+      <c r="C40" s="74"/>
+      <c r="D40" s="75"/>
+      <c r="E40" s="76"/>
+      <c r="F40" s="75"/>
+    </row>
+    <row r="41" spans="1:8" s="55" customFormat="1">
+      <c r="A41" s="73"/>
+      <c r="B41" s="73"/>
+      <c r="C41" s="74"/>
+      <c r="D41" s="75"/>
+      <c r="E41" s="76"/>
+      <c r="F41" s="75"/>
+    </row>
+    <row r="42" spans="1:8" s="55" customFormat="1">
+      <c r="A42" s="73"/>
+      <c r="B42" s="73"/>
+      <c r="C42" s="74"/>
+      <c r="D42" s="75"/>
+      <c r="E42" s="76"/>
+      <c r="F42" s="75"/>
+    </row>
+    <row r="43" spans="1:8" s="55" customFormat="1">
+      <c r="A43" s="73"/>
+      <c r="B43" s="73"/>
+      <c r="C43" s="74"/>
+      <c r="D43" s="75"/>
+      <c r="E43" s="76"/>
+      <c r="F43" s="75"/>
+    </row>
+    <row r="44" spans="1:8" s="55" customFormat="1">
+      <c r="A44" s="73"/>
+      <c r="B44" s="73"/>
+      <c r="C44" s="74"/>
+      <c r="D44" s="75"/>
+      <c r="E44" s="76"/>
+      <c r="F44" s="75"/>
+    </row>
+    <row r="45" spans="1:8" s="55" customFormat="1">
+      <c r="A45" s="73"/>
+      <c r="B45" s="73"/>
+      <c r="C45" s="74"/>
+      <c r="D45" s="75"/>
+      <c r="E45" s="76"/>
+      <c r="F45" s="75"/>
+    </row>
+    <row r="46" spans="1:8" s="55" customFormat="1">
+      <c r="A46" s="73"/>
+      <c r="B46" s="73"/>
+      <c r="C46" s="74"/>
+      <c r="D46" s="75"/>
+      <c r="E46" s="76"/>
+      <c r="F46" s="75"/>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="78"/>
-      <c r="B47" s="78"/>
-      <c r="C47" s="79"/>
-      <c r="D47" s="80"/>
-      <c r="E47" s="81"/>
-      <c r="F47" s="80"/>
+      <c r="A47" s="77"/>
+      <c r="B47" s="77"/>
+      <c r="C47" s="78"/>
+      <c r="D47" s="79"/>
+      <c r="E47" s="80"/>
+      <c r="F47" s="79"/>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="78"/>
-      <c r="B48" s="78"/>
-      <c r="C48" s="79"/>
-      <c r="D48" s="80"/>
-      <c r="E48" s="81"/>
-      <c r="F48" s="80"/>
+      <c r="A48" s="77"/>
+      <c r="B48" s="77"/>
+      <c r="C48" s="78"/>
+      <c r="D48" s="79"/>
+      <c r="E48" s="80"/>
+      <c r="F48" s="79"/>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="78"/>
-      <c r="B49" s="78"/>
-      <c r="C49" s="79"/>
-      <c r="D49" s="80"/>
-      <c r="E49" s="81"/>
-      <c r="F49" s="80"/>
+      <c r="A49" s="77"/>
+      <c r="B49" s="77"/>
+      <c r="C49" s="78"/>
+      <c r="D49" s="79"/>
+      <c r="E49" s="80"/>
+      <c r="F49" s="79"/>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="78"/>
-      <c r="B50" s="78"/>
-      <c r="C50" s="79"/>
-      <c r="D50" s="80"/>
-      <c r="E50" s="81"/>
-      <c r="F50" s="80"/>
+      <c r="A50" s="77"/>
+      <c r="B50" s="77"/>
+      <c r="C50" s="78"/>
+      <c r="D50" s="79"/>
+      <c r="E50" s="80"/>
+      <c r="F50" s="79"/>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="78"/>
-      <c r="B51" s="78"/>
-      <c r="C51" s="79"/>
-      <c r="D51" s="80"/>
-      <c r="E51" s="81"/>
-      <c r="F51" s="80"/>
+      <c r="A51" s="77"/>
+      <c r="B51" s="77"/>
+      <c r="C51" s="78"/>
+      <c r="D51" s="79"/>
+      <c r="E51" s="80"/>
+      <c r="F51" s="79"/>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="78"/>
-      <c r="B52" s="78"/>
-      <c r="C52" s="79"/>
-      <c r="D52" s="80"/>
-      <c r="E52" s="81"/>
-      <c r="F52" s="80"/>
+      <c r="A52" s="77"/>
+      <c r="B52" s="77"/>
+      <c r="C52" s="78"/>
+      <c r="D52" s="79"/>
+      <c r="E52" s="80"/>
+      <c r="F52" s="79"/>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="82"/>
-      <c r="B53" s="82"/>
-      <c r="D53" s="83"/>
-      <c r="E53" s="84"/>
-      <c r="F53" s="83"/>
+      <c r="A53" s="81"/>
+      <c r="B53" s="81"/>
+      <c r="D53" s="82"/>
+      <c r="E53" s="83"/>
+      <c r="F53" s="82"/>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="82"/>
-      <c r="B54" s="82"/>
-      <c r="D54" s="83"/>
-      <c r="E54" s="84"/>
-      <c r="F54" s="83"/>
+      <c r="A54" s="81"/>
+      <c r="B54" s="81"/>
+      <c r="D54" s="82"/>
+      <c r="E54" s="83"/>
+      <c r="F54" s="82"/>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="82"/>
-      <c r="B55" s="82"/>
-      <c r="D55" s="83"/>
-      <c r="E55" s="84"/>
-      <c r="F55" s="83"/>
+      <c r="A55" s="81"/>
+      <c r="B55" s="81"/>
+      <c r="D55" s="82"/>
+      <c r="E55" s="83"/>
+      <c r="F55" s="82"/>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="82"/>
-      <c r="B56" s="82"/>
-      <c r="D56" s="83"/>
-      <c r="E56" s="84"/>
-      <c r="F56" s="83"/>
+      <c r="A56" s="81"/>
+      <c r="B56" s="81"/>
+      <c r="D56" s="82"/>
+      <c r="E56" s="83"/>
+      <c r="F56" s="82"/>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="82"/>
-      <c r="B57" s="82"/>
-      <c r="D57" s="83"/>
-      <c r="E57" s="84"/>
-      <c r="F57" s="83"/>
+      <c r="A57" s="81"/>
+      <c r="B57" s="81"/>
+      <c r="D57" s="82"/>
+      <c r="E57" s="83"/>
+      <c r="F57" s="82"/>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="82"/>
-      <c r="B58" s="82"/>
-      <c r="D58" s="83"/>
-      <c r="E58" s="84"/>
-      <c r="F58" s="83"/>
+      <c r="A58" s="81"/>
+      <c r="B58" s="81"/>
+      <c r="D58" s="82"/>
+      <c r="E58" s="83"/>
+      <c r="F58" s="82"/>
     </row>
     <row r="59" spans="1:6">
-      <c r="A59" s="82"/>
-      <c r="B59" s="82"/>
-      <c r="D59" s="83"/>
-      <c r="E59" s="84"/>
-      <c r="F59" s="83"/>
+      <c r="A59" s="81"/>
+      <c r="B59" s="81"/>
+      <c r="D59" s="82"/>
+      <c r="E59" s="83"/>
+      <c r="F59" s="82"/>
     </row>
     <row r="60" spans="1:6">
-      <c r="A60" s="82"/>
-      <c r="B60" s="82"/>
-      <c r="D60" s="83"/>
-      <c r="E60" s="84"/>
-      <c r="F60" s="83"/>
+      <c r="A60" s="81"/>
+      <c r="B60" s="81"/>
+      <c r="D60" s="82"/>
+      <c r="E60" s="83"/>
+      <c r="F60" s="82"/>
     </row>
     <row r="61" spans="1:6">
-      <c r="A61" s="82"/>
-      <c r="B61" s="82"/>
-      <c r="D61" s="83"/>
-      <c r="E61" s="84"/>
-      <c r="F61" s="83"/>
+      <c r="A61" s="81"/>
+      <c r="B61" s="81"/>
+      <c r="D61" s="82"/>
+      <c r="E61" s="83"/>
+      <c r="F61" s="82"/>
     </row>
     <row r="62" spans="1:6">
-      <c r="A62" s="82"/>
-      <c r="B62" s="82"/>
-      <c r="D62" s="83"/>
-      <c r="E62" s="84"/>
-      <c r="F62" s="83"/>
+      <c r="A62" s="81"/>
+      <c r="B62" s="81"/>
+      <c r="D62" s="82"/>
+      <c r="E62" s="83"/>
+      <c r="F62" s="82"/>
     </row>
     <row r="63" spans="1:6">
-      <c r="A63" s="82"/>
-      <c r="B63" s="82"/>
-      <c r="D63" s="83"/>
-      <c r="E63" s="84"/>
-      <c r="F63" s="83"/>
+      <c r="A63" s="81"/>
+      <c r="B63" s="81"/>
+      <c r="D63" s="82"/>
+      <c r="E63" s="83"/>
+      <c r="F63" s="82"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="A64" s="82"/>
-      <c r="B64" s="82"/>
-      <c r="D64" s="83"/>
-      <c r="E64" s="84"/>
-      <c r="F64" s="83"/>
+      <c r="A64" s="81"/>
+      <c r="B64" s="81"/>
+      <c r="D64" s="82"/>
+      <c r="E64" s="83"/>
+      <c r="F64" s="82"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="A65" s="82"/>
-      <c r="B65" s="82"/>
-      <c r="D65" s="83"/>
-      <c r="E65" s="84"/>
-      <c r="F65" s="83"/>
+      <c r="A65" s="81"/>
+      <c r="B65" s="81"/>
+      <c r="D65" s="82"/>
+      <c r="E65" s="83"/>
+      <c r="F65" s="82"/>
     </row>
     <row r="66" spans="1:6">
-      <c r="A66" s="82"/>
-      <c r="B66" s="82"/>
-      <c r="D66" s="83"/>
-      <c r="E66" s="84"/>
-      <c r="F66" s="83"/>
+      <c r="A66" s="81"/>
+      <c r="B66" s="81"/>
+      <c r="D66" s="82"/>
+      <c r="E66" s="83"/>
+      <c r="F66" s="82"/>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="82"/>
-      <c r="B67" s="82"/>
-      <c r="D67" s="83"/>
-      <c r="E67" s="84"/>
-      <c r="F67" s="83"/>
+      <c r="A67" s="81"/>
+      <c r="B67" s="81"/>
+      <c r="D67" s="82"/>
+      <c r="E67" s="83"/>
+      <c r="F67" s="82"/>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="82"/>
-      <c r="B68" s="82"/>
-      <c r="D68" s="83"/>
-      <c r="E68" s="84"/>
-      <c r="F68" s="83"/>
+      <c r="A68" s="81"/>
+      <c r="B68" s="81"/>
+      <c r="D68" s="82"/>
+      <c r="E68" s="83"/>
+      <c r="F68" s="82"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="A69" s="82"/>
-      <c r="B69" s="82"/>
-      <c r="D69" s="83"/>
-      <c r="E69" s="84"/>
-      <c r="F69" s="83"/>
+      <c r="A69" s="81"/>
+      <c r="B69" s="81"/>
+      <c r="D69" s="82"/>
+      <c r="E69" s="83"/>
+      <c r="F69" s="82"/>
     </row>
     <row r="70" spans="1:6">
-      <c r="A70" s="82"/>
-      <c r="B70" s="82"/>
-      <c r="D70" s="83"/>
-      <c r="E70" s="84"/>
-      <c r="F70" s="83"/>
+      <c r="A70" s="81"/>
+      <c r="B70" s="81"/>
+      <c r="D70" s="82"/>
+      <c r="E70" s="83"/>
+      <c r="F70" s="82"/>
     </row>
     <row r="71" spans="1:6">
-      <c r="A71" s="82"/>
-      <c r="B71" s="82"/>
-      <c r="D71" s="83"/>
-      <c r="E71" s="84"/>
-      <c r="F71" s="83"/>
+      <c r="A71" s="81"/>
+      <c r="B71" s="81"/>
+      <c r="D71" s="82"/>
+      <c r="E71" s="83"/>
+      <c r="F71" s="82"/>
     </row>
     <row r="72" spans="1:6">
-      <c r="A72" s="82"/>
-      <c r="B72" s="82"/>
-      <c r="D72" s="83"/>
-      <c r="E72" s="84"/>
-      <c r="F72" s="83"/>
+      <c r="A72" s="81"/>
+      <c r="B72" s="81"/>
+      <c r="D72" s="82"/>
+      <c r="E72" s="83"/>
+      <c r="F72" s="82"/>
     </row>
     <row r="73" spans="1:6">
-      <c r="A73" s="82"/>
-      <c r="B73" s="82"/>
-      <c r="D73" s="83"/>
-      <c r="E73" s="84"/>
-      <c r="F73" s="83"/>
+      <c r="A73" s="81"/>
+      <c r="B73" s="81"/>
+      <c r="D73" s="82"/>
+      <c r="E73" s="83"/>
+      <c r="F73" s="82"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="A74" s="82"/>
-      <c r="B74" s="82"/>
-      <c r="D74" s="83"/>
-      <c r="E74" s="84"/>
-      <c r="F74" s="83"/>
+      <c r="A74" s="81"/>
+      <c r="B74" s="81"/>
+      <c r="D74" s="82"/>
+      <c r="E74" s="83"/>
+      <c r="F74" s="82"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="A75" s="82"/>
-      <c r="B75" s="82"/>
-      <c r="D75" s="83"/>
-      <c r="E75" s="84"/>
-      <c r="F75" s="83"/>
+      <c r="A75" s="81"/>
+      <c r="B75" s="81"/>
+      <c r="D75" s="82"/>
+      <c r="E75" s="83"/>
+      <c r="F75" s="82"/>
     </row>
     <row r="76" spans="1:6">
-      <c r="A76" s="82"/>
-      <c r="B76" s="82"/>
-      <c r="D76" s="83"/>
-      <c r="E76" s="84"/>
-      <c r="F76" s="83"/>
+      <c r="A76" s="81"/>
+      <c r="B76" s="81"/>
+      <c r="D76" s="82"/>
+      <c r="E76" s="83"/>
+      <c r="F76" s="82"/>
     </row>
     <row r="77" spans="1:6">
-      <c r="A77" s="82"/>
-      <c r="B77" s="82"/>
-      <c r="D77" s="83"/>
-      <c r="E77" s="84"/>
-      <c r="F77" s="83"/>
+      <c r="A77" s="81"/>
+      <c r="B77" s="81"/>
+      <c r="D77" s="82"/>
+      <c r="E77" s="83"/>
+      <c r="F77" s="82"/>
     </row>
     <row r="78" spans="1:6">
-      <c r="A78" s="82"/>
-      <c r="B78" s="85"/>
-      <c r="D78" s="83"/>
-      <c r="E78" s="84"/>
-      <c r="F78" s="83"/>
+      <c r="A78" s="81"/>
+      <c r="B78" s="84"/>
+      <c r="D78" s="82"/>
+      <c r="E78" s="83"/>
+      <c r="F78" s="82"/>
     </row>
     <row r="79" spans="1:6">
-      <c r="A79" s="82"/>
-      <c r="B79" s="85"/>
-      <c r="D79" s="83"/>
-      <c r="E79" s="84"/>
-      <c r="F79" s="83"/>
+      <c r="A79" s="81"/>
+      <c r="B79" s="84"/>
+      <c r="D79" s="82"/>
+      <c r="E79" s="83"/>
+      <c r="F79" s="82"/>
     </row>
     <row r="80" spans="1:6">
-      <c r="A80" s="82"/>
-      <c r="B80" s="85"/>
-      <c r="D80" s="83"/>
-      <c r="E80" s="84"/>
-      <c r="F80" s="83"/>
+      <c r="A80" s="81"/>
+      <c r="B80" s="84"/>
+      <c r="D80" s="82"/>
+      <c r="E80" s="83"/>
+      <c r="F80" s="82"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="A81" s="82"/>
-      <c r="B81" s="85"/>
-      <c r="D81" s="83"/>
-      <c r="E81" s="84"/>
-      <c r="F81" s="83"/>
+      <c r="A81" s="81"/>
+      <c r="B81" s="84"/>
+      <c r="D81" s="82"/>
+      <c r="E81" s="83"/>
+      <c r="F81" s="82"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="A82" s="82"/>
-      <c r="B82" s="85"/>
-      <c r="D82" s="83"/>
-      <c r="E82" s="84"/>
-      <c r="F82" s="83"/>
+      <c r="A82" s="81"/>
+      <c r="B82" s="84"/>
+      <c r="D82" s="82"/>
+      <c r="E82" s="83"/>
+      <c r="F82" s="82"/>
     </row>
     <row r="83" spans="1:6">
-      <c r="A83" s="82"/>
-      <c r="B83" s="85"/>
-      <c r="D83" s="83"/>
-      <c r="E83" s="84"/>
-      <c r="F83" s="83"/>
+      <c r="A83" s="81"/>
+      <c r="B83" s="84"/>
+      <c r="D83" s="82"/>
+      <c r="E83" s="83"/>
+      <c r="F83" s="82"/>
     </row>
     <row r="84" spans="1:6">
-      <c r="A84" s="82"/>
-      <c r="B84" s="85"/>
-      <c r="D84" s="83"/>
-      <c r="E84" s="84"/>
-      <c r="F84" s="83"/>
+      <c r="A84" s="81"/>
+      <c r="B84" s="84"/>
+      <c r="D84" s="82"/>
+      <c r="E84" s="83"/>
+      <c r="F84" s="82"/>
     </row>
     <row r="85" spans="1:6">
-      <c r="A85" s="82"/>
-      <c r="B85" s="85"/>
-      <c r="D85" s="83"/>
-      <c r="E85" s="84"/>
-      <c r="F85" s="83"/>
+      <c r="A85" s="81"/>
+      <c r="B85" s="84"/>
+      <c r="D85" s="82"/>
+      <c r="E85" s="83"/>
+      <c r="F85" s="82"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="A86" s="82"/>
-      <c r="B86" s="85"/>
-      <c r="D86" s="83"/>
-      <c r="E86" s="84"/>
-      <c r="F86" s="83"/>
+      <c r="A86" s="81"/>
+      <c r="B86" s="84"/>
+      <c r="D86" s="82"/>
+      <c r="E86" s="83"/>
+      <c r="F86" s="82"/>
     </row>
     <row r="87" spans="1:6">
-      <c r="A87" s="82"/>
-      <c r="B87" s="85"/>
-      <c r="D87" s="83"/>
-      <c r="E87" s="84"/>
-      <c r="F87" s="83"/>
+      <c r="A87" s="81"/>
+      <c r="B87" s="84"/>
+      <c r="D87" s="82"/>
+      <c r="E87" s="83"/>
+      <c r="F87" s="82"/>
     </row>
     <row r="88" spans="1:6">
-      <c r="A88" s="82"/>
-      <c r="B88" s="85"/>
-      <c r="D88" s="83"/>
-      <c r="E88" s="84"/>
-      <c r="F88" s="83"/>
+      <c r="A88" s="81"/>
+      <c r="B88" s="84"/>
+      <c r="D88" s="82"/>
+      <c r="E88" s="83"/>
+      <c r="F88" s="82"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="A89" s="82"/>
-      <c r="B89" s="85"/>
-      <c r="D89" s="83"/>
-      <c r="E89" s="84"/>
-      <c r="F89" s="83"/>
+      <c r="A89" s="81"/>
+      <c r="B89" s="84"/>
+      <c r="D89" s="82"/>
+      <c r="E89" s="83"/>
+      <c r="F89" s="82"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="A90" s="82"/>
-      <c r="B90" s="85"/>
-      <c r="D90" s="83"/>
-      <c r="E90" s="84"/>
-      <c r="F90" s="83"/>
+      <c r="A90" s="81"/>
+      <c r="B90" s="84"/>
+      <c r="D90" s="82"/>
+      <c r="E90" s="83"/>
+      <c r="F90" s="82"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="A91" s="82"/>
-      <c r="B91" s="85"/>
-      <c r="D91" s="83"/>
-      <c r="E91" s="84"/>
-      <c r="F91" s="83"/>
+      <c r="A91" s="81"/>
+      <c r="B91" s="84"/>
+      <c r="D91" s="82"/>
+      <c r="E91" s="83"/>
+      <c r="F91" s="82"/>
     </row>
     <row r="92" spans="1:6">
-      <c r="A92" s="82"/>
-      <c r="B92" s="85"/>
-      <c r="D92" s="83"/>
-      <c r="E92" s="84"/>
-      <c r="F92" s="83"/>
+      <c r="A92" s="81"/>
+      <c r="B92" s="84"/>
+      <c r="D92" s="82"/>
+      <c r="E92" s="83"/>
+      <c r="F92" s="82"/>
     </row>
     <row r="93" spans="1:6">
-      <c r="A93" s="82"/>
-      <c r="B93" s="85"/>
-      <c r="D93" s="83"/>
-      <c r="E93" s="84"/>
-      <c r="F93" s="83"/>
+      <c r="A93" s="81"/>
+      <c r="B93" s="84"/>
+      <c r="D93" s="82"/>
+      <c r="E93" s="83"/>
+      <c r="F93" s="82"/>
     </row>
     <row r="94" spans="1:6">
-      <c r="A94" s="82"/>
-      <c r="B94" s="85"/>
-      <c r="D94" s="83"/>
-      <c r="E94" s="84"/>
-      <c r="F94" s="83"/>
+      <c r="A94" s="81"/>
+      <c r="B94" s="84"/>
+      <c r="D94" s="82"/>
+      <c r="E94" s="83"/>
+      <c r="F94" s="82"/>
     </row>
     <row r="95" spans="1:6">
-      <c r="A95" s="82"/>
-      <c r="B95" s="85"/>
-      <c r="D95" s="83"/>
-      <c r="E95" s="84"/>
-      <c r="F95" s="83"/>
+      <c r="A95" s="81"/>
+      <c r="B95" s="84"/>
+      <c r="D95" s="82"/>
+      <c r="E95" s="83"/>
+      <c r="F95" s="82"/>
     </row>
     <row r="96" spans="1:6">
-      <c r="A96" s="82"/>
-      <c r="B96" s="85"/>
-      <c r="D96" s="83"/>
-      <c r="E96" s="84"/>
-      <c r="F96" s="83"/>
+      <c r="A96" s="81"/>
+      <c r="B96" s="84"/>
+      <c r="D96" s="82"/>
+      <c r="E96" s="83"/>
+      <c r="F96" s="82"/>
     </row>
     <row r="97" spans="1:6">
-      <c r="A97" s="82"/>
-      <c r="B97" s="85"/>
-      <c r="D97" s="83"/>
-      <c r="E97" s="84"/>
-      <c r="F97" s="83"/>
+      <c r="A97" s="81"/>
+      <c r="B97" s="84"/>
+      <c r="D97" s="82"/>
+      <c r="E97" s="83"/>
+      <c r="F97" s="82"/>
     </row>
     <row r="98" spans="1:6">
-      <c r="A98" s="82"/>
-      <c r="B98" s="85"/>
-      <c r="D98" s="83"/>
-      <c r="E98" s="84"/>
-      <c r="F98" s="83"/>
+      <c r="A98" s="81"/>
+      <c r="B98" s="84"/>
+      <c r="D98" s="82"/>
+      <c r="E98" s="83"/>
+      <c r="F98" s="82"/>
     </row>
     <row r="99" spans="1:6">
-      <c r="A99" s="82"/>
-      <c r="B99" s="85"/>
-      <c r="D99" s="83"/>
-      <c r="E99" s="84"/>
-      <c r="F99" s="83"/>
+      <c r="A99" s="81"/>
+      <c r="B99" s="84"/>
+      <c r="D99" s="82"/>
+      <c r="E99" s="83"/>
+      <c r="F99" s="82"/>
     </row>
     <row r="100" spans="1:6">
-      <c r="A100" s="82"/>
-      <c r="B100" s="85"/>
-      <c r="D100" s="83"/>
-      <c r="E100" s="84"/>
-      <c r="F100" s="83"/>
+      <c r="A100" s="81"/>
+      <c r="B100" s="84"/>
+      <c r="D100" s="82"/>
+      <c r="E100" s="83"/>
+      <c r="F100" s="82"/>
     </row>
     <row r="101" spans="1:6">
-      <c r="A101" s="82"/>
-      <c r="B101" s="85"/>
-      <c r="D101" s="83"/>
-      <c r="E101" s="84"/>
-      <c r="F101" s="83"/>
+      <c r="A101" s="81"/>
+      <c r="B101" s="84"/>
+      <c r="D101" s="82"/>
+      <c r="E101" s="83"/>
+      <c r="F101" s="82"/>
     </row>
     <row r="102" spans="1:6">
-      <c r="A102" s="82"/>
-      <c r="B102" s="85"/>
-      <c r="D102" s="83"/>
-      <c r="E102" s="84"/>
-      <c r="F102" s="83"/>
+      <c r="A102" s="81"/>
+      <c r="B102" s="84"/>
+      <c r="D102" s="82"/>
+      <c r="E102" s="83"/>
+      <c r="F102" s="82"/>
     </row>
     <row r="103" spans="1:6">
-      <c r="A103" s="82"/>
-      <c r="B103" s="85"/>
-      <c r="D103" s="83"/>
-      <c r="E103" s="84"/>
-      <c r="F103" s="83"/>
+      <c r="A103" s="81"/>
+      <c r="B103" s="84"/>
+      <c r="D103" s="82"/>
+      <c r="E103" s="83"/>
+      <c r="F103" s="82"/>
     </row>
     <row r="104" spans="1:6">
-      <c r="A104" s="82"/>
-      <c r="B104" s="85"/>
-      <c r="D104" s="83"/>
-      <c r="E104" s="84"/>
-      <c r="F104" s="83"/>
+      <c r="A104" s="81"/>
+      <c r="B104" s="84"/>
+      <c r="D104" s="82"/>
+      <c r="E104" s="83"/>
+      <c r="F104" s="82"/>
     </row>
     <row r="105" spans="1:6">
-      <c r="A105" s="82"/>
-      <c r="B105" s="85"/>
-      <c r="D105" s="83"/>
-      <c r="E105" s="84"/>
-      <c r="F105" s="83"/>
+      <c r="A105" s="81"/>
+      <c r="B105" s="84"/>
+      <c r="D105" s="82"/>
+      <c r="E105" s="83"/>
+      <c r="F105" s="82"/>
     </row>
     <row r="106" spans="1:6">
-      <c r="A106" s="82"/>
-      <c r="B106" s="85"/>
-      <c r="D106" s="83"/>
-      <c r="E106" s="84"/>
-      <c r="F106" s="83"/>
+      <c r="A106" s="81"/>
+      <c r="B106" s="84"/>
+      <c r="D106" s="82"/>
+      <c r="E106" s="83"/>
+      <c r="F106" s="82"/>
     </row>
     <row r="107" spans="1:6">
-      <c r="A107" s="82"/>
-      <c r="B107" s="85"/>
-      <c r="D107" s="83"/>
-      <c r="E107" s="84"/>
-      <c r="F107" s="83"/>
+      <c r="A107" s="81"/>
+      <c r="B107" s="84"/>
+      <c r="D107" s="82"/>
+      <c r="E107" s="83"/>
+      <c r="F107" s="82"/>
     </row>
     <row r="108" spans="1:6">
-      <c r="A108" s="82"/>
-      <c r="B108" s="85"/>
-      <c r="D108" s="83"/>
-      <c r="E108" s="84"/>
-      <c r="F108" s="83"/>
+      <c r="A108" s="81"/>
+      <c r="B108" s="84"/>
+      <c r="D108" s="82"/>
+      <c r="E108" s="83"/>
+      <c r="F108" s="82"/>
     </row>
     <row r="109" spans="1:6">
-      <c r="A109" s="82"/>
-      <c r="B109" s="85"/>
-      <c r="D109" s="83"/>
-      <c r="E109" s="84"/>
-      <c r="F109" s="83"/>
+      <c r="A109" s="81"/>
+      <c r="B109" s="84"/>
+      <c r="D109" s="82"/>
+      <c r="E109" s="83"/>
+      <c r="F109" s="82"/>
     </row>
     <row r="110" spans="1:6">
-      <c r="A110" s="82"/>
-      <c r="B110" s="85"/>
-      <c r="D110" s="83"/>
-      <c r="E110" s="84"/>
-      <c r="F110" s="83"/>
+      <c r="A110" s="81"/>
+      <c r="B110" s="84"/>
+      <c r="D110" s="82"/>
+      <c r="E110" s="83"/>
+      <c r="F110" s="82"/>
     </row>
     <row r="111" spans="1:6">
-      <c r="A111" s="82"/>
-      <c r="B111" s="85"/>
-      <c r="D111" s="83"/>
-      <c r="E111" s="84"/>
-      <c r="F111" s="83"/>
+      <c r="A111" s="81"/>
+      <c r="B111" s="84"/>
+      <c r="D111" s="82"/>
+      <c r="E111" s="83"/>
+      <c r="F111" s="82"/>
     </row>
     <row r="112" spans="1:6">
-      <c r="A112" s="82"/>
-      <c r="B112" s="85"/>
-      <c r="D112" s="83"/>
-      <c r="E112" s="84"/>
-      <c r="F112" s="83"/>
+      <c r="A112" s="81"/>
+      <c r="B112" s="84"/>
+      <c r="D112" s="82"/>
+      <c r="E112" s="83"/>
+      <c r="F112" s="82"/>
     </row>
     <row r="113" spans="1:6">
-      <c r="A113" s="82"/>
-      <c r="B113" s="85"/>
-      <c r="D113" s="83"/>
-      <c r="E113" s="84"/>
-      <c r="F113" s="83"/>
+      <c r="A113" s="81"/>
+      <c r="B113" s="84"/>
+      <c r="D113" s="82"/>
+      <c r="E113" s="83"/>
+      <c r="F113" s="82"/>
     </row>
     <row r="114" spans="1:6">
-      <c r="A114" s="82"/>
-      <c r="B114" s="85"/>
-      <c r="D114" s="83"/>
-      <c r="E114" s="84"/>
-      <c r="F114" s="83"/>
+      <c r="A114" s="81"/>
+      <c r="B114" s="84"/>
+      <c r="D114" s="82"/>
+      <c r="E114" s="83"/>
+      <c r="F114" s="82"/>
     </row>
     <row r="115" spans="1:6">
-      <c r="A115" s="82"/>
-      <c r="B115" s="85"/>
-      <c r="D115" s="83"/>
-      <c r="E115" s="84"/>
-      <c r="F115" s="83"/>
+      <c r="A115" s="81"/>
+      <c r="B115" s="84"/>
+      <c r="D115" s="82"/>
+      <c r="E115" s="83"/>
+      <c r="F115" s="82"/>
     </row>
     <row r="116" spans="1:6">
-      <c r="A116" s="82"/>
-      <c r="B116" s="85"/>
-      <c r="D116" s="83"/>
-      <c r="E116" s="84"/>
-      <c r="F116" s="83"/>
+      <c r="A116" s="81"/>
+      <c r="B116" s="84"/>
+      <c r="D116" s="82"/>
+      <c r="E116" s="83"/>
+      <c r="F116" s="82"/>
     </row>
     <row r="117" spans="1:6">
-      <c r="A117" s="82"/>
-      <c r="B117" s="85"/>
-      <c r="D117" s="83"/>
-      <c r="E117" s="84"/>
-      <c r="F117" s="83"/>
+      <c r="A117" s="81"/>
+      <c r="B117" s="84"/>
+      <c r="D117" s="82"/>
+      <c r="E117" s="83"/>
+      <c r="F117" s="82"/>
     </row>
     <row r="118" spans="1:6">
-      <c r="A118" s="82"/>
-      <c r="B118" s="85"/>
-      <c r="D118" s="83"/>
-      <c r="E118" s="84"/>
-      <c r="F118" s="83"/>
+      <c r="A118" s="81"/>
+      <c r="B118" s="84"/>
+      <c r="D118" s="82"/>
+      <c r="E118" s="83"/>
+      <c r="F118" s="82"/>
     </row>
     <row r="119" spans="1:6">
-      <c r="A119" s="82"/>
-      <c r="B119" s="85"/>
-      <c r="D119" s="83"/>
-      <c r="E119" s="84"/>
-      <c r="F119" s="83"/>
+      <c r="A119" s="81"/>
+      <c r="B119" s="84"/>
+      <c r="D119" s="82"/>
+      <c r="E119" s="83"/>
+      <c r="F119" s="82"/>
     </row>
     <row r="120" spans="1:6">
-      <c r="A120" s="82"/>
-      <c r="B120" s="85"/>
-      <c r="D120" s="83"/>
-      <c r="E120" s="84"/>
-      <c r="F120" s="83"/>
+      <c r="A120" s="81"/>
+      <c r="B120" s="84"/>
+      <c r="D120" s="82"/>
+      <c r="E120" s="83"/>
+      <c r="F120" s="82"/>
     </row>
     <row r="121" spans="1:6">
-      <c r="A121" s="82"/>
-      <c r="B121" s="85"/>
-      <c r="D121" s="83"/>
-      <c r="E121" s="84"/>
-      <c r="F121" s="83"/>
+      <c r="A121" s="81"/>
+      <c r="B121" s="84"/>
+      <c r="D121" s="82"/>
+      <c r="E121" s="83"/>
+      <c r="F121" s="82"/>
     </row>
     <row r="122" spans="1:6">
-      <c r="A122" s="82"/>
-      <c r="B122" s="85"/>
-      <c r="D122" s="83"/>
-      <c r="E122" s="84"/>
-      <c r="F122" s="83"/>
+      <c r="A122" s="81"/>
+      <c r="B122" s="84"/>
+      <c r="D122" s="82"/>
+      <c r="E122" s="83"/>
+      <c r="F122" s="82"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="A123" s="82"/>
-      <c r="B123" s="85"/>
-      <c r="D123" s="83"/>
-      <c r="E123" s="84"/>
-      <c r="F123" s="83"/>
+      <c r="A123" s="81"/>
+      <c r="B123" s="84"/>
+      <c r="D123" s="82"/>
+      <c r="E123" s="83"/>
+      <c r="F123" s="82"/>
     </row>
     <row r="124" spans="1:6">
-      <c r="A124" s="82"/>
-      <c r="B124" s="85"/>
-      <c r="D124" s="83"/>
-      <c r="E124" s="84"/>
-      <c r="F124" s="83"/>
+      <c r="A124" s="81"/>
+      <c r="B124" s="84"/>
+      <c r="D124" s="82"/>
+      <c r="E124" s="83"/>
+      <c r="F124" s="82"/>
     </row>
     <row r="125" spans="1:6">
-      <c r="A125" s="82"/>
-      <c r="B125" s="85"/>
-      <c r="D125" s="83"/>
-      <c r="E125" s="84"/>
-      <c r="F125" s="83"/>
+      <c r="A125" s="81"/>
+      <c r="B125" s="84"/>
+      <c r="D125" s="82"/>
+      <c r="E125" s="83"/>
+      <c r="F125" s="82"/>
     </row>
     <row r="126" spans="1:6">
-      <c r="A126" s="82"/>
-      <c r="B126" s="85"/>
-      <c r="D126" s="83"/>
-      <c r="E126" s="84"/>
-      <c r="F126" s="83"/>
+      <c r="A126" s="81"/>
+      <c r="B126" s="84"/>
+      <c r="D126" s="82"/>
+      <c r="E126" s="83"/>
+      <c r="F126" s="82"/>
     </row>
     <row r="127" spans="1:6">
-      <c r="A127" s="82"/>
-      <c r="B127" s="85"/>
-      <c r="D127" s="83"/>
-      <c r="E127" s="84"/>
-      <c r="F127" s="83"/>
+      <c r="A127" s="81"/>
+      <c r="B127" s="84"/>
+      <c r="D127" s="82"/>
+      <c r="E127" s="83"/>
+      <c r="F127" s="82"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="A128" s="82"/>
-      <c r="B128" s="85"/>
-      <c r="D128" s="83"/>
-      <c r="E128" s="84"/>
-      <c r="F128" s="83"/>
+      <c r="A128" s="81"/>
+      <c r="B128" s="84"/>
+      <c r="D128" s="82"/>
+      <c r="E128" s="83"/>
+      <c r="F128" s="82"/>
     </row>
     <row r="129" spans="1:6">
-      <c r="A129" s="82"/>
-      <c r="B129" s="85"/>
-      <c r="D129" s="83"/>
-      <c r="E129" s="84"/>
-      <c r="F129" s="83"/>
+      <c r="A129" s="81"/>
+      <c r="B129" s="84"/>
+      <c r="D129" s="82"/>
+      <c r="E129" s="83"/>
+      <c r="F129" s="82"/>
     </row>
     <row r="130" spans="1:6">
-      <c r="A130" s="82"/>
-      <c r="B130" s="85"/>
-      <c r="D130" s="83"/>
-      <c r="E130" s="84"/>
-      <c r="F130" s="83"/>
+      <c r="A130" s="81"/>
+      <c r="B130" s="84"/>
+      <c r="D130" s="82"/>
+      <c r="E130" s="83"/>
+      <c r="F130" s="82"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="A131" s="82"/>
-      <c r="B131" s="85"/>
-      <c r="D131" s="83"/>
-      <c r="E131" s="84"/>
-      <c r="F131" s="83"/>
+      <c r="A131" s="81"/>
+      <c r="B131" s="84"/>
+      <c r="D131" s="82"/>
+      <c r="E131" s="83"/>
+      <c r="F131" s="82"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="A132" s="82"/>
-      <c r="B132" s="85"/>
-      <c r="D132" s="83"/>
-      <c r="E132" s="84"/>
-      <c r="F132" s="83"/>
+      <c r="A132" s="81"/>
+      <c r="B132" s="84"/>
+      <c r="D132" s="82"/>
+      <c r="E132" s="83"/>
+      <c r="F132" s="82"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="A133" s="82"/>
-      <c r="B133" s="85"/>
-      <c r="D133" s="83"/>
-      <c r="E133" s="84"/>
-      <c r="F133" s="83"/>
+      <c r="A133" s="81"/>
+      <c r="B133" s="84"/>
+      <c r="D133" s="82"/>
+      <c r="E133" s="83"/>
+      <c r="F133" s="82"/>
     </row>
     <row r="134" spans="1:6">
-      <c r="A134" s="82"/>
-      <c r="B134" s="85"/>
-      <c r="D134" s="83"/>
-      <c r="E134" s="84"/>
-      <c r="F134" s="83"/>
+      <c r="A134" s="81"/>
+      <c r="B134" s="84"/>
+      <c r="D134" s="82"/>
+      <c r="E134" s="83"/>
+      <c r="F134" s="82"/>
     </row>
     <row r="135" spans="1:6">
-      <c r="A135" s="82"/>
-      <c r="B135" s="85"/>
-      <c r="D135" s="83"/>
-      <c r="E135" s="84"/>
-      <c r="F135" s="83"/>
+      <c r="A135" s="81"/>
+      <c r="B135" s="84"/>
+      <c r="D135" s="82"/>
+      <c r="E135" s="83"/>
+      <c r="F135" s="82"/>
     </row>
     <row r="136" spans="1:6">
-      <c r="A136" s="82"/>
-      <c r="B136" s="85"/>
-      <c r="D136" s="83"/>
-      <c r="E136" s="84"/>
-      <c r="F136" s="83"/>
+      <c r="A136" s="81"/>
+      <c r="B136" s="84"/>
+      <c r="D136" s="82"/>
+      <c r="E136" s="83"/>
+      <c r="F136" s="82"/>
     </row>
     <row r="137" spans="1:6">
-      <c r="A137" s="82"/>
-      <c r="B137" s="85"/>
-      <c r="D137" s="83"/>
-      <c r="E137" s="84"/>
-      <c r="F137" s="83"/>
+      <c r="A137" s="81"/>
+      <c r="B137" s="84"/>
+      <c r="D137" s="82"/>
+      <c r="E137" s="83"/>
+      <c r="F137" s="82"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="A138" s="82"/>
-      <c r="B138" s="85"/>
-      <c r="D138" s="83"/>
-      <c r="E138" s="84"/>
-      <c r="F138" s="83"/>
+      <c r="A138" s="81"/>
+      <c r="B138" s="84"/>
+      <c r="D138" s="82"/>
+      <c r="E138" s="83"/>
+      <c r="F138" s="82"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="A139" s="82"/>
-      <c r="B139" s="85"/>
-      <c r="D139" s="83"/>
-      <c r="E139" s="84"/>
-      <c r="F139" s="83"/>
+      <c r="A139" s="81"/>
+      <c r="B139" s="84"/>
+      <c r="D139" s="82"/>
+      <c r="E139" s="83"/>
+      <c r="F139" s="82"/>
     </row>
     <row r="140" spans="1:6">
-      <c r="A140" s="82"/>
-      <c r="B140" s="85"/>
-      <c r="D140" s="83"/>
-      <c r="E140" s="84"/>
-      <c r="F140" s="83"/>
+      <c r="A140" s="81"/>
+      <c r="B140" s="84"/>
+      <c r="D140" s="82"/>
+      <c r="E140" s="83"/>
+      <c r="F140" s="82"/>
     </row>
     <row r="141" spans="1:6">
-      <c r="A141" s="82"/>
-      <c r="B141" s="85"/>
-      <c r="D141" s="83"/>
-      <c r="E141" s="84"/>
-      <c r="F141" s="83"/>
+      <c r="A141" s="81"/>
+      <c r="B141" s="84"/>
+      <c r="D141" s="82"/>
+      <c r="E141" s="83"/>
+      <c r="F141" s="82"/>
     </row>
     <row r="142" spans="1:6">
-      <c r="A142" s="82"/>
-      <c r="B142" s="85"/>
-      <c r="D142" s="83"/>
-      <c r="E142" s="84"/>
-      <c r="F142" s="83"/>
+      <c r="A142" s="81"/>
+      <c r="B142" s="84"/>
+      <c r="D142" s="82"/>
+      <c r="E142" s="83"/>
+      <c r="F142" s="82"/>
     </row>
     <row r="143" spans="1:6">
-      <c r="A143" s="82"/>
-      <c r="B143" s="85"/>
-      <c r="D143" s="83"/>
-      <c r="E143" s="84"/>
-      <c r="F143" s="83"/>
+      <c r="A143" s="81"/>
+      <c r="B143" s="84"/>
+      <c r="D143" s="82"/>
+      <c r="E143" s="83"/>
+      <c r="F143" s="82"/>
     </row>
     <row r="144" spans="1:6">
-      <c r="A144" s="82"/>
-      <c r="B144" s="85"/>
-      <c r="D144" s="83"/>
-      <c r="E144" s="84"/>
-      <c r="F144" s="83"/>
+      <c r="A144" s="81"/>
+      <c r="B144" s="84"/>
+      <c r="D144" s="82"/>
+      <c r="E144" s="83"/>
+      <c r="F144" s="82"/>
     </row>
     <row r="145" spans="1:6">
-      <c r="A145" s="82"/>
-      <c r="B145" s="85"/>
-      <c r="D145" s="83"/>
-      <c r="E145" s="84"/>
-      <c r="F145" s="83"/>
+      <c r="A145" s="81"/>
+      <c r="B145" s="84"/>
+      <c r="D145" s="82"/>
+      <c r="E145" s="83"/>
+      <c r="F145" s="82"/>
     </row>
     <row r="146" spans="1:6">
-      <c r="A146" s="82"/>
-      <c r="B146" s="85"/>
-      <c r="D146" s="83"/>
-      <c r="E146" s="84"/>
-      <c r="F146" s="83"/>
+      <c r="A146" s="81"/>
+      <c r="B146" s="84"/>
+      <c r="D146" s="82"/>
+      <c r="E146" s="83"/>
+      <c r="F146" s="82"/>
     </row>
     <row r="147" spans="1:6">
-      <c r="A147" s="82"/>
-      <c r="B147" s="85"/>
-      <c r="D147" s="83"/>
-      <c r="E147" s="84"/>
-      <c r="F147" s="83"/>
+      <c r="A147" s="81"/>
+      <c r="B147" s="84"/>
+      <c r="D147" s="82"/>
+      <c r="E147" s="83"/>
+      <c r="F147" s="82"/>
     </row>
     <row r="148" spans="1:6">
-      <c r="A148" s="82"/>
-      <c r="B148" s="85"/>
-      <c r="D148" s="83"/>
-      <c r="E148" s="84"/>
-      <c r="F148" s="83"/>
+      <c r="A148" s="81"/>
+      <c r="B148" s="84"/>
+      <c r="D148" s="82"/>
+      <c r="E148" s="83"/>
+      <c r="F148" s="82"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="A149" s="82"/>
-      <c r="B149" s="85"/>
-      <c r="D149" s="83"/>
-      <c r="E149" s="84"/>
-      <c r="F149" s="83"/>
+      <c r="A149" s="81"/>
+      <c r="B149" s="84"/>
+      <c r="D149" s="82"/>
+      <c r="E149" s="83"/>
+      <c r="F149" s="82"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="A150" s="82"/>
-      <c r="B150" s="85"/>
-      <c r="D150" s="83"/>
-      <c r="E150" s="84"/>
-      <c r="F150" s="83"/>
+      <c r="A150" s="81"/>
+      <c r="B150" s="84"/>
+      <c r="D150" s="82"/>
+      <c r="E150" s="83"/>
+      <c r="F150" s="82"/>
     </row>
     <row r="151" spans="1:6">
-      <c r="A151" s="82"/>
-      <c r="B151" s="85"/>
-      <c r="D151" s="83"/>
-      <c r="E151" s="84"/>
-      <c r="F151" s="83"/>
+      <c r="A151" s="81"/>
+      <c r="B151" s="84"/>
+      <c r="D151" s="82"/>
+      <c r="E151" s="83"/>
+      <c r="F151" s="82"/>
     </row>
     <row r="152" spans="1:6">
-      <c r="A152" s="82"/>
-      <c r="B152" s="85"/>
-      <c r="D152" s="83"/>
-      <c r="E152" s="84"/>
-      <c r="F152" s="83"/>
+      <c r="A152" s="81"/>
+      <c r="B152" s="84"/>
+      <c r="D152" s="82"/>
+      <c r="E152" s="83"/>
+      <c r="F152" s="82"/>
     </row>
     <row r="153" spans="1:6">
-      <c r="A153" s="82"/>
-      <c r="B153" s="85"/>
-      <c r="D153" s="83"/>
-      <c r="E153" s="84"/>
-      <c r="F153" s="83"/>
+      <c r="A153" s="81"/>
+      <c r="B153" s="84"/>
+      <c r="D153" s="82"/>
+      <c r="E153" s="83"/>
+      <c r="F153" s="82"/>
     </row>
     <row r="154" spans="1:6">
-      <c r="A154" s="82"/>
-      <c r="B154" s="85"/>
-      <c r="D154" s="83"/>
-      <c r="E154" s="84"/>
-      <c r="F154" s="83"/>
+      <c r="A154" s="81"/>
+      <c r="B154" s="84"/>
+      <c r="D154" s="82"/>
+      <c r="E154" s="83"/>
+      <c r="F154" s="82"/>
     </row>
     <row r="155" spans="1:6">
-      <c r="A155" s="82"/>
-      <c r="B155" s="85"/>
-      <c r="D155" s="83"/>
-      <c r="E155" s="84"/>
-      <c r="F155" s="83"/>
+      <c r="A155" s="81"/>
+      <c r="B155" s="84"/>
+      <c r="D155" s="82"/>
+      <c r="E155" s="83"/>
+      <c r="F155" s="82"/>
     </row>
     <row r="156" spans="1:6">
-      <c r="A156" s="82"/>
-      <c r="B156" s="85"/>
-      <c r="D156" s="83"/>
-      <c r="E156" s="84"/>
-      <c r="F156" s="83"/>
+      <c r="A156" s="81"/>
+      <c r="B156" s="84"/>
+      <c r="D156" s="82"/>
+      <c r="E156" s="83"/>
+      <c r="F156" s="82"/>
     </row>
     <row r="157" spans="1:6">
-      <c r="A157" s="82"/>
-      <c r="B157" s="85"/>
+      <c r="A157" s="81"/>
+      <c r="B157" s="84"/>
     </row>
     <row r="158" spans="1:6">
-      <c r="A158" s="82"/>
-      <c r="B158" s="85"/>
+      <c r="A158" s="81"/>
+      <c r="B158" s="84"/>
     </row>
     <row r="159" spans="1:6">
-      <c r="A159" s="82"/>
-      <c r="B159" s="85"/>
+      <c r="A159" s="81"/>
+      <c r="B159" s="84"/>
     </row>
     <row r="160" spans="1:6">
-      <c r="A160" s="82"/>
-      <c r="B160" s="85"/>
+      <c r="A160" s="81"/>
+      <c r="B160" s="84"/>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="82"/>
-      <c r="B161" s="85"/>
+      <c r="A161" s="81"/>
+      <c r="B161" s="84"/>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="82"/>
-      <c r="B162" s="85"/>
+      <c r="A162" s="81"/>
+      <c r="B162" s="84"/>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="82"/>
-      <c r="B163" s="85"/>
+      <c r="A163" s="81"/>
+      <c r="B163" s="84"/>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="82"/>
-      <c r="B164" s="85"/>
+      <c r="A164" s="81"/>
+      <c r="B164" s="84"/>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="82"/>
-      <c r="B165" s="85"/>
+      <c r="A165" s="81"/>
+      <c r="B165" s="84"/>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="82"/>
-      <c r="B166" s="85"/>
+      <c r="A166" s="81"/>
+      <c r="B166" s="84"/>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="82"/>
-      <c r="B167" s="85"/>
+      <c r="A167" s="81"/>
+      <c r="B167" s="84"/>
     </row>
   </sheetData>
   <customSheetViews>
@@ -5546,25 +5305,17 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="48">
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B4:B5"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="E14:E15"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="B10:B11"/>
     <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B4:B5"/>
     <mergeCell ref="D36:F36"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="E6:E7"/>
@@ -5576,16 +5327,16 @@
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="B18:B19"/>
     <mergeCell ref="G32:H32"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="G31:H31"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="B18:B19"/>
     <mergeCell ref="E18:E19"/>
     <mergeCell ref="F18:F19"/>
     <mergeCell ref="A1:F1"/>
@@ -5594,6 +5345,14 @@
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="B10:B11"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -5609,91 +5368,85 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:O47"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" style="40" customWidth="1"/>
-    <col min="2" max="2" width="9.44140625" style="40" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" style="40" customWidth="1"/>
-    <col min="4" max="4" width="4.5546875" style="100" customWidth="1"/>
-    <col min="5" max="5" width="10.44140625" style="100" customWidth="1"/>
-    <col min="6" max="6" width="3.88671875" style="143" customWidth="1"/>
-    <col min="7" max="7" width="10.33203125" style="100" customWidth="1"/>
-    <col min="8" max="8" width="5.109375" style="40" customWidth="1"/>
-    <col min="9" max="9" width="9.44140625" style="40" customWidth="1"/>
-    <col min="10" max="10" width="5.33203125" style="104" customWidth="1"/>
-    <col min="11" max="11" width="10.109375" style="40" customWidth="1"/>
-    <col min="12" max="12" width="9.6640625" style="40" customWidth="1"/>
-    <col min="13" max="13" width="10.6640625" style="40" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11" style="40" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.109375" style="40"/>
+    <col min="1" max="1" width="4.6640625" style="39" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" style="39" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" style="39" customWidth="1"/>
+    <col min="4" max="4" width="4.5546875" style="99" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" style="99" customWidth="1"/>
+    <col min="6" max="6" width="3.88671875" style="142" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" style="99" customWidth="1"/>
+    <col min="8" max="8" width="5.109375" style="39" customWidth="1"/>
+    <col min="9" max="9" width="9.44140625" style="39" customWidth="1"/>
+    <col min="10" max="10" width="5.33203125" style="103" customWidth="1"/>
+    <col min="11" max="11" width="10.109375" style="39" customWidth="1"/>
+    <col min="12" max="12" width="9.6640625" style="39" customWidth="1"/>
+    <col min="13" max="13" width="10.6640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11" style="39" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.109375" style="39"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="47.25" customHeight="1" thickBot="1">
-      <c r="A1" s="354" t="str">
+    <row r="1" spans="1:14" ht="47.25" customHeight="1" thickBot="1">
+      <c r="A1" s="353" t="str">
         <f>'FACE SHEET'!A21</f>
         <v>કામ નું નામ :</v>
       </c>
-      <c r="B1" s="355"/>
-      <c r="C1" s="352" t="str">
+      <c r="B1" s="354"/>
+      <c r="C1" s="351" t="str">
         <f>Abstract!B2</f>
         <v xml:space="preserve">ગોળજ ગામે ઉનાળીયા ચેરમેનના ઘર થી ખૂટતા સી.સી. રસ્તાનું કામ . </v>
       </c>
-      <c r="D1" s="333"/>
-      <c r="E1" s="333"/>
-      <c r="F1" s="333"/>
-      <c r="G1" s="333"/>
-      <c r="H1" s="333"/>
-      <c r="I1" s="333"/>
-      <c r="J1" s="333"/>
-      <c r="K1" s="333"/>
-      <c r="L1" s="353"/>
-    </row>
-    <row r="2" spans="1:15" ht="27" customHeight="1" thickBot="1">
-      <c r="A2" s="356" t="s">
+      <c r="D1" s="332"/>
+      <c r="E1" s="332"/>
+      <c r="F1" s="332"/>
+      <c r="G1" s="332"/>
+      <c r="H1" s="332"/>
+      <c r="I1" s="332"/>
+      <c r="J1" s="332"/>
+      <c r="K1" s="332"/>
+      <c r="L1" s="352"/>
+    </row>
+    <row r="2" spans="1:14" ht="27" customHeight="1" thickBot="1">
+      <c r="A2" s="355" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="357"/>
-      <c r="C2" s="357"/>
-      <c r="D2" s="357"/>
-      <c r="E2" s="357"/>
-      <c r="F2" s="357"/>
-      <c r="G2" s="357"/>
-      <c r="H2" s="357"/>
-      <c r="I2" s="357"/>
-      <c r="J2" s="357"/>
-      <c r="K2" s="357"/>
-      <c r="L2" s="358"/>
-      <c r="M2" s="40" t="s">
-        <v>154</v>
-      </c>
-      <c r="N2" s="100">
-        <f>Abstract!F25</f>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="A3" s="350" t="s">
+      <c r="B2" s="356"/>
+      <c r="C2" s="356"/>
+      <c r="D2" s="356"/>
+      <c r="E2" s="356"/>
+      <c r="F2" s="356"/>
+      <c r="G2" s="356"/>
+      <c r="H2" s="356"/>
+      <c r="I2" s="356"/>
+      <c r="J2" s="356"/>
+      <c r="K2" s="356"/>
+      <c r="L2" s="357"/>
+      <c r="N2" s="99"/>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="349" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="351"/>
+      <c r="B3" s="350"/>
       <c r="C3" s="32">
         <v>40</v>
       </c>
-      <c r="D3" s="146" t="s">
+      <c r="D3" s="145" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="147"/>
-      <c r="F3" s="145"/>
-      <c r="G3" s="148" t="s">
-        <v>89</v>
-      </c>
-      <c r="H3" s="144"/>
-      <c r="I3" s="154">
+      <c r="E3" s="146"/>
+      <c r="F3" s="144"/>
+      <c r="G3" s="147" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" s="143"/>
+      <c r="I3" s="153">
         <f>C3</f>
         <v>40</v>
       </c>
-      <c r="J3" s="155">
+      <c r="J3" s="154">
         <f>C4</f>
         <v>3</v>
       </c>
@@ -5701,758 +5454,737 @@
         <f>I3*J3</f>
         <v>120</v>
       </c>
-      <c r="L3" s="149" t="s">
-        <v>92</v>
-      </c>
-      <c r="M3" s="100" t="s">
-        <v>153</v>
-      </c>
-      <c r="N3" s="100">
-        <f>Abstract!F24</f>
-        <v>99634.802375999992</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4" s="350" t="s">
-        <v>91</v>
-      </c>
-      <c r="B4" s="351"/>
+      <c r="L3" s="148" t="s">
+        <v>88</v>
+      </c>
+      <c r="M3" s="99"/>
+      <c r="N3" s="99"/>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="349" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" s="350"/>
       <c r="C4" s="32">
         <v>3</v>
       </c>
-      <c r="D4" s="146" t="s">
+      <c r="D4" s="145" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="147"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="102"/>
-      <c r="H4" s="351" t="s">
-        <v>89</v>
-      </c>
-      <c r="I4" s="351"/>
-      <c r="J4" s="351"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="102"/>
+      <c r="G4" s="101"/>
+      <c r="H4" s="350" t="s">
+        <v>85</v>
+      </c>
+      <c r="I4" s="350"/>
+      <c r="J4" s="350"/>
       <c r="K4" s="32">
         <f>C3*C4</f>
         <v>120</v>
       </c>
-      <c r="L4" s="149" t="s">
-        <v>92</v>
-      </c>
-      <c r="M4" s="100"/>
-    </row>
-    <row r="5" spans="1:15" ht="55.5" customHeight="1">
-      <c r="A5" s="336" t="s">
-        <v>80</v>
-      </c>
-      <c r="B5" s="337"/>
-      <c r="C5" s="337"/>
-      <c r="D5" s="337"/>
-      <c r="E5" s="337"/>
-      <c r="F5" s="337"/>
-      <c r="G5" s="337"/>
-      <c r="H5" s="337"/>
-      <c r="I5" s="337"/>
-      <c r="J5" s="337"/>
-      <c r="K5" s="337"/>
-      <c r="L5" s="338"/>
-      <c r="N5" s="100">
-        <v>1.5</v>
-      </c>
-      <c r="O5" s="40">
-        <v>90.2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="19.5" customHeight="1">
-      <c r="A6" s="105"/>
-      <c r="B6" s="106"/>
-      <c r="C6" s="156">
+      <c r="L4" s="148" t="s">
+        <v>88</v>
+      </c>
+      <c r="M4" s="99"/>
+    </row>
+    <row r="5" spans="1:14" ht="55.5" customHeight="1">
+      <c r="A5" s="335" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" s="336"/>
+      <c r="C5" s="336"/>
+      <c r="D5" s="336"/>
+      <c r="E5" s="336"/>
+      <c r="F5" s="336"/>
+      <c r="G5" s="336"/>
+      <c r="H5" s="336"/>
+      <c r="I5" s="336"/>
+      <c r="J5" s="336"/>
+      <c r="K5" s="336"/>
+      <c r="L5" s="337"/>
+      <c r="N5" s="99"/>
+    </row>
+    <row r="6" spans="1:14" ht="19.5" customHeight="1">
+      <c r="A6" s="104"/>
+      <c r="B6" s="105"/>
+      <c r="C6" s="155">
         <v>1</v>
       </c>
-      <c r="D6" s="157"/>
-      <c r="E6" s="157">
+      <c r="D6" s="156"/>
+      <c r="E6" s="156">
         <v>1</v>
       </c>
-      <c r="F6" s="168" t="s">
+      <c r="F6" s="167" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="157">
+      <c r="G6" s="156">
         <f>K3</f>
         <v>120</v>
       </c>
-      <c r="H6" s="168" t="s">
+      <c r="H6" s="167" t="s">
         <v>40</v>
       </c>
-      <c r="I6" s="157">
+      <c r="I6" s="156">
         <v>0.3</v>
       </c>
-      <c r="J6" s="169" t="s">
-        <v>72</v>
-      </c>
-      <c r="K6" s="159">
+      <c r="J6" s="168" t="s">
+        <v>69</v>
+      </c>
+      <c r="K6" s="158">
         <f>E6*G6*I6</f>
         <v>36</v>
       </c>
-      <c r="L6" s="150" t="s">
-        <v>77</v>
-      </c>
-      <c r="N6" s="40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="L6" s="149" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="13"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="112"/>
-      <c r="D7" s="113"/>
-      <c r="E7" s="114"/>
-      <c r="F7" s="103"/>
-      <c r="G7" s="101"/>
-      <c r="H7" s="109"/>
-      <c r="I7" s="360"/>
-      <c r="J7" s="360"/>
-      <c r="K7" s="113"/>
+      <c r="C7" s="111"/>
+      <c r="D7" s="112"/>
+      <c r="E7" s="113"/>
+      <c r="F7" s="102"/>
+      <c r="G7" s="100"/>
+      <c r="H7" s="108"/>
+      <c r="I7" s="359"/>
+      <c r="J7" s="359"/>
+      <c r="K7" s="112"/>
       <c r="L7" s="8"/>
     </row>
-    <row r="8" spans="1:15" s="116" customFormat="1" ht="41.25" customHeight="1">
-      <c r="A8" s="336" t="s">
-        <v>138</v>
-      </c>
-      <c r="B8" s="337"/>
-      <c r="C8" s="337"/>
-      <c r="D8" s="337"/>
-      <c r="E8" s="337"/>
-      <c r="F8" s="337"/>
-      <c r="G8" s="337"/>
-      <c r="H8" s="337"/>
-      <c r="I8" s="337"/>
-      <c r="J8" s="337"/>
-      <c r="K8" s="337"/>
-      <c r="L8" s="338"/>
-      <c r="O8" s="116">
-        <f>O5</f>
-        <v>90.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" s="339" t="s">
+    <row r="8" spans="1:14" s="115" customFormat="1" ht="41.25" customHeight="1">
+      <c r="A8" s="335" t="s">
+        <v>116</v>
+      </c>
+      <c r="B8" s="336"/>
+      <c r="C8" s="336"/>
+      <c r="D8" s="336"/>
+      <c r="E8" s="336"/>
+      <c r="F8" s="336"/>
+      <c r="G8" s="336"/>
+      <c r="H8" s="336"/>
+      <c r="I8" s="336"/>
+      <c r="J8" s="336"/>
+      <c r="K8" s="336"/>
+      <c r="L8" s="337"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="338" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="340"/>
-      <c r="C9" s="156">
+      <c r="B9" s="339"/>
+      <c r="C9" s="155">
         <v>1</v>
       </c>
-      <c r="D9" s="167" t="s">
+      <c r="D9" s="166" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="157">
+      <c r="E9" s="156">
         <f>E6</f>
         <v>1</v>
       </c>
-      <c r="F9" s="167" t="s">
+      <c r="F9" s="166" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="157">
+      <c r="G9" s="156">
         <f>G6</f>
         <v>120</v>
       </c>
-      <c r="H9" s="168" t="s">
+      <c r="H9" s="167" t="s">
         <v>40</v>
       </c>
-      <c r="I9" s="157">
+      <c r="I9" s="156">
         <v>0.12</v>
       </c>
-      <c r="J9" s="170" t="s">
-        <v>72</v>
-      </c>
-      <c r="K9" s="159">
+      <c r="J9" s="169" t="s">
+        <v>69</v>
+      </c>
+      <c r="K9" s="158">
         <f>E9*G9*I9</f>
         <v>14.399999999999999</v>
       </c>
       <c r="L9" s="8"/>
-      <c r="O9" s="40">
-        <f>O8/N5</f>
-        <v>60.133333333333333</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10" s="339" t="s">
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="338" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="340"/>
-      <c r="C10" s="340"/>
-      <c r="D10" s="340"/>
-      <c r="E10" s="157">
+      <c r="B10" s="339"/>
+      <c r="C10" s="339"/>
+      <c r="D10" s="339"/>
+      <c r="E10" s="156">
         <f>K9</f>
         <v>14.399999999999999</v>
       </c>
-      <c r="F10" s="171" t="s">
+      <c r="F10" s="170" t="s">
         <v>40</v>
       </c>
-      <c r="G10" s="160">
+      <c r="G10" s="159">
         <v>0.15</v>
       </c>
-      <c r="H10" s="158"/>
-      <c r="I10" s="161"/>
-      <c r="J10" s="162"/>
-      <c r="K10" s="163">
+      <c r="H10" s="157"/>
+      <c r="I10" s="160"/>
+      <c r="J10" s="161"/>
+      <c r="K10" s="162">
         <f>E10*G10</f>
         <v>2.1599999999999997</v>
       </c>
       <c r="L10" s="8"/>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:14">
       <c r="A11" s="13"/>
       <c r="B11" s="7"/>
-      <c r="C11" s="112"/>
-      <c r="D11" s="113"/>
-      <c r="E11" s="114"/>
-      <c r="F11" s="103"/>
-      <c r="G11" s="101"/>
-      <c r="H11" s="109"/>
-      <c r="I11" s="359" t="s">
+      <c r="C11" s="111"/>
+      <c r="D11" s="112"/>
+      <c r="E11" s="113"/>
+      <c r="F11" s="102"/>
+      <c r="G11" s="100"/>
+      <c r="H11" s="108"/>
+      <c r="I11" s="358" t="s">
         <v>43</v>
       </c>
-      <c r="J11" s="359"/>
-      <c r="K11" s="159">
+      <c r="J11" s="358"/>
+      <c r="K11" s="158">
         <f>SUM(K9:K10)</f>
         <v>16.559999999999999</v>
       </c>
-      <c r="L11" s="150" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="L11" s="149" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="13"/>
       <c r="B12" s="7"/>
-      <c r="C12" s="112"/>
-      <c r="D12" s="113"/>
-      <c r="E12" s="114"/>
-      <c r="F12" s="103"/>
-      <c r="G12" s="101"/>
-      <c r="H12" s="109"/>
-      <c r="I12" s="115"/>
-      <c r="J12" s="115"/>
-      <c r="K12" s="110"/>
-      <c r="L12" s="111"/>
-    </row>
-    <row r="13" spans="1:15" s="119" customFormat="1" ht="42.75" customHeight="1">
-      <c r="A13" s="336" t="s">
-        <v>139</v>
-      </c>
-      <c r="B13" s="337"/>
-      <c r="C13" s="337"/>
-      <c r="D13" s="337"/>
-      <c r="E13" s="337"/>
-      <c r="F13" s="337"/>
-      <c r="G13" s="337"/>
-      <c r="H13" s="337"/>
-      <c r="I13" s="337"/>
-      <c r="J13" s="337"/>
-      <c r="K13" s="337"/>
-      <c r="L13" s="338"/>
-    </row>
-    <row r="14" spans="1:15" s="119" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A14" s="346" t="s">
+      <c r="C12" s="111"/>
+      <c r="D12" s="112"/>
+      <c r="E12" s="113"/>
+      <c r="F12" s="102"/>
+      <c r="G12" s="100"/>
+      <c r="H12" s="108"/>
+      <c r="I12" s="114"/>
+      <c r="J12" s="114"/>
+      <c r="K12" s="109"/>
+      <c r="L12" s="110"/>
+    </row>
+    <row r="13" spans="1:14" s="118" customFormat="1" ht="42.75" customHeight="1">
+      <c r="A13" s="335" t="s">
+        <v>117</v>
+      </c>
+      <c r="B13" s="336"/>
+      <c r="C13" s="336"/>
+      <c r="D13" s="336"/>
+      <c r="E13" s="336"/>
+      <c r="F13" s="336"/>
+      <c r="G13" s="336"/>
+      <c r="H13" s="336"/>
+      <c r="I13" s="336"/>
+      <c r="J13" s="336"/>
+      <c r="K13" s="336"/>
+      <c r="L13" s="337"/>
+    </row>
+    <row r="14" spans="1:14" s="118" customFormat="1" ht="20.25" customHeight="1">
+      <c r="A14" s="345" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="347"/>
-      <c r="C14" s="153" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" s="106"/>
-      <c r="E14" s="120"/>
-      <c r="F14" s="118"/>
-      <c r="G14" s="160">
+      <c r="B14" s="346"/>
+      <c r="C14" s="152" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="105"/>
+      <c r="E14" s="119"/>
+      <c r="F14" s="117"/>
+      <c r="G14" s="159">
         <f>K11</f>
         <v>16.559999999999999</v>
       </c>
-      <c r="H14" s="165" t="s">
+      <c r="H14" s="164" t="s">
         <v>40</v>
       </c>
-      <c r="I14" s="160">
+      <c r="I14" s="159">
         <v>25</v>
       </c>
-      <c r="J14" s="166" t="s">
-        <v>72</v>
-      </c>
-      <c r="K14" s="164">
+      <c r="J14" s="165" t="s">
+        <v>69</v>
+      </c>
+      <c r="K14" s="163">
         <f>I14*G14%</f>
         <v>4.1399999999999997</v>
       </c>
-      <c r="L14" s="151" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" s="119" customFormat="1">
-      <c r="A15" s="125"/>
-      <c r="B15" s="126"/>
-      <c r="C15" s="106"/>
-      <c r="D15" s="106"/>
-      <c r="E15" s="120"/>
-      <c r="F15" s="118"/>
-      <c r="G15" s="118"/>
-      <c r="H15" s="121"/>
-      <c r="I15" s="118"/>
-      <c r="J15" s="122"/>
-      <c r="K15" s="123"/>
-      <c r="L15" s="124"/>
-    </row>
-    <row r="16" spans="1:15" s="119" customFormat="1" ht="54.75" customHeight="1">
-      <c r="A16" s="336" t="s">
-        <v>84</v>
-      </c>
-      <c r="B16" s="337"/>
-      <c r="C16" s="337"/>
-      <c r="D16" s="337"/>
-      <c r="E16" s="337"/>
-      <c r="F16" s="337"/>
-      <c r="G16" s="337"/>
-      <c r="H16" s="337"/>
-      <c r="I16" s="337"/>
-      <c r="J16" s="337"/>
-      <c r="K16" s="337"/>
-      <c r="L16" s="338"/>
+      <c r="L14" s="150" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" s="118" customFormat="1">
+      <c r="A15" s="124"/>
+      <c r="B15" s="125"/>
+      <c r="C15" s="105"/>
+      <c r="D15" s="105"/>
+      <c r="E15" s="119"/>
+      <c r="F15" s="117"/>
+      <c r="G15" s="117"/>
+      <c r="H15" s="120"/>
+      <c r="I15" s="117"/>
+      <c r="J15" s="121"/>
+      <c r="K15" s="122"/>
+      <c r="L15" s="123"/>
+    </row>
+    <row r="16" spans="1:14" s="118" customFormat="1" ht="54.75" customHeight="1">
+      <c r="A16" s="335" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="336"/>
+      <c r="C16" s="336"/>
+      <c r="D16" s="336"/>
+      <c r="E16" s="336"/>
+      <c r="F16" s="336"/>
+      <c r="G16" s="336"/>
+      <c r="H16" s="336"/>
+      <c r="I16" s="336"/>
+      <c r="J16" s="336"/>
+      <c r="K16" s="336"/>
+      <c r="L16" s="337"/>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="348" t="s">
-        <v>78</v>
-      </c>
-      <c r="B17" s="349"/>
-      <c r="C17" s="349"/>
-      <c r="D17" s="349"/>
-      <c r="E17" s="349"/>
-      <c r="F17" s="349"/>
-      <c r="G17" s="349"/>
-      <c r="H17" s="349"/>
-      <c r="I17" s="349"/>
-      <c r="J17" s="128" t="s">
-        <v>72</v>
-      </c>
-      <c r="K17" s="159">
+      <c r="A17" s="347" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="348"/>
+      <c r="C17" s="348"/>
+      <c r="D17" s="348"/>
+      <c r="E17" s="348"/>
+      <c r="F17" s="348"/>
+      <c r="G17" s="348"/>
+      <c r="H17" s="348"/>
+      <c r="I17" s="348"/>
+      <c r="J17" s="127" t="s">
+        <v>69</v>
+      </c>
+      <c r="K17" s="158">
         <f>K11</f>
         <v>16.559999999999999</v>
       </c>
-      <c r="L17" s="150" t="s">
-        <v>77</v>
+      <c r="L17" s="149" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="129"/>
-      <c r="B18" s="127"/>
-      <c r="C18" s="127"/>
-      <c r="D18" s="130"/>
-      <c r="E18" s="130"/>
-      <c r="F18" s="130"/>
-      <c r="G18" s="130"/>
-      <c r="H18" s="130"/>
-      <c r="I18" s="130"/>
-      <c r="J18" s="128"/>
-      <c r="K18" s="110"/>
-      <c r="L18" s="111"/>
-    </row>
-    <row r="19" spans="1:12" s="119" customFormat="1" ht="33" customHeight="1">
-      <c r="A19" s="336" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="337"/>
-      <c r="C19" s="337"/>
-      <c r="D19" s="337"/>
-      <c r="E19" s="337"/>
-      <c r="F19" s="337"/>
-      <c r="G19" s="337"/>
-      <c r="H19" s="337"/>
-      <c r="I19" s="337"/>
-      <c r="J19" s="337"/>
-      <c r="K19" s="337"/>
-      <c r="L19" s="338"/>
+      <c r="A18" s="128"/>
+      <c r="B18" s="126"/>
+      <c r="C18" s="126"/>
+      <c r="D18" s="129"/>
+      <c r="E18" s="129"/>
+      <c r="F18" s="129"/>
+      <c r="G18" s="129"/>
+      <c r="H18" s="129"/>
+      <c r="I18" s="129"/>
+      <c r="J18" s="127"/>
+      <c r="K18" s="109"/>
+      <c r="L18" s="110"/>
+    </row>
+    <row r="19" spans="1:12" s="118" customFormat="1" ht="33" customHeight="1">
+      <c r="A19" s="335" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="336"/>
+      <c r="C19" s="336"/>
+      <c r="D19" s="336"/>
+      <c r="E19" s="336"/>
+      <c r="F19" s="336"/>
+      <c r="G19" s="336"/>
+      <c r="H19" s="336"/>
+      <c r="I19" s="336"/>
+      <c r="J19" s="336"/>
+      <c r="K19" s="336"/>
+      <c r="L19" s="337"/>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="348" t="s">
-        <v>79</v>
-      </c>
-      <c r="B20" s="349"/>
-      <c r="C20" s="349"/>
-      <c r="D20" s="349"/>
-      <c r="E20" s="349"/>
-      <c r="F20" s="349"/>
-      <c r="G20" s="349"/>
-      <c r="H20" s="349"/>
-      <c r="I20" s="349"/>
-      <c r="J20" s="128" t="s">
-        <v>72</v>
-      </c>
-      <c r="K20" s="159">
+      <c r="A20" s="347" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="348"/>
+      <c r="C20" s="348"/>
+      <c r="D20" s="348"/>
+      <c r="E20" s="348"/>
+      <c r="F20" s="348"/>
+      <c r="G20" s="348"/>
+      <c r="H20" s="348"/>
+      <c r="I20" s="348"/>
+      <c r="J20" s="127" t="s">
+        <v>69</v>
+      </c>
+      <c r="K20" s="158">
         <f>K14</f>
         <v>4.1399999999999997</v>
       </c>
-      <c r="L20" s="150" t="s">
-        <v>77</v>
+      <c r="L20" s="149" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="129"/>
-      <c r="B21" s="127"/>
-      <c r="C21" s="127"/>
-      <c r="D21" s="130"/>
-      <c r="E21" s="130"/>
-      <c r="F21" s="130"/>
-      <c r="G21" s="130"/>
-      <c r="H21" s="130"/>
-      <c r="I21" s="130"/>
-      <c r="J21" s="128"/>
-      <c r="K21" s="110"/>
-      <c r="L21" s="111"/>
-    </row>
-    <row r="22" spans="1:12" s="119" customFormat="1" ht="64.2" hidden="1" customHeight="1">
-      <c r="A22" s="343" t="s">
-        <v>75</v>
-      </c>
-      <c r="B22" s="344"/>
-      <c r="C22" s="344"/>
-      <c r="D22" s="344"/>
-      <c r="E22" s="344"/>
-      <c r="F22" s="344"/>
-      <c r="G22" s="344"/>
-      <c r="H22" s="344"/>
-      <c r="I22" s="344"/>
-      <c r="J22" s="344"/>
-      <c r="K22" s="344"/>
-      <c r="L22" s="345"/>
+      <c r="A21" s="128"/>
+      <c r="B21" s="126"/>
+      <c r="C21" s="126"/>
+      <c r="D21" s="129"/>
+      <c r="E21" s="129"/>
+      <c r="F21" s="129"/>
+      <c r="G21" s="129"/>
+      <c r="H21" s="129"/>
+      <c r="I21" s="129"/>
+      <c r="J21" s="127"/>
+      <c r="K21" s="109"/>
+      <c r="L21" s="110"/>
+    </row>
+    <row r="22" spans="1:12" s="118" customFormat="1" ht="64.2" hidden="1" customHeight="1">
+      <c r="A22" s="342" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" s="343"/>
+      <c r="C22" s="343"/>
+      <c r="D22" s="343"/>
+      <c r="E22" s="343"/>
+      <c r="F22" s="343"/>
+      <c r="G22" s="343"/>
+      <c r="H22" s="343"/>
+      <c r="I22" s="343"/>
+      <c r="J22" s="343"/>
+      <c r="K22" s="343"/>
+      <c r="L22" s="344"/>
     </row>
     <row r="23" spans="1:12" hidden="1">
-      <c r="A23" s="341" t="s">
+      <c r="A23" s="340" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="342"/>
-      <c r="C23" s="342"/>
-      <c r="D23" s="113"/>
-      <c r="E23" s="113">
+      <c r="B23" s="341"/>
+      <c r="C23" s="341"/>
+      <c r="D23" s="112"/>
+      <c r="E23" s="112">
         <f>C3</f>
         <v>40</v>
       </c>
-      <c r="F23" s="131" t="s">
+      <c r="F23" s="130" t="s">
         <v>40</v>
       </c>
-      <c r="G23" s="113">
+      <c r="G23" s="112">
         <f>K3</f>
         <v>120</v>
       </c>
       <c r="H23" s="7"/>
-      <c r="I23" s="132"/>
-      <c r="J23" s="117" t="s">
-        <v>72</v>
-      </c>
-      <c r="K23" s="110">
+      <c r="I23" s="131"/>
+      <c r="J23" s="116" t="s">
+        <v>69</v>
+      </c>
+      <c r="K23" s="109">
         <f>TRUNC((G23*E23),2)</f>
         <v>4800</v>
       </c>
-      <c r="L23" s="111" t="s">
+      <c r="L23" s="110" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:12" hidden="1">
-      <c r="A24" s="129"/>
-      <c r="B24" s="127"/>
-      <c r="C24" s="127"/>
-      <c r="D24" s="113"/>
-      <c r="E24" s="113"/>
-      <c r="F24" s="131"/>
-      <c r="G24" s="113"/>
+      <c r="A24" s="128"/>
+      <c r="B24" s="126"/>
+      <c r="C24" s="126"/>
+      <c r="D24" s="112"/>
+      <c r="E24" s="112"/>
+      <c r="F24" s="130"/>
+      <c r="G24" s="112"/>
       <c r="H24" s="7"/>
-      <c r="I24" s="132"/>
-      <c r="J24" s="117"/>
-      <c r="K24" s="110"/>
-      <c r="L24" s="111"/>
-    </row>
-    <row r="25" spans="1:12" s="119" customFormat="1" ht="51.75" customHeight="1">
-      <c r="A25" s="336" t="s">
-        <v>93</v>
-      </c>
-      <c r="B25" s="337"/>
-      <c r="C25" s="337"/>
-      <c r="D25" s="337"/>
-      <c r="E25" s="337"/>
-      <c r="F25" s="337"/>
-      <c r="G25" s="337"/>
-      <c r="H25" s="337"/>
-      <c r="I25" s="337"/>
-      <c r="J25" s="337"/>
-      <c r="K25" s="337"/>
-      <c r="L25" s="338"/>
+      <c r="I24" s="131"/>
+      <c r="J24" s="116"/>
+      <c r="K24" s="109"/>
+      <c r="L24" s="110"/>
+    </row>
+    <row r="25" spans="1:12" s="118" customFormat="1" ht="51.75" customHeight="1">
+      <c r="A25" s="335" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" s="336"/>
+      <c r="C25" s="336"/>
+      <c r="D25" s="336"/>
+      <c r="E25" s="336"/>
+      <c r="F25" s="336"/>
+      <c r="G25" s="336"/>
+      <c r="H25" s="336"/>
+      <c r="I25" s="336"/>
+      <c r="J25" s="336"/>
+      <c r="K25" s="336"/>
+      <c r="L25" s="337"/>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="339" t="s">
+      <c r="A26" s="338" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="340"/>
-      <c r="C26" s="107"/>
-      <c r="D26" s="108"/>
-      <c r="E26" s="157">
+      <c r="B26" s="339"/>
+      <c r="C26" s="106"/>
+      <c r="D26" s="107"/>
+      <c r="E26" s="156">
         <f>E9</f>
         <v>1</v>
       </c>
-      <c r="F26" s="167" t="s">
+      <c r="F26" s="166" t="s">
         <v>40</v>
       </c>
-      <c r="G26" s="157">
+      <c r="G26" s="156">
         <f>K4</f>
         <v>120</v>
       </c>
-      <c r="H26" s="168" t="s">
+      <c r="H26" s="167" t="s">
         <v>40</v>
       </c>
-      <c r="I26" s="157">
+      <c r="I26" s="156">
         <v>0.1</v>
       </c>
-      <c r="J26" s="170" t="s">
-        <v>72</v>
-      </c>
-      <c r="K26" s="159">
+      <c r="J26" s="169" t="s">
+        <v>69</v>
+      </c>
+      <c r="K26" s="158">
         <f>E26*G26*I26</f>
         <v>12</v>
       </c>
-      <c r="L26" s="150" t="s">
-        <v>77</v>
+      <c r="L26" s="149" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="133"/>
-      <c r="B27" s="120"/>
-      <c r="C27" s="107"/>
-      <c r="D27" s="108"/>
-      <c r="E27" s="108"/>
-      <c r="F27" s="108"/>
-      <c r="G27" s="108"/>
-      <c r="H27" s="109"/>
-      <c r="I27" s="108"/>
-      <c r="J27" s="117"/>
-      <c r="K27" s="110"/>
-      <c r="L27" s="111"/>
-    </row>
-    <row r="28" spans="1:12" s="119" customFormat="1" ht="38.4" customHeight="1">
-      <c r="A28" s="336" t="s">
-        <v>171</v>
-      </c>
-      <c r="B28" s="337"/>
-      <c r="C28" s="337"/>
-      <c r="D28" s="337"/>
-      <c r="E28" s="337"/>
-      <c r="F28" s="337"/>
-      <c r="G28" s="337"/>
-      <c r="H28" s="337"/>
-      <c r="I28" s="337"/>
-      <c r="J28" s="337"/>
-      <c r="K28" s="337"/>
-      <c r="L28" s="338"/>
+      <c r="A27" s="132"/>
+      <c r="B27" s="119"/>
+      <c r="C27" s="106"/>
+      <c r="D27" s="107"/>
+      <c r="E27" s="107"/>
+      <c r="F27" s="107"/>
+      <c r="G27" s="107"/>
+      <c r="H27" s="108"/>
+      <c r="I27" s="107"/>
+      <c r="J27" s="116"/>
+      <c r="K27" s="109"/>
+      <c r="L27" s="110"/>
+    </row>
+    <row r="28" spans="1:12" s="118" customFormat="1" ht="38.4" customHeight="1">
+      <c r="A28" s="335" t="s">
+        <v>146</v>
+      </c>
+      <c r="B28" s="336"/>
+      <c r="C28" s="336"/>
+      <c r="D28" s="336"/>
+      <c r="E28" s="336"/>
+      <c r="F28" s="336"/>
+      <c r="G28" s="336"/>
+      <c r="H28" s="336"/>
+      <c r="I28" s="336"/>
+      <c r="J28" s="336"/>
+      <c r="K28" s="336"/>
+      <c r="L28" s="337"/>
     </row>
     <row r="29" spans="1:12" ht="16.2" thickBot="1">
-      <c r="A29" s="134"/>
-      <c r="B29" s="135"/>
-      <c r="C29" s="136"/>
-      <c r="D29" s="137"/>
-      <c r="E29" s="137"/>
-      <c r="F29" s="138"/>
-      <c r="G29" s="137"/>
-      <c r="H29" s="135"/>
-      <c r="I29" s="139"/>
-      <c r="J29" s="173" t="s">
-        <v>72</v>
-      </c>
-      <c r="K29" s="172">
+      <c r="A29" s="133"/>
+      <c r="B29" s="134"/>
+      <c r="C29" s="135"/>
+      <c r="D29" s="136"/>
+      <c r="E29" s="136"/>
+      <c r="F29" s="137"/>
+      <c r="G29" s="136"/>
+      <c r="H29" s="134"/>
+      <c r="I29" s="138"/>
+      <c r="J29" s="172" t="s">
+        <v>69</v>
+      </c>
+      <c r="K29" s="171">
         <v>1</v>
       </c>
-      <c r="L29" s="152" t="s">
+      <c r="L29" s="151" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="140"/>
-      <c r="B30" s="140"/>
-      <c r="C30" s="140"/>
-      <c r="D30" s="141"/>
-      <c r="E30" s="141"/>
-      <c r="F30" s="142"/>
-      <c r="G30" s="141"/>
-      <c r="H30" s="140"/>
+      <c r="A30" s="139"/>
+      <c r="B30" s="139"/>
+      <c r="C30" s="139"/>
+      <c r="D30" s="140"/>
+      <c r="E30" s="140"/>
+      <c r="F30" s="141"/>
+      <c r="G30" s="140"/>
+      <c r="H30" s="139"/>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="140"/>
-      <c r="B31" s="140"/>
-      <c r="C31" s="140"/>
-      <c r="D31" s="141"/>
-      <c r="E31" s="141"/>
-      <c r="F31" s="142"/>
-      <c r="G31" s="141"/>
-      <c r="H31" s="140"/>
-      <c r="I31" s="335"/>
-      <c r="J31" s="335"/>
-      <c r="K31" s="335"/>
+      <c r="A31" s="139"/>
+      <c r="B31" s="139"/>
+      <c r="C31" s="139"/>
+      <c r="D31" s="140"/>
+      <c r="E31" s="140"/>
+      <c r="F31" s="141"/>
+      <c r="G31" s="140"/>
+      <c r="H31" s="139"/>
+      <c r="I31" s="334"/>
+      <c r="J31" s="334"/>
+      <c r="K31" s="334"/>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="140"/>
-      <c r="B32" s="140"/>
-      <c r="C32" s="140"/>
-      <c r="D32" s="141"/>
-      <c r="E32" s="141"/>
-      <c r="F32" s="142"/>
-      <c r="G32" s="141"/>
-      <c r="H32" s="140"/>
-      <c r="I32" s="335"/>
-      <c r="J32" s="335"/>
-      <c r="K32" s="335"/>
+      <c r="A32" s="139"/>
+      <c r="B32" s="139"/>
+      <c r="C32" s="139"/>
+      <c r="D32" s="140"/>
+      <c r="E32" s="140"/>
+      <c r="F32" s="141"/>
+      <c r="G32" s="140"/>
+      <c r="H32" s="139"/>
+      <c r="I32" s="334"/>
+      <c r="J32" s="334"/>
+      <c r="K32" s="334"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="140"/>
-      <c r="B33" s="140"/>
-      <c r="C33" s="140"/>
-      <c r="D33" s="141"/>
-      <c r="E33" s="141"/>
-      <c r="F33" s="142"/>
-      <c r="G33" s="141"/>
-      <c r="H33" s="140"/>
-      <c r="I33" s="335"/>
-      <c r="J33" s="335"/>
-      <c r="K33" s="335"/>
+      <c r="A33" s="139"/>
+      <c r="B33" s="139"/>
+      <c r="C33" s="139"/>
+      <c r="D33" s="140"/>
+      <c r="E33" s="140"/>
+      <c r="F33" s="141"/>
+      <c r="G33" s="140"/>
+      <c r="H33" s="139"/>
+      <c r="I33" s="334"/>
+      <c r="J33" s="334"/>
+      <c r="K33" s="334"/>
     </row>
     <row r="34" spans="1:11">
-      <c r="A34" s="140"/>
-      <c r="B34" s="140"/>
-      <c r="C34" s="140"/>
-      <c r="D34" s="141"/>
-      <c r="E34" s="141"/>
-      <c r="F34" s="142"/>
-      <c r="G34" s="141"/>
-      <c r="H34" s="140"/>
+      <c r="A34" s="139"/>
+      <c r="B34" s="139"/>
+      <c r="C34" s="139"/>
+      <c r="D34" s="140"/>
+      <c r="E34" s="140"/>
+      <c r="F34" s="141"/>
+      <c r="G34" s="140"/>
+      <c r="H34" s="139"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="140"/>
-      <c r="B35" s="140"/>
-      <c r="C35" s="140"/>
-      <c r="D35" s="141"/>
-      <c r="E35" s="141"/>
-      <c r="F35" s="142"/>
-      <c r="G35" s="141"/>
-      <c r="H35" s="140"/>
+      <c r="A35" s="139"/>
+      <c r="B35" s="139"/>
+      <c r="C35" s="139"/>
+      <c r="D35" s="140"/>
+      <c r="E35" s="140"/>
+      <c r="F35" s="141"/>
+      <c r="G35" s="140"/>
+      <c r="H35" s="139"/>
     </row>
     <row r="36" spans="1:11">
-      <c r="A36" s="140"/>
-      <c r="B36" s="140"/>
-      <c r="C36" s="140"/>
-      <c r="D36" s="141"/>
-      <c r="E36" s="141"/>
-      <c r="F36" s="142"/>
-      <c r="G36" s="141"/>
-      <c r="H36" s="140"/>
+      <c r="A36" s="139"/>
+      <c r="B36" s="139"/>
+      <c r="C36" s="139"/>
+      <c r="D36" s="140"/>
+      <c r="E36" s="140"/>
+      <c r="F36" s="141"/>
+      <c r="G36" s="140"/>
+      <c r="H36" s="139"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="140"/>
-      <c r="B37" s="140"/>
-      <c r="C37" s="140"/>
-      <c r="D37" s="141"/>
-      <c r="E37" s="141"/>
-      <c r="F37" s="142"/>
-      <c r="G37" s="141"/>
-      <c r="H37" s="140"/>
+      <c r="A37" s="139"/>
+      <c r="B37" s="139"/>
+      <c r="C37" s="139"/>
+      <c r="D37" s="140"/>
+      <c r="E37" s="140"/>
+      <c r="F37" s="141"/>
+      <c r="G37" s="140"/>
+      <c r="H37" s="139"/>
     </row>
     <row r="38" spans="1:11">
-      <c r="A38" s="140"/>
-      <c r="B38" s="140"/>
-      <c r="C38" s="140"/>
-      <c r="D38" s="141"/>
-      <c r="E38" s="141"/>
-      <c r="F38" s="142"/>
-      <c r="G38" s="141"/>
-      <c r="H38" s="140"/>
+      <c r="A38" s="139"/>
+      <c r="B38" s="139"/>
+      <c r="C38" s="139"/>
+      <c r="D38" s="140"/>
+      <c r="E38" s="140"/>
+      <c r="F38" s="141"/>
+      <c r="G38" s="140"/>
+      <c r="H38" s="139"/>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="140"/>
-      <c r="B39" s="140"/>
-      <c r="C39" s="140"/>
-      <c r="D39" s="141"/>
-      <c r="E39" s="141"/>
-      <c r="F39" s="142"/>
-      <c r="G39" s="141"/>
-      <c r="H39" s="140"/>
+      <c r="A39" s="139"/>
+      <c r="B39" s="139"/>
+      <c r="C39" s="139"/>
+      <c r="D39" s="140"/>
+      <c r="E39" s="140"/>
+      <c r="F39" s="141"/>
+      <c r="G39" s="140"/>
+      <c r="H39" s="139"/>
     </row>
     <row r="40" spans="1:11">
-      <c r="A40" s="140"/>
-      <c r="B40" s="140"/>
-      <c r="C40" s="140"/>
-      <c r="D40" s="141"/>
-      <c r="E40" s="141"/>
-      <c r="F40" s="142"/>
-      <c r="G40" s="141"/>
-      <c r="H40" s="140"/>
+      <c r="A40" s="139"/>
+      <c r="B40" s="139"/>
+      <c r="C40" s="139"/>
+      <c r="D40" s="140"/>
+      <c r="E40" s="140"/>
+      <c r="F40" s="141"/>
+      <c r="G40" s="140"/>
+      <c r="H40" s="139"/>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="140"/>
-      <c r="B41" s="140"/>
-      <c r="C41" s="140"/>
-      <c r="D41" s="141"/>
-      <c r="E41" s="141"/>
-      <c r="F41" s="142"/>
-      <c r="G41" s="141"/>
-      <c r="H41" s="140"/>
+      <c r="A41" s="139"/>
+      <c r="B41" s="139"/>
+      <c r="C41" s="139"/>
+      <c r="D41" s="140"/>
+      <c r="E41" s="140"/>
+      <c r="F41" s="141"/>
+      <c r="G41" s="140"/>
+      <c r="H41" s="139"/>
     </row>
     <row r="42" spans="1:11">
-      <c r="A42" s="140"/>
-      <c r="B42" s="140"/>
-      <c r="C42" s="140"/>
-      <c r="D42" s="141"/>
-      <c r="E42" s="141"/>
-      <c r="F42" s="142"/>
-      <c r="G42" s="141"/>
-      <c r="H42" s="140"/>
+      <c r="A42" s="139"/>
+      <c r="B42" s="139"/>
+      <c r="C42" s="139"/>
+      <c r="D42" s="140"/>
+      <c r="E42" s="140"/>
+      <c r="F42" s="141"/>
+      <c r="G42" s="140"/>
+      <c r="H42" s="139"/>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="140"/>
-      <c r="B43" s="140"/>
-      <c r="C43" s="140"/>
-      <c r="D43" s="141"/>
-      <c r="E43" s="141"/>
-      <c r="F43" s="142"/>
-      <c r="G43" s="141"/>
-      <c r="H43" s="140"/>
+      <c r="A43" s="139"/>
+      <c r="B43" s="139"/>
+      <c r="C43" s="139"/>
+      <c r="D43" s="140"/>
+      <c r="E43" s="140"/>
+      <c r="F43" s="141"/>
+      <c r="G43" s="140"/>
+      <c r="H43" s="139"/>
     </row>
     <row r="44" spans="1:11">
-      <c r="A44" s="140"/>
-      <c r="B44" s="140"/>
-      <c r="C44" s="140"/>
-      <c r="D44" s="141"/>
-      <c r="E44" s="141"/>
-      <c r="F44" s="142"/>
-      <c r="G44" s="141"/>
-      <c r="H44" s="140"/>
+      <c r="A44" s="139"/>
+      <c r="B44" s="139"/>
+      <c r="C44" s="139"/>
+      <c r="D44" s="140"/>
+      <c r="E44" s="140"/>
+      <c r="F44" s="141"/>
+      <c r="G44" s="140"/>
+      <c r="H44" s="139"/>
     </row>
     <row r="45" spans="1:11">
-      <c r="A45" s="140"/>
-      <c r="B45" s="140"/>
-      <c r="C45" s="140"/>
-      <c r="D45" s="141"/>
-      <c r="E45" s="141"/>
-      <c r="F45" s="142"/>
-      <c r="G45" s="141"/>
-      <c r="H45" s="140"/>
+      <c r="A45" s="139"/>
+      <c r="B45" s="139"/>
+      <c r="C45" s="139"/>
+      <c r="D45" s="140"/>
+      <c r="E45" s="140"/>
+      <c r="F45" s="141"/>
+      <c r="G45" s="140"/>
+      <c r="H45" s="139"/>
     </row>
     <row r="46" spans="1:11">
-      <c r="A46" s="140"/>
-      <c r="B46" s="140"/>
-      <c r="C46" s="140"/>
-      <c r="D46" s="141"/>
-      <c r="E46" s="141"/>
-      <c r="F46" s="142"/>
-      <c r="G46" s="141"/>
-      <c r="H46" s="140"/>
+      <c r="A46" s="139"/>
+      <c r="B46" s="139"/>
+      <c r="C46" s="139"/>
+      <c r="D46" s="140"/>
+      <c r="E46" s="140"/>
+      <c r="F46" s="141"/>
+      <c r="G46" s="140"/>
+      <c r="H46" s="139"/>
     </row>
     <row r="47" spans="1:11">
-      <c r="A47" s="140"/>
-      <c r="B47" s="140"/>
-      <c r="C47" s="140"/>
-      <c r="D47" s="141"/>
-      <c r="E47" s="141"/>
-      <c r="F47" s="142"/>
-      <c r="G47" s="141"/>
-      <c r="H47" s="140"/>
+      <c r="A47" s="139"/>
+      <c r="B47" s="139"/>
+      <c r="C47" s="139"/>
+      <c r="D47" s="140"/>
+      <c r="E47" s="140"/>
+      <c r="F47" s="141"/>
+      <c r="G47" s="140"/>
+      <c r="H47" s="139"/>
     </row>
   </sheetData>
   <customSheetViews>
@@ -6476,13 +6208,11 @@
     <mergeCell ref="A8:L8"/>
     <mergeCell ref="H4:J4"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A22:L22"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A19:L19"/>
     <mergeCell ref="A13:L13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A17:I17"/>
-    <mergeCell ref="A20:I20"/>
     <mergeCell ref="I33:K33"/>
     <mergeCell ref="A25:L25"/>
     <mergeCell ref="A26:B26"/>
@@ -6491,6 +6221,8 @@
     <mergeCell ref="A28:L28"/>
     <mergeCell ref="I32:K32"/>
     <mergeCell ref="I31:K31"/>
+    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A20:I20"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -6506,752 +6238,721 @@
   <dimension ref="A1:N43"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="10" style="175" customWidth="1"/>
-    <col min="2" max="2" width="12.33203125" style="175" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="175"/>
-    <col min="4" max="5" width="12.88671875" style="175" customWidth="1"/>
-    <col min="6" max="6" width="14.21875" style="175" customWidth="1"/>
-    <col min="7" max="8" width="12.88671875" style="175" customWidth="1"/>
-    <col min="9" max="9" width="5.109375" style="175" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="175"/>
+    <col min="1" max="1" width="10" style="174" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" style="174" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="174"/>
+    <col min="4" max="5" width="12.88671875" style="174" customWidth="1"/>
+    <col min="6" max="6" width="14.21875" style="174" customWidth="1"/>
+    <col min="7" max="8" width="12.88671875" style="174" customWidth="1"/>
+    <col min="9" max="9" width="5.109375" style="174" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="174"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="43.95" customHeight="1" thickBot="1">
-      <c r="A1" s="365" t="str">
+      <c r="A1" s="364" t="str">
         <f>Measurement!A1</f>
         <v>કામ નું નામ :</v>
       </c>
-      <c r="B1" s="366"/>
-      <c r="C1" s="352" t="str">
+      <c r="B1" s="365"/>
+      <c r="C1" s="351" t="str">
         <f>Abstract!B2</f>
         <v xml:space="preserve">ગોળજ ગામે ઉનાળીયા ચેરમેનના ઘર થી ખૂટતા સી.સી. રસ્તાનું કામ . </v>
       </c>
-      <c r="D1" s="333"/>
-      <c r="E1" s="333"/>
-      <c r="F1" s="333"/>
-      <c r="G1" s="333"/>
-      <c r="H1" s="333"/>
-      <c r="I1" s="353"/>
-      <c r="J1" s="174"/>
+      <c r="D1" s="332"/>
+      <c r="E1" s="332"/>
+      <c r="F1" s="332"/>
+      <c r="G1" s="332"/>
+      <c r="H1" s="332"/>
+      <c r="I1" s="352"/>
+      <c r="J1" s="173"/>
     </row>
     <row r="2" spans="1:10" ht="21.6" thickBot="1">
-      <c r="A2" s="367" t="s">
+      <c r="A2" s="366" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="368"/>
-      <c r="C2" s="368"/>
-      <c r="D2" s="368"/>
-      <c r="E2" s="368"/>
-      <c r="F2" s="368"/>
-      <c r="G2" s="368"/>
-      <c r="H2" s="368"/>
-      <c r="I2" s="369"/>
+      <c r="B2" s="367"/>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367"/>
+      <c r="E2" s="367"/>
+      <c r="F2" s="367"/>
+      <c r="G2" s="367"/>
+      <c r="H2" s="367"/>
+      <c r="I2" s="368"/>
     </row>
     <row r="3" spans="1:10" ht="68.400000000000006" customHeight="1">
-      <c r="A3" s="336" t="str">
+      <c r="A3" s="335" t="str">
         <f>Measurement!A25</f>
         <v xml:space="preserve">Item No. :- 6 Providing and Laying Ordinary Ciment Concrete 1:2:4 exposed work with  Curing etc. Complete including compacting with surface mechanical vibrator,mechanical loater, channaling, from work, grooving, excluding cost of reinforcement for R.C.C work  . </v>
       </c>
-      <c r="B3" s="337"/>
-      <c r="C3" s="337"/>
-      <c r="D3" s="337"/>
-      <c r="E3" s="337"/>
-      <c r="F3" s="337"/>
-      <c r="G3" s="337"/>
-      <c r="H3" s="337"/>
-      <c r="I3" s="338"/>
+      <c r="B3" s="336"/>
+      <c r="C3" s="336"/>
+      <c r="D3" s="336"/>
+      <c r="E3" s="336"/>
+      <c r="F3" s="336"/>
+      <c r="G3" s="336"/>
+      <c r="H3" s="336"/>
+      <c r="I3" s="337"/>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1">
-      <c r="A4" s="180" t="s">
+      <c r="A4" s="179" t="s">
+        <v>91</v>
+      </c>
+      <c r="B4" s="180"/>
+      <c r="C4" s="180"/>
+      <c r="D4" s="180"/>
+      <c r="E4" s="180"/>
+      <c r="F4" s="181" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="182">
+        <v>3616.35</v>
+      </c>
+      <c r="H4" s="183" t="s">
+        <v>92</v>
+      </c>
+      <c r="I4" s="184" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15" customHeight="1">
+      <c r="A5" s="185" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="180"/>
+      <c r="C5" s="180"/>
+      <c r="D5" s="180"/>
+      <c r="E5" s="180"/>
+      <c r="F5" s="181"/>
+      <c r="G5" s="182"/>
+      <c r="H5" s="183"/>
+      <c r="I5" s="184"/>
+    </row>
+    <row r="6" spans="1:10" ht="35.25" customHeight="1">
+      <c r="A6" s="369" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="370"/>
+      <c r="C6" s="370"/>
+      <c r="D6" s="370"/>
+      <c r="E6" s="370"/>
+      <c r="F6" s="370"/>
+      <c r="G6" s="370"/>
+      <c r="H6" s="370"/>
+      <c r="I6" s="371"/>
+    </row>
+    <row r="7" spans="1:10" ht="15" customHeight="1">
+      <c r="A7" s="186"/>
+      <c r="B7" s="180"/>
+      <c r="C7" s="180"/>
+      <c r="D7" s="180"/>
+      <c r="E7" s="180"/>
+      <c r="F7" s="180"/>
+      <c r="G7" s="180"/>
+      <c r="H7" s="180"/>
+      <c r="I7" s="184"/>
+    </row>
+    <row r="8" spans="1:10" ht="33.75" customHeight="1">
+      <c r="A8" s="186" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="181"/>
-      <c r="C4" s="181"/>
-      <c r="D4" s="181"/>
-      <c r="E4" s="181"/>
-      <c r="F4" s="182" t="s">
-        <v>72</v>
-      </c>
-      <c r="G4" s="183">
-        <v>3616.35</v>
-      </c>
-      <c r="H4" s="184" t="s">
+      <c r="B8" s="180"/>
+      <c r="C8" s="180"/>
+      <c r="D8" s="180"/>
+      <c r="E8" s="180"/>
+      <c r="F8" s="180"/>
+      <c r="G8" s="180"/>
+      <c r="H8" s="180"/>
+      <c r="I8" s="184"/>
+    </row>
+    <row r="9" spans="1:10" ht="15" customHeight="1">
+      <c r="A9" s="186" t="s">
         <v>96</v>
       </c>
-      <c r="I4" s="185" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="15" customHeight="1">
-      <c r="A5" s="186" t="s">
+      <c r="B9" s="180"/>
+      <c r="C9" s="180"/>
+      <c r="D9" s="180"/>
+      <c r="E9" s="180"/>
+      <c r="F9" s="180"/>
+      <c r="G9" s="180"/>
+      <c r="H9" s="180"/>
+      <c r="I9" s="184"/>
+    </row>
+    <row r="10" spans="1:10" ht="15">
+      <c r="A10" s="186" t="s">
         <v>97</v>
       </c>
-      <c r="B5" s="181"/>
-      <c r="C5" s="181"/>
-      <c r="D5" s="181"/>
-      <c r="E5" s="181"/>
-      <c r="F5" s="182"/>
-      <c r="G5" s="183"/>
-      <c r="H5" s="184"/>
-      <c r="I5" s="185"/>
-    </row>
-    <row r="6" spans="1:10" ht="35.25" customHeight="1">
-      <c r="A6" s="370" t="s">
-        <v>98</v>
-      </c>
-      <c r="B6" s="371"/>
-      <c r="C6" s="371"/>
-      <c r="D6" s="371"/>
-      <c r="E6" s="371"/>
-      <c r="F6" s="371"/>
-      <c r="G6" s="371"/>
-      <c r="H6" s="371"/>
-      <c r="I6" s="372"/>
-    </row>
-    <row r="7" spans="1:10" ht="15" customHeight="1">
-      <c r="A7" s="187"/>
-      <c r="B7" s="181"/>
-      <c r="C7" s="181"/>
-      <c r="D7" s="181"/>
-      <c r="E7" s="181"/>
-      <c r="F7" s="181"/>
-      <c r="G7" s="181"/>
-      <c r="H7" s="181"/>
-      <c r="I7" s="185"/>
-    </row>
-    <row r="8" spans="1:10" ht="33.75" customHeight="1">
-      <c r="A8" s="187" t="s">
-        <v>99</v>
-      </c>
-      <c r="B8" s="181"/>
-      <c r="C8" s="181"/>
-      <c r="D8" s="181"/>
-      <c r="E8" s="181"/>
-      <c r="F8" s="181"/>
-      <c r="G8" s="181"/>
-      <c r="H8" s="181"/>
-      <c r="I8" s="185"/>
-    </row>
-    <row r="9" spans="1:10" ht="15" customHeight="1">
-      <c r="A9" s="187" t="s">
-        <v>100</v>
-      </c>
-      <c r="B9" s="181"/>
-      <c r="C9" s="181"/>
-      <c r="D9" s="181"/>
-      <c r="E9" s="181"/>
-      <c r="F9" s="181"/>
-      <c r="G9" s="181"/>
-      <c r="H9" s="181"/>
-      <c r="I9" s="185"/>
-    </row>
-    <row r="10" spans="1:10" ht="15">
-      <c r="A10" s="187" t="s">
-        <v>101</v>
-      </c>
-      <c r="B10" s="181"/>
-      <c r="C10" s="188">
+      <c r="B10" s="180"/>
+      <c r="C10" s="187">
         <v>10</v>
       </c>
-      <c r="D10" s="189" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" s="188">
+      <c r="D10" s="188" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" s="187">
         <v>125</v>
       </c>
-      <c r="F10" s="181" t="s">
+      <c r="F10" s="180" t="s">
         <v>39</v>
       </c>
-      <c r="G10" s="190">
+      <c r="G10" s="189">
         <f>C10*E10</f>
         <v>1250</v>
       </c>
-      <c r="H10" s="184" t="s">
-        <v>96</v>
-      </c>
-      <c r="I10" s="185" t="s">
+      <c r="H10" s="183" t="s">
+        <v>92</v>
+      </c>
+      <c r="I10" s="184" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="33.75" customHeight="1">
-      <c r="A11" s="187"/>
-      <c r="B11" s="181"/>
-      <c r="C11" s="181"/>
-      <c r="D11" s="181"/>
-      <c r="E11" s="181"/>
-      <c r="F11" s="184" t="s">
-        <v>102</v>
-      </c>
-      <c r="G11" s="191">
+      <c r="A11" s="186"/>
+      <c r="B11" s="180"/>
+      <c r="C11" s="180"/>
+      <c r="D11" s="180"/>
+      <c r="E11" s="180"/>
+      <c r="F11" s="183" t="s">
+        <v>98</v>
+      </c>
+      <c r="G11" s="190">
         <f>SUM(G4:G10)</f>
         <v>4866.3500000000004</v>
       </c>
-      <c r="H11" s="192" t="s">
-        <v>96</v>
-      </c>
-      <c r="I11" s="185"/>
+      <c r="H11" s="191" t="s">
+        <v>92</v>
+      </c>
+      <c r="I11" s="184"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1">
-      <c r="A12" s="187"/>
-      <c r="B12" s="181"/>
-      <c r="C12" s="181"/>
-      <c r="D12" s="181"/>
-      <c r="E12" s="181"/>
-      <c r="F12" s="181"/>
-      <c r="G12" s="181"/>
-      <c r="H12" s="181"/>
-      <c r="I12" s="185"/>
+      <c r="A12" s="186"/>
+      <c r="B12" s="180"/>
+      <c r="C12" s="180"/>
+      <c r="D12" s="180"/>
+      <c r="E12" s="180"/>
+      <c r="F12" s="180"/>
+      <c r="G12" s="180"/>
+      <c r="H12" s="180"/>
+      <c r="I12" s="184"/>
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1">
-      <c r="A13" s="187"/>
-      <c r="B13" s="181"/>
-      <c r="C13" s="181"/>
-      <c r="D13" s="181"/>
-      <c r="E13" s="181"/>
-      <c r="F13" s="181"/>
-      <c r="G13" s="181"/>
-      <c r="H13" s="181"/>
-      <c r="I13" s="185"/>
+      <c r="A13" s="186"/>
+      <c r="B13" s="180"/>
+      <c r="C13" s="180"/>
+      <c r="D13" s="180"/>
+      <c r="E13" s="180"/>
+      <c r="F13" s="180"/>
+      <c r="G13" s="180"/>
+      <c r="H13" s="180"/>
+      <c r="I13" s="184"/>
     </row>
     <row r="14" spans="1:10" ht="15.6">
-      <c r="A14" s="193" t="s">
-        <v>103</v>
-      </c>
-      <c r="B14" s="181"/>
-      <c r="C14" s="181"/>
-      <c r="D14" s="181"/>
-      <c r="E14" s="181"/>
-      <c r="F14" s="184"/>
-      <c r="G14" s="191">
+      <c r="A14" s="192" t="s">
+        <v>99</v>
+      </c>
+      <c r="B14" s="180"/>
+      <c r="C14" s="180"/>
+      <c r="D14" s="180"/>
+      <c r="E14" s="180"/>
+      <c r="F14" s="183"/>
+      <c r="G14" s="190">
         <f>G11</f>
         <v>4866.3500000000004</v>
       </c>
-      <c r="H14" s="192" t="s">
-        <v>96</v>
-      </c>
-      <c r="I14" s="185"/>
+      <c r="H14" s="191" t="s">
+        <v>92</v>
+      </c>
+      <c r="I14" s="184"/>
     </row>
     <row r="15" spans="1:10" ht="15">
-      <c r="A15" s="187"/>
-      <c r="B15" s="181"/>
-      <c r="C15" s="181"/>
-      <c r="D15" s="181"/>
-      <c r="E15" s="181"/>
-      <c r="F15" s="184"/>
-      <c r="G15" s="181"/>
-      <c r="H15" s="181"/>
-      <c r="I15" s="185"/>
+      <c r="A15" s="186"/>
+      <c r="B15" s="180"/>
+      <c r="C15" s="180"/>
+      <c r="D15" s="180"/>
+      <c r="E15" s="180"/>
+      <c r="F15" s="183"/>
+      <c r="G15" s="180"/>
+      <c r="H15" s="180"/>
+      <c r="I15" s="184"/>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1">
-      <c r="A16" s="363" t="s">
-        <v>172</v>
-      </c>
-      <c r="B16" s="363"/>
-      <c r="C16" s="363"/>
-      <c r="D16" s="363"/>
-      <c r="E16" s="363"/>
-      <c r="F16" s="363"/>
-      <c r="G16" s="363"/>
-      <c r="H16" s="194"/>
-      <c r="I16" s="194"/>
+      <c r="A16" s="362" t="s">
+        <v>147</v>
+      </c>
+      <c r="B16" s="362"/>
+      <c r="C16" s="362"/>
+      <c r="D16" s="362"/>
+      <c r="E16" s="362"/>
+      <c r="F16" s="362"/>
+      <c r="G16" s="362"/>
+      <c r="H16" s="193"/>
+      <c r="I16" s="193"/>
     </row>
     <row r="17" spans="1:14" ht="39.6">
-      <c r="A17" s="195" t="s">
+      <c r="A17" s="194" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" s="194" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" s="195" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="194"/>
+      <c r="E17" s="194" t="s">
+        <v>103</v>
+      </c>
+      <c r="F17" s="194"/>
+      <c r="G17" s="194" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="196"/>
+      <c r="I17" s="196"/>
+    </row>
+    <row r="18" spans="1:14" ht="15" customHeight="1">
+      <c r="A18" s="194">
+        <v>1</v>
+      </c>
+      <c r="B18" s="194" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="195" t="s">
-        <v>105</v>
-      </c>
-      <c r="C17" s="196" t="s">
-        <v>106</v>
-      </c>
-      <c r="D17" s="195"/>
-      <c r="E17" s="195" t="s">
-        <v>107</v>
-      </c>
-      <c r="F17" s="195"/>
-      <c r="G17" s="195" t="s">
-        <v>23</v>
-      </c>
-      <c r="H17" s="197"/>
-      <c r="I17" s="197"/>
-    </row>
-    <row r="18" spans="1:14" ht="15" customHeight="1">
-      <c r="A18" s="195">
-        <v>1</v>
-      </c>
-      <c r="B18" s="195" t="s">
-        <v>108</v>
-      </c>
-      <c r="C18" s="198">
+      <c r="C18" s="197">
         <v>0</v>
       </c>
-      <c r="D18" s="198" t="s">
+      <c r="D18" s="197" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="198">
+      <c r="E18" s="197">
         <v>578</v>
       </c>
-      <c r="F18" s="198" t="s">
-        <v>72</v>
-      </c>
-      <c r="G18" s="195">
+      <c r="F18" s="197" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="194">
         <f t="shared" ref="G18:G27" si="0">C18*E18</f>
         <v>0</v>
       </c>
-      <c r="H18" s="197"/>
-      <c r="I18" s="197"/>
-      <c r="M18" s="364" t="s">
-        <v>125</v>
-      </c>
-      <c r="N18" s="364"/>
+      <c r="H18" s="196"/>
+      <c r="I18" s="196"/>
+      <c r="M18" s="363"/>
+      <c r="N18" s="363"/>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="199">
+      <c r="A19" s="198">
         <v>2</v>
       </c>
-      <c r="B19" s="199" t="s">
-        <v>109</v>
-      </c>
-      <c r="C19" s="198">
+      <c r="B19" s="198" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" s="197">
         <v>1</v>
       </c>
-      <c r="D19" s="198" t="s">
+      <c r="D19" s="197" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="198">
+      <c r="E19" s="197">
         <v>388</v>
       </c>
-      <c r="F19" s="198" t="s">
-        <v>72</v>
-      </c>
-      <c r="G19" s="195">
+      <c r="F19" s="197" t="s">
+        <v>69</v>
+      </c>
+      <c r="G19" s="194">
         <f t="shared" si="0"/>
         <v>388</v>
       </c>
-      <c r="H19" s="197"/>
-      <c r="I19" s="197"/>
-      <c r="M19" s="176" t="s">
-        <v>120</v>
-      </c>
-      <c r="N19" s="175">
-        <v>238</v>
-      </c>
+      <c r="H19" s="196"/>
+      <c r="I19" s="196"/>
+      <c r="M19" s="175"/>
     </row>
     <row r="20" spans="1:14" ht="15" customHeight="1">
-      <c r="A20" s="199">
+      <c r="A20" s="198">
         <v>3</v>
       </c>
-      <c r="B20" s="199" t="s">
-        <v>110</v>
-      </c>
-      <c r="C20" s="198">
+      <c r="B20" s="198" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" s="197">
         <v>1</v>
       </c>
-      <c r="D20" s="198" t="s">
+      <c r="D20" s="197" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="198">
+      <c r="E20" s="197">
         <v>788</v>
       </c>
-      <c r="F20" s="198" t="s">
-        <v>72</v>
-      </c>
-      <c r="G20" s="195">
+      <c r="F20" s="197" t="s">
+        <v>69</v>
+      </c>
+      <c r="G20" s="194">
         <f t="shared" si="0"/>
         <v>788</v>
       </c>
-      <c r="H20" s="197"/>
-      <c r="I20" s="197"/>
-      <c r="M20" s="176" t="s">
-        <v>121</v>
-      </c>
-      <c r="N20" s="175">
-        <v>833</v>
-      </c>
+      <c r="H20" s="196"/>
+      <c r="I20" s="196"/>
+      <c r="M20" s="175"/>
     </row>
     <row r="21" spans="1:14" ht="18" customHeight="1">
-      <c r="A21" s="199">
+      <c r="A21" s="198">
         <v>4</v>
       </c>
-      <c r="B21" s="199" t="s">
-        <v>111</v>
-      </c>
-      <c r="C21" s="198">
+      <c r="B21" s="198" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" s="197">
         <v>1</v>
       </c>
-      <c r="D21" s="198" t="s">
+      <c r="D21" s="197" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="198">
+      <c r="E21" s="197">
         <v>238</v>
       </c>
-      <c r="F21" s="198" t="s">
-        <v>72</v>
-      </c>
-      <c r="G21" s="195">
+      <c r="F21" s="197" t="s">
+        <v>69</v>
+      </c>
+      <c r="G21" s="194">
         <f t="shared" si="0"/>
         <v>238</v>
       </c>
-      <c r="H21" s="197"/>
-      <c r="I21" s="197"/>
-      <c r="M21" s="176" t="s">
-        <v>122</v>
-      </c>
-      <c r="N21" s="175">
-        <v>388</v>
-      </c>
+      <c r="H21" s="196"/>
+      <c r="I21" s="196"/>
+      <c r="M21" s="175"/>
     </row>
     <row r="22" spans="1:14" ht="18" customHeight="1">
-      <c r="A22" s="199">
+      <c r="A22" s="198">
         <v>5</v>
       </c>
-      <c r="B22" s="199" t="s">
-        <v>112</v>
-      </c>
-      <c r="C22" s="198">
+      <c r="B22" s="198" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" s="197">
         <v>1</v>
       </c>
-      <c r="D22" s="198" t="s">
+      <c r="D22" s="197" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="198">
+      <c r="E22" s="197">
         <v>546</v>
       </c>
-      <c r="F22" s="198" t="s">
-        <v>72</v>
-      </c>
-      <c r="G22" s="195">
+      <c r="F22" s="197" t="s">
+        <v>69</v>
+      </c>
+      <c r="G22" s="194">
         <f t="shared" si="0"/>
         <v>546</v>
       </c>
-      <c r="H22" s="197"/>
-      <c r="I22" s="197"/>
-      <c r="M22" s="176" t="s">
-        <v>123</v>
-      </c>
-      <c r="N22" s="175">
-        <v>1096</v>
-      </c>
+      <c r="H22" s="196"/>
+      <c r="I22" s="196"/>
+      <c r="M22" s="175"/>
     </row>
     <row r="23" spans="1:14" ht="15">
-      <c r="A23" s="199">
+      <c r="A23" s="198">
         <v>6</v>
       </c>
-      <c r="B23" s="199" t="s">
-        <v>113</v>
-      </c>
-      <c r="C23" s="198">
+      <c r="B23" s="198" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="197">
         <v>1</v>
       </c>
-      <c r="D23" s="198" t="s">
+      <c r="D23" s="197" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="198">
+      <c r="E23" s="197">
         <v>696</v>
       </c>
-      <c r="F23" s="198" t="s">
-        <v>72</v>
-      </c>
-      <c r="G23" s="195">
+      <c r="F23" s="197" t="s">
+        <v>69</v>
+      </c>
+      <c r="G23" s="194">
         <f t="shared" si="0"/>
         <v>696</v>
       </c>
-      <c r="H23" s="200"/>
-      <c r="I23" s="200"/>
-      <c r="M23" s="176" t="s">
-        <v>124</v>
-      </c>
-      <c r="N23" s="175">
-        <v>1096</v>
-      </c>
+      <c r="H23" s="199"/>
+      <c r="I23" s="199"/>
+      <c r="M23" s="175"/>
     </row>
     <row r="24" spans="1:14" ht="15" customHeight="1">
-      <c r="A24" s="199">
+      <c r="A24" s="198">
         <v>7</v>
       </c>
-      <c r="B24" s="201" t="s">
-        <v>114</v>
-      </c>
-      <c r="C24" s="202">
+      <c r="B24" s="200" t="s">
+        <v>110</v>
+      </c>
+      <c r="C24" s="201">
         <v>0</v>
       </c>
-      <c r="D24" s="202" t="s">
+      <c r="D24" s="201" t="s">
         <v>40</v>
       </c>
-      <c r="E24" s="198">
+      <c r="E24" s="197">
         <v>220</v>
       </c>
-      <c r="F24" s="198" t="s">
-        <v>72</v>
-      </c>
-      <c r="G24" s="195">
+      <c r="F24" s="197" t="s">
+        <v>69</v>
+      </c>
+      <c r="G24" s="194">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H24" s="203"/>
-      <c r="I24" s="203"/>
-      <c r="N24" s="175">
-        <f>SUM(N19:N23)</f>
-        <v>3651</v>
-      </c>
+      <c r="H24" s="202"/>
+      <c r="I24" s="202"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="199">
+      <c r="A25" s="198">
         <v>8</v>
       </c>
-      <c r="B25" s="201" t="s">
-        <v>115</v>
-      </c>
-      <c r="C25" s="202">
+      <c r="B25" s="200" t="s">
+        <v>111</v>
+      </c>
+      <c r="C25" s="201">
         <v>0</v>
       </c>
-      <c r="D25" s="202" t="s">
+      <c r="D25" s="201" t="s">
         <v>40</v>
       </c>
-      <c r="E25" s="198">
+      <c r="E25" s="197">
         <v>294</v>
       </c>
-      <c r="F25" s="198" t="s">
-        <v>72</v>
-      </c>
-      <c r="G25" s="195">
+      <c r="F25" s="197" t="s">
+        <v>69</v>
+      </c>
+      <c r="G25" s="194">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H25" s="203"/>
-      <c r="I25" s="203"/>
+      <c r="H25" s="202"/>
+      <c r="I25" s="202"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="199">
+      <c r="A26" s="198">
         <v>9</v>
       </c>
-      <c r="B26" s="201" t="s">
-        <v>117</v>
-      </c>
-      <c r="C26" s="202">
+      <c r="B26" s="200" t="s">
+        <v>113</v>
+      </c>
+      <c r="C26" s="201">
         <v>0</v>
       </c>
-      <c r="D26" s="202" t="s">
+      <c r="D26" s="201" t="s">
         <v>40</v>
       </c>
-      <c r="E26" s="198">
+      <c r="E26" s="197">
         <v>300</v>
       </c>
-      <c r="F26" s="198" t="s">
-        <v>72</v>
-      </c>
-      <c r="G26" s="195">
+      <c r="F26" s="197" t="s">
+        <v>69</v>
+      </c>
+      <c r="G26" s="194">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H26" s="203"/>
-      <c r="I26" s="203"/>
+      <c r="H26" s="202"/>
+      <c r="I26" s="202"/>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="199">
+      <c r="A27" s="198">
         <v>10</v>
       </c>
-      <c r="B27" s="201" t="s">
-        <v>116</v>
-      </c>
-      <c r="C27" s="202">
+      <c r="B27" s="200" t="s">
+        <v>112</v>
+      </c>
+      <c r="C27" s="201">
         <v>0</v>
       </c>
-      <c r="D27" s="202" t="s">
+      <c r="D27" s="201" t="s">
         <v>40</v>
       </c>
-      <c r="E27" s="198">
+      <c r="E27" s="197">
         <v>300</v>
       </c>
-      <c r="F27" s="198" t="s">
-        <v>72</v>
-      </c>
-      <c r="G27" s="195">
+      <c r="F27" s="197" t="s">
+        <v>69</v>
+      </c>
+      <c r="G27" s="194">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H27" s="204"/>
-      <c r="I27" s="204"/>
+      <c r="H27" s="203"/>
+      <c r="I27" s="203"/>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="199"/>
-      <c r="B28" s="205"/>
-      <c r="C28" s="205"/>
-      <c r="D28" s="205"/>
-      <c r="E28" s="205"/>
-      <c r="F28" s="205"/>
-      <c r="G28" s="206">
+      <c r="A28" s="198"/>
+      <c r="B28" s="204"/>
+      <c r="C28" s="204"/>
+      <c r="D28" s="204"/>
+      <c r="E28" s="204"/>
+      <c r="F28" s="204"/>
+      <c r="G28" s="205">
         <f>SUM(G18:G27)</f>
         <v>2656</v>
       </c>
-      <c r="H28" s="204"/>
-      <c r="I28" s="204"/>
+      <c r="H28" s="203"/>
+      <c r="I28" s="203"/>
     </row>
     <row r="29" spans="1:14">
-      <c r="A29" s="207"/>
-      <c r="B29" s="204"/>
-      <c r="C29" s="204"/>
-      <c r="D29" s="204"/>
-      <c r="E29" s="204"/>
-      <c r="F29" s="204"/>
-      <c r="G29" s="204"/>
-      <c r="H29" s="204"/>
-      <c r="I29" s="208"/>
+      <c r="A29" s="206"/>
+      <c r="B29" s="203"/>
+      <c r="C29" s="203"/>
+      <c r="D29" s="203"/>
+      <c r="E29" s="203"/>
+      <c r="F29" s="203"/>
+      <c r="G29" s="203"/>
+      <c r="H29" s="203"/>
+      <c r="I29" s="207"/>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="209"/>
-      <c r="B30" s="204"/>
-      <c r="C30" s="204"/>
-      <c r="D30" s="204"/>
-      <c r="E30" s="204"/>
-      <c r="F30" s="204"/>
-      <c r="G30" s="204"/>
-      <c r="H30" s="204"/>
-      <c r="I30" s="208"/>
+      <c r="A30" s="208"/>
+      <c r="B30" s="203"/>
+      <c r="C30" s="203"/>
+      <c r="D30" s="203"/>
+      <c r="E30" s="203"/>
+      <c r="F30" s="203"/>
+      <c r="G30" s="203"/>
+      <c r="H30" s="203"/>
+      <c r="I30" s="207"/>
     </row>
     <row r="31" spans="1:14">
-      <c r="A31" s="209"/>
-      <c r="B31" s="210"/>
-      <c r="C31" s="210"/>
-      <c r="D31" s="210"/>
-      <c r="E31" s="204"/>
-      <c r="F31" s="204"/>
-      <c r="G31" s="204"/>
-      <c r="H31" s="204"/>
-      <c r="I31" s="208"/>
+      <c r="A31" s="208"/>
+      <c r="B31" s="209"/>
+      <c r="C31" s="209"/>
+      <c r="D31" s="209"/>
+      <c r="E31" s="203"/>
+      <c r="F31" s="203"/>
+      <c r="G31" s="203"/>
+      <c r="H31" s="203"/>
+      <c r="I31" s="207"/>
     </row>
     <row r="32" spans="1:14">
-      <c r="A32" s="209"/>
-      <c r="B32" s="210"/>
-      <c r="C32" s="210"/>
-      <c r="D32" s="210"/>
-      <c r="E32" s="204"/>
-      <c r="F32" s="204"/>
-      <c r="G32" s="204"/>
-      <c r="H32" s="204"/>
-      <c r="I32" s="208"/>
+      <c r="A32" s="208"/>
+      <c r="B32" s="209"/>
+      <c r="C32" s="209"/>
+      <c r="D32" s="209"/>
+      <c r="E32" s="203"/>
+      <c r="F32" s="203"/>
+      <c r="G32" s="203"/>
+      <c r="H32" s="203"/>
+      <c r="I32" s="207"/>
     </row>
     <row r="33" spans="1:9" ht="15">
-      <c r="A33" s="209"/>
-      <c r="B33" s="361"/>
-      <c r="C33" s="361"/>
-      <c r="D33" s="361"/>
-      <c r="E33" s="204"/>
-      <c r="F33" s="204"/>
-      <c r="G33" s="204"/>
-      <c r="H33" s="204"/>
-      <c r="I33" s="208"/>
+      <c r="A33" s="208"/>
+      <c r="B33" s="360"/>
+      <c r="C33" s="360"/>
+      <c r="D33" s="360"/>
+      <c r="E33" s="203"/>
+      <c r="F33" s="203"/>
+      <c r="G33" s="203"/>
+      <c r="H33" s="203"/>
+      <c r="I33" s="207"/>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="204"/>
-      <c r="B34" s="204"/>
-      <c r="C34" s="204"/>
-      <c r="D34" s="204"/>
-      <c r="E34" s="204"/>
-      <c r="F34" s="204"/>
-      <c r="G34" s="204"/>
-      <c r="H34" s="204"/>
-      <c r="I34" s="204"/>
+      <c r="A34" s="203"/>
+      <c r="B34" s="203"/>
+      <c r="C34" s="203"/>
+      <c r="D34" s="203"/>
+      <c r="E34" s="203"/>
+      <c r="F34" s="203"/>
+      <c r="G34" s="203"/>
+      <c r="H34" s="203"/>
+      <c r="I34" s="203"/>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="204"/>
-      <c r="B35" s="204"/>
-      <c r="C35" s="204"/>
-      <c r="D35" s="204"/>
-      <c r="E35" s="204"/>
-      <c r="F35" s="204"/>
-      <c r="G35" s="204"/>
-      <c r="H35" s="204"/>
-      <c r="I35" s="204"/>
+      <c r="A35" s="203"/>
+      <c r="B35" s="203"/>
+      <c r="C35" s="203"/>
+      <c r="D35" s="203"/>
+      <c r="E35" s="203"/>
+      <c r="F35" s="203"/>
+      <c r="G35" s="203"/>
+      <c r="H35" s="203"/>
+      <c r="I35" s="203"/>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="210"/>
-      <c r="B36" s="210"/>
-      <c r="C36" s="210"/>
-      <c r="D36" s="210"/>
-      <c r="E36" s="210"/>
-      <c r="F36" s="210"/>
-      <c r="G36" s="210"/>
-      <c r="H36" s="210"/>
-      <c r="I36" s="210"/>
+      <c r="A36" s="209"/>
+      <c r="B36" s="209"/>
+      <c r="C36" s="209"/>
+      <c r="D36" s="209"/>
+      <c r="E36" s="209"/>
+      <c r="F36" s="209"/>
+      <c r="G36" s="209"/>
+      <c r="H36" s="209"/>
+      <c r="I36" s="209"/>
     </row>
     <row r="37" spans="1:9" ht="15.6">
-      <c r="A37" s="210"/>
-      <c r="B37" s="362" t="s">
-        <v>76</v>
-      </c>
-      <c r="C37" s="362"/>
-      <c r="D37" s="362"/>
-      <c r="E37" s="210"/>
-      <c r="F37" s="210"/>
-      <c r="G37" s="210"/>
-      <c r="H37" s="210"/>
-      <c r="I37" s="210"/>
+      <c r="A37" s="209"/>
+      <c r="B37" s="361" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="209"/>
+      <c r="F37" s="209"/>
+      <c r="G37" s="209"/>
+      <c r="H37" s="209"/>
+      <c r="I37" s="209"/>
     </row>
     <row r="38" spans="1:9" ht="15.6">
-      <c r="A38" s="210"/>
-      <c r="B38" s="211" t="s">
-        <v>167</v>
-      </c>
-      <c r="C38" s="212"/>
-      <c r="D38" s="179" t="s">
-        <v>168</v>
-      </c>
-      <c r="E38" s="210"/>
-      <c r="F38" s="210"/>
-      <c r="G38" s="210"/>
-      <c r="H38" s="210"/>
-      <c r="I38" s="210"/>
+      <c r="A38" s="209"/>
+      <c r="B38" s="210" t="s">
+        <v>142</v>
+      </c>
+      <c r="C38" s="211"/>
+      <c r="D38" s="178" t="s">
+        <v>143</v>
+      </c>
+      <c r="E38" s="209"/>
+      <c r="F38" s="209"/>
+      <c r="G38" s="209"/>
+      <c r="H38" s="209"/>
+      <c r="I38" s="209"/>
     </row>
     <row r="39" spans="1:9">
-      <c r="A39" s="177"/>
-      <c r="E39" s="177"/>
-      <c r="F39" s="177"/>
-      <c r="G39" s="177"/>
-      <c r="H39" s="177"/>
-      <c r="I39" s="177"/>
+      <c r="A39" s="176"/>
+      <c r="E39" s="176"/>
+      <c r="F39" s="176"/>
+      <c r="G39" s="176"/>
+      <c r="H39" s="176"/>
+      <c r="I39" s="176"/>
     </row>
     <row r="40" spans="1:9">
-      <c r="A40" s="177"/>
-      <c r="E40" s="177"/>
-      <c r="F40" s="177"/>
-      <c r="G40" s="177"/>
-      <c r="H40" s="177"/>
-      <c r="I40" s="177"/>
+      <c r="A40" s="176"/>
+      <c r="E40" s="176"/>
+      <c r="F40" s="176"/>
+      <c r="G40" s="176"/>
+      <c r="H40" s="176"/>
+      <c r="I40" s="176"/>
     </row>
     <row r="41" spans="1:9" ht="13.8" thickBot="1">
-      <c r="A41" s="178"/>
-      <c r="B41" s="178"/>
-      <c r="C41" s="178"/>
-      <c r="D41" s="178"/>
-      <c r="E41" s="178"/>
-      <c r="F41" s="178"/>
-      <c r="G41" s="178"/>
-      <c r="H41" s="178"/>
-      <c r="I41" s="178"/>
+      <c r="A41" s="177"/>
+      <c r="B41" s="177"/>
+      <c r="C41" s="177"/>
+      <c r="D41" s="177"/>
+      <c r="E41" s="177"/>
+      <c r="F41" s="177"/>
+      <c r="G41" s="177"/>
+      <c r="H41" s="177"/>
+      <c r="I41" s="177"/>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="177"/>
-      <c r="B42" s="177"/>
-      <c r="C42" s="177"/>
-      <c r="D42" s="177"/>
-      <c r="E42" s="177"/>
-      <c r="F42" s="177"/>
-      <c r="G42" s="177"/>
-      <c r="H42" s="177"/>
-      <c r="I42" s="177"/>
+      <c r="A42" s="176"/>
+      <c r="B42" s="176"/>
+      <c r="C42" s="176"/>
+      <c r="D42" s="176"/>
+      <c r="E42" s="176"/>
+      <c r="F42" s="176"/>
+      <c r="G42" s="176"/>
+      <c r="H42" s="176"/>
+      <c r="I42" s="176"/>
     </row>
     <row r="43" spans="1:9">
-      <c r="A43" s="177"/>
-      <c r="B43" s="177"/>
-      <c r="C43" s="177"/>
-      <c r="D43" s="177"/>
-      <c r="E43" s="177"/>
-      <c r="F43" s="177"/>
-      <c r="G43" s="177"/>
-      <c r="H43" s="177"/>
-      <c r="I43" s="177"/>
+      <c r="A43" s="176"/>
+      <c r="B43" s="176"/>
+      <c r="C43" s="176"/>
+      <c r="D43" s="176"/>
+      <c r="E43" s="176"/>
+      <c r="F43" s="176"/>
+      <c r="G43" s="176"/>
+      <c r="H43" s="176"/>
+      <c r="I43" s="176"/>
     </row>
   </sheetData>
   <customSheetViews>
@@ -7298,496 +6999,496 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="53.25" customHeight="1" thickBot="1">
-      <c r="A1" s="226" t="str">
+      <c r="A1" s="225" t="str">
         <f>Abstract!A2</f>
         <v>કામ નું નામ :</v>
       </c>
-      <c r="B1" s="373" t="str">
+      <c r="B1" s="372" t="str">
         <f>Abstract!B2</f>
         <v xml:space="preserve">ગોળજ ગામે ઉનાળીયા ચેરમેનના ઘર થી ખૂટતા સી.સી. રસ્તાનું કામ . </v>
       </c>
-      <c r="C1" s="374"/>
-      <c r="D1" s="374"/>
-      <c r="E1" s="374"/>
-      <c r="F1" s="374"/>
-      <c r="G1" s="374"/>
-      <c r="H1" s="375"/>
+      <c r="C1" s="373"/>
+      <c r="D1" s="373"/>
+      <c r="E1" s="373"/>
+      <c r="F1" s="373"/>
+      <c r="G1" s="373"/>
+      <c r="H1" s="374"/>
     </row>
     <row r="2" spans="1:8" ht="33" customHeight="1" thickBot="1">
-      <c r="A2" s="385" t="s">
+      <c r="A2" s="384" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="386"/>
-      <c r="C2" s="386"/>
-      <c r="D2" s="386"/>
-      <c r="E2" s="386"/>
-      <c r="F2" s="386"/>
-      <c r="G2" s="386"/>
-      <c r="H2" s="387"/>
+      <c r="B2" s="385"/>
+      <c r="C2" s="385"/>
+      <c r="D2" s="385"/>
+      <c r="E2" s="385"/>
+      <c r="F2" s="385"/>
+      <c r="G2" s="385"/>
+      <c r="H2" s="386"/>
     </row>
     <row r="3" spans="1:8" ht="15">
-      <c r="A3" s="393"/>
-      <c r="B3" s="394"/>
-      <c r="C3" s="394"/>
-      <c r="D3" s="394"/>
-      <c r="E3" s="394"/>
-      <c r="F3" s="394"/>
-      <c r="G3" s="394"/>
-      <c r="H3" s="395"/>
-    </row>
-    <row r="4" spans="1:8" s="213" customFormat="1" ht="15" customHeight="1">
-      <c r="A4" s="382" t="s">
+      <c r="A3" s="387"/>
+      <c r="B3" s="388"/>
+      <c r="C3" s="388"/>
+      <c r="D3" s="388"/>
+      <c r="E3" s="388"/>
+      <c r="F3" s="388"/>
+      <c r="G3" s="388"/>
+      <c r="H3" s="389"/>
+    </row>
+    <row r="4" spans="1:8" s="212" customFormat="1" ht="15" customHeight="1">
+      <c r="A4" s="381" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="383"/>
-      <c r="C4" s="383"/>
-      <c r="D4" s="383"/>
-      <c r="E4" s="383"/>
-      <c r="F4" s="383"/>
-      <c r="G4" s="383"/>
-      <c r="H4" s="384"/>
-    </row>
-    <row r="5" spans="1:8" s="213" customFormat="1" ht="22.2" customHeight="1">
-      <c r="A5" s="227" t="s">
-        <v>175</v>
-      </c>
-      <c r="B5" s="228" t="s">
-        <v>173</v>
-      </c>
-      <c r="C5" s="222" t="str">
+      <c r="B4" s="382"/>
+      <c r="C4" s="382"/>
+      <c r="D4" s="382"/>
+      <c r="E4" s="382"/>
+      <c r="F4" s="382"/>
+      <c r="G4" s="382"/>
+      <c r="H4" s="383"/>
+    </row>
+    <row r="5" spans="1:8" s="212" customFormat="1" ht="22.2" customHeight="1">
+      <c r="A5" s="226" t="s">
+        <v>150</v>
+      </c>
+      <c r="B5" s="227" t="s">
+        <v>148</v>
+      </c>
+      <c r="C5" s="221" t="str">
         <f>'FACE SHEET'!H39</f>
         <v>Thasra</v>
       </c>
-      <c r="D5" s="224">
+      <c r="D5" s="223">
         <v>15</v>
       </c>
-      <c r="E5" s="380" t="s">
+      <c r="E5" s="379" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="380"/>
-      <c r="G5" s="380"/>
-      <c r="H5" s="381"/>
-    </row>
-    <row r="6" spans="1:8" s="213" customFormat="1" ht="22.2" customHeight="1">
-      <c r="A6" s="223" t="str">
+      <c r="F5" s="379"/>
+      <c r="G5" s="379"/>
+      <c r="H5" s="380"/>
+    </row>
+    <row r="6" spans="1:8" s="212" customFormat="1" ht="22.2" customHeight="1">
+      <c r="A6" s="222" t="str">
         <f xml:space="preserve"> C5</f>
         <v>Thasra</v>
       </c>
-      <c r="B6" s="228" t="s">
-        <v>173</v>
-      </c>
-      <c r="C6" s="228" t="s">
-        <v>174</v>
-      </c>
-      <c r="D6" s="224">
+      <c r="B6" s="227" t="s">
+        <v>148</v>
+      </c>
+      <c r="C6" s="227" t="s">
+        <v>149</v>
+      </c>
+      <c r="D6" s="223">
         <v>15</v>
       </c>
-      <c r="E6" s="380" t="s">
+      <c r="E6" s="379" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="380"/>
-      <c r="G6" s="380"/>
-      <c r="H6" s="381"/>
-    </row>
-    <row r="7" spans="1:8" s="213" customFormat="1" ht="22.2" customHeight="1">
-      <c r="A7" s="389" t="s">
+      <c r="F6" s="379"/>
+      <c r="G6" s="379"/>
+      <c r="H6" s="380"/>
+    </row>
+    <row r="7" spans="1:8" s="212" customFormat="1" ht="22.2" customHeight="1">
+      <c r="A7" s="390" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="390"/>
-      <c r="C7" s="390"/>
-      <c r="D7" s="224">
+      <c r="B7" s="391"/>
+      <c r="C7" s="391"/>
+      <c r="D7" s="223">
         <f>D5+D6</f>
         <v>30</v>
       </c>
-      <c r="E7" s="380" t="s">
+      <c r="E7" s="379" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="380"/>
-      <c r="G7" s="380"/>
-      <c r="H7" s="381"/>
-    </row>
-    <row r="8" spans="1:8" s="213" customFormat="1" ht="22.2" customHeight="1">
-      <c r="A8" s="389" t="s">
+      <c r="F7" s="379"/>
+      <c r="G7" s="379"/>
+      <c r="H7" s="380"/>
+    </row>
+    <row r="8" spans="1:8" s="212" customFormat="1" ht="22.2" customHeight="1">
+      <c r="A8" s="390" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="390"/>
-      <c r="C8" s="390"/>
-      <c r="D8" s="224">
+      <c r="B8" s="391"/>
+      <c r="C8" s="391"/>
+      <c r="D8" s="223">
         <f>TRUNC(D7,0)</f>
         <v>30</v>
       </c>
-      <c r="E8" s="380" t="s">
+      <c r="E8" s="379" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="380"/>
-      <c r="G8" s="380"/>
-      <c r="H8" s="381"/>
+      <c r="F8" s="379"/>
+      <c r="G8" s="379"/>
+      <c r="H8" s="380"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="376"/>
-      <c r="B9" s="377"/>
-      <c r="C9" s="377"/>
-      <c r="D9" s="377"/>
-      <c r="E9" s="377"/>
-      <c r="F9" s="377"/>
-      <c r="G9" s="377"/>
-      <c r="H9" s="378"/>
-    </row>
-    <row r="10" spans="1:8" s="213" customFormat="1" ht="15" customHeight="1">
-      <c r="A10" s="382" t="s">
+      <c r="A9" s="375"/>
+      <c r="B9" s="376"/>
+      <c r="C9" s="376"/>
+      <c r="D9" s="376"/>
+      <c r="E9" s="376"/>
+      <c r="F9" s="376"/>
+      <c r="G9" s="376"/>
+      <c r="H9" s="377"/>
+    </row>
+    <row r="10" spans="1:8" s="212" customFormat="1" ht="15" customHeight="1">
+      <c r="A10" s="381" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="383"/>
-      <c r="C10" s="383"/>
-      <c r="D10" s="383"/>
-      <c r="E10" s="383"/>
-      <c r="F10" s="383"/>
-      <c r="G10" s="383"/>
-      <c r="H10" s="384"/>
-    </row>
-    <row r="11" spans="1:8" s="213" customFormat="1" ht="25.2" customHeight="1">
-      <c r="A11" s="379" t="s">
+      <c r="B10" s="382"/>
+      <c r="C10" s="382"/>
+      <c r="D10" s="382"/>
+      <c r="E10" s="382"/>
+      <c r="F10" s="382"/>
+      <c r="G10" s="382"/>
+      <c r="H10" s="383"/>
+    </row>
+    <row r="11" spans="1:8" s="212" customFormat="1" ht="25.2" customHeight="1">
+      <c r="A11" s="378" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="380"/>
-      <c r="C11" s="380"/>
-      <c r="D11" s="224">
+      <c r="B11" s="379"/>
+      <c r="C11" s="379"/>
+      <c r="D11" s="223">
         <v>5</v>
       </c>
-      <c r="E11" s="380" t="s">
+      <c r="E11" s="379" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="380"/>
-      <c r="G11" s="380"/>
-      <c r="H11" s="381"/>
+      <c r="F11" s="379"/>
+      <c r="G11" s="379"/>
+      <c r="H11" s="380"/>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
-      <c r="A12" s="376"/>
-      <c r="B12" s="377"/>
-      <c r="C12" s="377"/>
-      <c r="D12" s="377"/>
-      <c r="E12" s="377"/>
-      <c r="F12" s="377"/>
-      <c r="G12" s="377"/>
-      <c r="H12" s="378"/>
+      <c r="A12" s="375"/>
+      <c r="B12" s="376"/>
+      <c r="C12" s="376"/>
+      <c r="D12" s="376"/>
+      <c r="E12" s="376"/>
+      <c r="F12" s="376"/>
+      <c r="G12" s="376"/>
+      <c r="H12" s="377"/>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1">
-      <c r="A13" s="396" t="s">
+      <c r="A13" s="392" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="397"/>
-      <c r="C13" s="397"/>
-      <c r="D13" s="397"/>
-      <c r="E13" s="397"/>
-      <c r="F13" s="397"/>
-      <c r="G13" s="397"/>
-      <c r="H13" s="398"/>
+      <c r="B13" s="393"/>
+      <c r="C13" s="393"/>
+      <c r="D13" s="393"/>
+      <c r="E13" s="393"/>
+      <c r="F13" s="393"/>
+      <c r="G13" s="393"/>
+      <c r="H13" s="394"/>
     </row>
     <row r="14" spans="1:8" ht="15">
-      <c r="A14" s="209"/>
-      <c r="B14" s="204"/>
-      <c r="C14" s="204"/>
-      <c r="D14" s="204"/>
-      <c r="E14" s="204"/>
-      <c r="F14" s="204"/>
-      <c r="G14" s="229"/>
-      <c r="H14" s="208"/>
+      <c r="A14" s="208"/>
+      <c r="B14" s="203"/>
+      <c r="C14" s="203"/>
+      <c r="D14" s="203"/>
+      <c r="E14" s="203"/>
+      <c r="F14" s="203"/>
+      <c r="G14" s="228"/>
+      <c r="H14" s="207"/>
     </row>
     <row r="15" spans="1:8" ht="15">
-      <c r="A15" s="230"/>
-      <c r="B15" s="231"/>
-      <c r="C15" s="231"/>
-      <c r="D15" s="231"/>
-      <c r="E15" s="231"/>
-      <c r="F15" s="231"/>
-      <c r="G15" s="229"/>
-      <c r="H15" s="208"/>
+      <c r="A15" s="229"/>
+      <c r="B15" s="230"/>
+      <c r="C15" s="230"/>
+      <c r="D15" s="230"/>
+      <c r="E15" s="230"/>
+      <c r="F15" s="230"/>
+      <c r="G15" s="228"/>
+      <c r="H15" s="207"/>
     </row>
     <row r="16" spans="1:8" ht="15">
-      <c r="A16" s="230"/>
-      <c r="B16" s="231"/>
-      <c r="C16" s="388" t="s">
+      <c r="A16" s="229"/>
+      <c r="B16" s="230"/>
+      <c r="C16" s="399" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="399"/>
+      <c r="E16" s="230"/>
+      <c r="F16" s="230"/>
+      <c r="G16" s="228"/>
+      <c r="H16" s="207"/>
+    </row>
+    <row r="17" spans="1:8" ht="15">
+      <c r="A17" s="229"/>
+      <c r="B17" s="230"/>
+      <c r="C17" s="230"/>
+      <c r="D17" s="230"/>
+      <c r="E17" s="230"/>
+      <c r="F17" s="230"/>
+      <c r="G17" s="228"/>
+      <c r="H17" s="207"/>
+    </row>
+    <row r="18" spans="1:8" s="214" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A18" s="231"/>
+      <c r="B18" s="232"/>
+      <c r="C18" s="232"/>
+      <c r="D18" s="232"/>
+      <c r="E18" s="232"/>
+      <c r="F18" s="401" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="388"/>
-      <c r="E16" s="231"/>
-      <c r="F16" s="231"/>
-      <c r="G16" s="229"/>
-      <c r="H16" s="208"/>
-    </row>
-    <row r="17" spans="1:8" ht="15">
-      <c r="A17" s="230"/>
-      <c r="B17" s="231"/>
-      <c r="C17" s="231"/>
-      <c r="D17" s="231"/>
-      <c r="E17" s="231"/>
-      <c r="F17" s="231"/>
-      <c r="G17" s="229"/>
-      <c r="H17" s="208"/>
-    </row>
-    <row r="18" spans="1:8" s="215" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A18" s="232"/>
-      <c r="B18" s="233"/>
-      <c r="C18" s="233"/>
-      <c r="D18" s="233"/>
-      <c r="E18" s="233"/>
-      <c r="F18" s="392" t="s">
+      <c r="G18" s="401"/>
+      <c r="H18" s="233"/>
+    </row>
+    <row r="19" spans="1:8" s="214" customFormat="1" ht="15.6">
+      <c r="A19" s="231"/>
+      <c r="B19" s="232"/>
+      <c r="C19" s="232"/>
+      <c r="D19" s="232"/>
+      <c r="E19" s="232"/>
+      <c r="F19" s="232"/>
+      <c r="G19" s="145"/>
+      <c r="H19" s="233"/>
+    </row>
+    <row r="20" spans="1:8" s="214" customFormat="1" ht="15.6">
+      <c r="A20" s="231"/>
+      <c r="B20" s="232"/>
+      <c r="C20" s="232"/>
+      <c r="D20" s="398" t="s">
         <v>59</v>
       </c>
-      <c r="G18" s="392"/>
-      <c r="H18" s="234"/>
-    </row>
-    <row r="19" spans="1:8" s="215" customFormat="1" ht="15.6">
-      <c r="A19" s="232"/>
-      <c r="B19" s="233"/>
-      <c r="C19" s="233"/>
-      <c r="D19" s="233"/>
-      <c r="E19" s="233"/>
-      <c r="F19" s="233"/>
-      <c r="G19" s="146"/>
-      <c r="H19" s="234"/>
-    </row>
-    <row r="20" spans="1:8" s="215" customFormat="1" ht="15.6">
-      <c r="A20" s="232"/>
-      <c r="B20" s="233"/>
-      <c r="C20" s="233"/>
-      <c r="D20" s="402" t="s">
+      <c r="E20" s="398"/>
+      <c r="F20" s="232"/>
+      <c r="G20" s="145"/>
+      <c r="H20" s="233"/>
+    </row>
+    <row r="21" spans="1:8" ht="22.5" customHeight="1">
+      <c r="A21" s="234"/>
+      <c r="B21" s="235"/>
+      <c r="C21" s="235"/>
+      <c r="D21" s="395" t="s">
         <v>60</v>
       </c>
-      <c r="E20" s="402"/>
-      <c r="F20" s="233"/>
-      <c r="G20" s="146"/>
-      <c r="H20" s="234"/>
-    </row>
-    <row r="21" spans="1:8" ht="22.5" customHeight="1">
-      <c r="A21" s="235"/>
-      <c r="B21" s="236"/>
-      <c r="C21" s="236"/>
-      <c r="D21" s="399" t="s">
+      <c r="E21" s="395"/>
+      <c r="F21" s="235"/>
+      <c r="G21" s="228"/>
+      <c r="H21" s="207"/>
+    </row>
+    <row r="22" spans="1:8" ht="15">
+      <c r="A22" s="234"/>
+      <c r="B22" s="235"/>
+      <c r="C22" s="235"/>
+      <c r="D22" s="235"/>
+      <c r="E22" s="235"/>
+      <c r="F22" s="235"/>
+      <c r="G22" s="228"/>
+      <c r="H22" s="207"/>
+    </row>
+    <row r="23" spans="1:8" ht="15">
+      <c r="A23" s="234"/>
+      <c r="B23" s="235"/>
+      <c r="C23" s="235"/>
+      <c r="D23" s="235"/>
+      <c r="E23" s="235"/>
+      <c r="F23" s="400" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="399"/>
-      <c r="F21" s="236"/>
-      <c r="G21" s="229"/>
-      <c r="H21" s="208"/>
-    </row>
-    <row r="22" spans="1:8" ht="15">
-      <c r="A22" s="235"/>
-      <c r="B22" s="236"/>
-      <c r="C22" s="236"/>
-      <c r="D22" s="236"/>
-      <c r="E22" s="236"/>
-      <c r="F22" s="236"/>
-      <c r="G22" s="229"/>
-      <c r="H22" s="208"/>
-    </row>
-    <row r="23" spans="1:8" ht="15">
-      <c r="A23" s="235"/>
-      <c r="B23" s="236"/>
-      <c r="C23" s="236"/>
-      <c r="D23" s="236"/>
-      <c r="E23" s="236"/>
-      <c r="F23" s="391" t="s">
-        <v>62</v>
-      </c>
-      <c r="G23" s="391"/>
-      <c r="H23" s="208"/>
+      <c r="G23" s="400"/>
+      <c r="H23" s="207"/>
     </row>
     <row r="24" spans="1:8" ht="15">
-      <c r="A24" s="235"/>
-      <c r="B24" s="236"/>
-      <c r="C24" s="236"/>
-      <c r="D24" s="236"/>
-      <c r="E24" s="236"/>
-      <c r="F24" s="236"/>
-      <c r="G24" s="229"/>
-      <c r="H24" s="208"/>
+      <c r="A24" s="234"/>
+      <c r="B24" s="235"/>
+      <c r="C24" s="235"/>
+      <c r="D24" s="235"/>
+      <c r="E24" s="235"/>
+      <c r="F24" s="235"/>
+      <c r="G24" s="228"/>
+      <c r="H24" s="207"/>
     </row>
     <row r="25" spans="1:8" ht="15">
-      <c r="A25" s="235"/>
-      <c r="B25" s="236"/>
-      <c r="C25" s="236"/>
-      <c r="D25" s="236"/>
-      <c r="E25" s="236"/>
-      <c r="F25" s="236"/>
-      <c r="G25" s="229"/>
-      <c r="H25" s="208"/>
+      <c r="A25" s="234"/>
+      <c r="B25" s="235"/>
+      <c r="C25" s="235"/>
+      <c r="D25" s="235"/>
+      <c r="E25" s="235"/>
+      <c r="F25" s="235"/>
+      <c r="G25" s="228"/>
+      <c r="H25" s="207"/>
     </row>
     <row r="26" spans="1:8" ht="15">
-      <c r="A26" s="235"/>
-      <c r="B26" s="236"/>
-      <c r="C26" s="236"/>
-      <c r="D26" s="236"/>
-      <c r="E26" s="236"/>
-      <c r="F26" s="236"/>
-      <c r="G26" s="229"/>
-      <c r="H26" s="208"/>
+      <c r="A26" s="234"/>
+      <c r="B26" s="235"/>
+      <c r="C26" s="235"/>
+      <c r="D26" s="235"/>
+      <c r="E26" s="235"/>
+      <c r="F26" s="235"/>
+      <c r="G26" s="228"/>
+      <c r="H26" s="207"/>
     </row>
     <row r="27" spans="1:8" ht="15">
-      <c r="A27" s="235"/>
-      <c r="B27" s="236"/>
-      <c r="C27" s="236"/>
-      <c r="D27" s="236"/>
-      <c r="E27" s="236"/>
-      <c r="F27" s="236"/>
-      <c r="G27" s="229"/>
-      <c r="H27" s="208"/>
+      <c r="A27" s="234"/>
+      <c r="B27" s="235"/>
+      <c r="C27" s="235"/>
+      <c r="D27" s="235"/>
+      <c r="E27" s="235"/>
+      <c r="F27" s="235"/>
+      <c r="G27" s="228"/>
+      <c r="H27" s="207"/>
     </row>
     <row r="28" spans="1:8" ht="15">
-      <c r="A28" s="209"/>
-      <c r="B28" s="236"/>
-      <c r="C28" s="236"/>
-      <c r="D28" s="236"/>
-      <c r="E28" s="236"/>
-      <c r="F28" s="236"/>
-      <c r="G28" s="229"/>
-      <c r="H28" s="208"/>
+      <c r="A28" s="208"/>
+      <c r="B28" s="235"/>
+      <c r="C28" s="235"/>
+      <c r="D28" s="235"/>
+      <c r="E28" s="235"/>
+      <c r="F28" s="235"/>
+      <c r="G28" s="228"/>
+      <c r="H28" s="207"/>
     </row>
     <row r="29" spans="1:8" ht="15">
-      <c r="A29" s="209"/>
-      <c r="B29" s="236"/>
-      <c r="C29" s="236"/>
-      <c r="D29" s="236"/>
-      <c r="E29" s="236"/>
-      <c r="F29" s="236"/>
-      <c r="G29" s="229"/>
-      <c r="H29" s="208"/>
+      <c r="A29" s="208"/>
+      <c r="B29" s="235"/>
+      <c r="C29" s="235"/>
+      <c r="D29" s="235"/>
+      <c r="E29" s="235"/>
+      <c r="F29" s="235"/>
+      <c r="G29" s="228"/>
+      <c r="H29" s="207"/>
     </row>
     <row r="30" spans="1:8" ht="15">
-      <c r="A30" s="209"/>
-      <c r="B30" s="236"/>
-      <c r="C30" s="236"/>
-      <c r="D30" s="236"/>
-      <c r="E30" s="236"/>
-      <c r="F30" s="236"/>
-      <c r="G30" s="229"/>
-      <c r="H30" s="208"/>
+      <c r="A30" s="208"/>
+      <c r="B30" s="235"/>
+      <c r="C30" s="235"/>
+      <c r="D30" s="235"/>
+      <c r="E30" s="235"/>
+      <c r="F30" s="235"/>
+      <c r="G30" s="228"/>
+      <c r="H30" s="207"/>
     </row>
     <row r="31" spans="1:8" ht="15">
-      <c r="A31" s="235"/>
-      <c r="B31" s="236"/>
-      <c r="C31" s="236"/>
-      <c r="D31" s="236"/>
-      <c r="E31" s="236"/>
-      <c r="F31" s="236"/>
-      <c r="G31" s="229"/>
-      <c r="H31" s="208"/>
+      <c r="A31" s="234"/>
+      <c r="B31" s="235"/>
+      <c r="C31" s="235"/>
+      <c r="D31" s="235"/>
+      <c r="E31" s="235"/>
+      <c r="F31" s="235"/>
+      <c r="G31" s="228"/>
+      <c r="H31" s="207"/>
     </row>
     <row r="32" spans="1:8" ht="15">
-      <c r="A32" s="235"/>
-      <c r="B32" s="236"/>
-      <c r="C32" s="236"/>
-      <c r="D32" s="236"/>
-      <c r="E32" s="236"/>
-      <c r="F32" s="236"/>
-      <c r="G32" s="229"/>
-      <c r="H32" s="208"/>
+      <c r="A32" s="234"/>
+      <c r="B32" s="235"/>
+      <c r="C32" s="235"/>
+      <c r="D32" s="235"/>
+      <c r="E32" s="235"/>
+      <c r="F32" s="235"/>
+      <c r="G32" s="228"/>
+      <c r="H32" s="207"/>
     </row>
     <row r="33" spans="1:8" ht="15">
-      <c r="A33" s="235"/>
-      <c r="B33" s="236"/>
-      <c r="C33" s="236"/>
-      <c r="D33" s="236"/>
-      <c r="E33" s="236"/>
-      <c r="F33" s="236"/>
-      <c r="G33" s="229"/>
-      <c r="H33" s="208"/>
+      <c r="A33" s="234"/>
+      <c r="B33" s="235"/>
+      <c r="C33" s="235"/>
+      <c r="D33" s="235"/>
+      <c r="E33" s="235"/>
+      <c r="F33" s="235"/>
+      <c r="G33" s="228"/>
+      <c r="H33" s="207"/>
     </row>
     <row r="34" spans="1:8" ht="15">
-      <c r="A34" s="235"/>
-      <c r="B34" s="236"/>
-      <c r="C34" s="236"/>
-      <c r="D34" s="236"/>
-      <c r="E34" s="236"/>
-      <c r="F34" s="236"/>
-      <c r="G34" s="229"/>
-      <c r="H34" s="208"/>
+      <c r="A34" s="234"/>
+      <c r="B34" s="235"/>
+      <c r="C34" s="235"/>
+      <c r="D34" s="235"/>
+      <c r="E34" s="235"/>
+      <c r="F34" s="235"/>
+      <c r="G34" s="228"/>
+      <c r="H34" s="207"/>
     </row>
     <row r="35" spans="1:8" ht="15">
-      <c r="A35" s="235"/>
-      <c r="B35" s="236"/>
-      <c r="C35" s="236"/>
-      <c r="D35" s="236"/>
-      <c r="E35" s="236"/>
-      <c r="F35" s="236"/>
-      <c r="G35" s="229"/>
-      <c r="H35" s="208"/>
+      <c r="A35" s="234"/>
+      <c r="B35" s="235"/>
+      <c r="C35" s="235"/>
+      <c r="D35" s="235"/>
+      <c r="E35" s="235"/>
+      <c r="F35" s="235"/>
+      <c r="G35" s="228"/>
+      <c r="H35" s="207"/>
     </row>
     <row r="36" spans="1:8" ht="15">
-      <c r="A36" s="235"/>
-      <c r="B36" s="236"/>
-      <c r="C36" s="236"/>
-      <c r="D36" s="236"/>
-      <c r="E36" s="236"/>
-      <c r="F36" s="236"/>
-      <c r="G36" s="229"/>
-      <c r="H36" s="208"/>
+      <c r="A36" s="234"/>
+      <c r="B36" s="235"/>
+      <c r="C36" s="235"/>
+      <c r="D36" s="235"/>
+      <c r="E36" s="235"/>
+      <c r="F36" s="235"/>
+      <c r="G36" s="228"/>
+      <c r="H36" s="207"/>
     </row>
     <row r="37" spans="1:8" ht="15.6">
-      <c r="A37" s="400" t="s">
-        <v>76</v>
-      </c>
-      <c r="B37" s="401"/>
-      <c r="C37" s="236"/>
-      <c r="D37" s="236"/>
-      <c r="E37" s="236"/>
-      <c r="F37" s="236"/>
-      <c r="G37" s="229"/>
-      <c r="H37" s="208"/>
+      <c r="A37" s="396" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" s="397"/>
+      <c r="C37" s="235"/>
+      <c r="D37" s="235"/>
+      <c r="E37" s="235"/>
+      <c r="F37" s="235"/>
+      <c r="G37" s="228"/>
+      <c r="H37" s="207"/>
     </row>
     <row r="38" spans="1:8" ht="15.6">
-      <c r="A38" s="237" t="s">
-        <v>167</v>
-      </c>
-      <c r="B38" s="225" t="s">
-        <v>168</v>
-      </c>
-      <c r="C38" s="236"/>
-      <c r="D38" s="236"/>
-      <c r="E38" s="236"/>
-      <c r="F38" s="236"/>
-      <c r="G38" s="229"/>
-      <c r="H38" s="208"/>
+      <c r="A38" s="236" t="s">
+        <v>142</v>
+      </c>
+      <c r="B38" s="224" t="s">
+        <v>143</v>
+      </c>
+      <c r="C38" s="235"/>
+      <c r="D38" s="235"/>
+      <c r="E38" s="235"/>
+      <c r="F38" s="235"/>
+      <c r="G38" s="228"/>
+      <c r="H38" s="207"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="216"/>
-      <c r="B39" s="217"/>
-      <c r="C39" s="217"/>
-      <c r="D39" s="217"/>
-      <c r="E39" s="217"/>
-      <c r="F39" s="217"/>
-      <c r="G39" s="217"/>
-      <c r="H39" s="214"/>
+      <c r="A39" s="215"/>
+      <c r="B39" s="216"/>
+      <c r="C39" s="216"/>
+      <c r="D39" s="216"/>
+      <c r="E39" s="216"/>
+      <c r="F39" s="216"/>
+      <c r="G39" s="216"/>
+      <c r="H39" s="213"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="218"/>
-      <c r="B40" s="217"/>
-      <c r="C40" s="217"/>
-      <c r="D40" s="217"/>
-      <c r="E40" s="217"/>
-      <c r="F40" s="217"/>
-      <c r="G40" s="217"/>
-      <c r="H40" s="214"/>
+      <c r="A40" s="217"/>
+      <c r="B40" s="216"/>
+      <c r="C40" s="216"/>
+      <c r="D40" s="216"/>
+      <c r="E40" s="216"/>
+      <c r="F40" s="216"/>
+      <c r="G40" s="216"/>
+      <c r="H40" s="213"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="218"/>
-      <c r="B41" s="217"/>
-      <c r="C41" s="217"/>
-      <c r="D41" s="217"/>
-      <c r="E41" s="217"/>
-      <c r="F41" s="217"/>
-      <c r="G41" s="217"/>
-      <c r="H41" s="214"/>
+      <c r="A41" s="217"/>
+      <c r="B41" s="216"/>
+      <c r="C41" s="216"/>
+      <c r="D41" s="216"/>
+      <c r="E41" s="216"/>
+      <c r="F41" s="216"/>
+      <c r="G41" s="216"/>
+      <c r="H41" s="213"/>
     </row>
     <row r="42" spans="1:8" ht="13.8" thickBot="1">
-      <c r="A42" s="219"/>
-      <c r="B42" s="220"/>
-      <c r="C42" s="220"/>
-      <c r="D42" s="220"/>
-      <c r="E42" s="220"/>
-      <c r="F42" s="220"/>
-      <c r="G42" s="220"/>
-      <c r="H42" s="221"/>
+      <c r="A42" s="218"/>
+      <c r="B42" s="219"/>
+      <c r="C42" s="219"/>
+      <c r="D42" s="219"/>
+      <c r="E42" s="219"/>
+      <c r="F42" s="219"/>
+      <c r="G42" s="219"/>
+      <c r="H42" s="220"/>
     </row>
   </sheetData>
   <customSheetViews>
@@ -7800,6 +7501,7 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="22">
+    <mergeCell ref="A13:H13"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="E5:H5"/>
     <mergeCell ref="D21:E21"/>
@@ -7810,11 +7512,6 @@
     <mergeCell ref="E7:H7"/>
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="F18:G18"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A13:H13"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A11:C11"/>
@@ -7822,6 +7519,10 @@
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="E6:H6"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="A8:C8"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -7835,535 +7536,453 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:S30"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" style="210" customWidth="1"/>
-    <col min="2" max="2" width="19.33203125" style="210" customWidth="1"/>
-    <col min="3" max="3" width="6.88671875" style="210" customWidth="1"/>
-    <col min="4" max="4" width="11.33203125" style="210" customWidth="1"/>
-    <col min="5" max="5" width="15" style="210" customWidth="1"/>
-    <col min="6" max="6" width="6.44140625" style="210" customWidth="1"/>
-    <col min="7" max="7" width="7.6640625" style="210" customWidth="1"/>
-    <col min="8" max="8" width="8.44140625" style="210" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="210"/>
+    <col min="1" max="1" width="4.33203125" style="209" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" style="209" customWidth="1"/>
+    <col min="3" max="3" width="6.88671875" style="209" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" style="209" customWidth="1"/>
+    <col min="5" max="5" width="15" style="209" customWidth="1"/>
+    <col min="6" max="6" width="6.44140625" style="209" customWidth="1"/>
+    <col min="7" max="7" width="7.6640625" style="209" customWidth="1"/>
+    <col min="8" max="8" width="8.44140625" style="209" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="209"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="64.2" customHeight="1" thickBot="1">
-      <c r="A1" s="411" t="str">
+    <row r="1" spans="1:9" ht="64.2" customHeight="1" thickBot="1">
+      <c r="A1" s="409" t="str">
         <f>Abstract!A2</f>
         <v>કામ નું નામ :</v>
       </c>
-      <c r="B1" s="412"/>
-      <c r="C1" s="373" t="str">
+      <c r="B1" s="410"/>
+      <c r="C1" s="372" t="str">
         <f>Abstract!B2</f>
         <v xml:space="preserve">ગોળજ ગામે ઉનાળીયા ચેરમેનના ઘર થી ખૂટતા સી.સી. રસ્તાનું કામ . </v>
       </c>
-      <c r="D1" s="374"/>
-      <c r="E1" s="374"/>
-      <c r="F1" s="374"/>
-      <c r="G1" s="374"/>
-      <c r="H1" s="374"/>
-      <c r="I1" s="375"/>
-    </row>
-    <row r="2" spans="1:19" ht="49.2" customHeight="1" thickBot="1">
-      <c r="A2" s="413" t="s">
+      <c r="D1" s="373"/>
+      <c r="E1" s="373"/>
+      <c r="F1" s="373"/>
+      <c r="G1" s="373"/>
+      <c r="H1" s="373"/>
+      <c r="I1" s="374"/>
+    </row>
+    <row r="2" spans="1:9" ht="49.2" customHeight="1" thickBot="1">
+      <c r="A2" s="411" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="414"/>
-      <c r="C2" s="414"/>
-      <c r="D2" s="414"/>
-      <c r="E2" s="414"/>
-      <c r="F2" s="414"/>
-      <c r="G2" s="414"/>
-      <c r="H2" s="414"/>
-      <c r="I2" s="415"/>
-    </row>
-    <row r="3" spans="1:19" ht="34.5" customHeight="1">
-      <c r="A3" s="238" t="s">
+      <c r="B2" s="412"/>
+      <c r="C2" s="412"/>
+      <c r="D2" s="412"/>
+      <c r="E2" s="412"/>
+      <c r="F2" s="412"/>
+      <c r="G2" s="412"/>
+      <c r="H2" s="412"/>
+      <c r="I2" s="413"/>
+    </row>
+    <row r="3" spans="1:9" ht="34.5" customHeight="1">
+      <c r="A3" s="237" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="239" t="s">
+      <c r="B3" s="238" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="240" t="s">
+      <c r="C3" s="239" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="240" t="s">
+      <c r="D3" s="239" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="240" t="s">
+      <c r="E3" s="239" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="416" t="s">
+      <c r="F3" s="414" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="416"/>
-      <c r="H3" s="416"/>
-      <c r="I3" s="241" t="s">
+      <c r="G3" s="414"/>
+      <c r="H3" s="414"/>
+      <c r="I3" s="240" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="210" t="s">
-        <v>126</v>
-      </c>
-      <c r="M3" s="210" t="s">
-        <v>127</v>
-      </c>
-      <c r="R3" s="210" t="s">
-        <v>128</v>
-      </c>
-      <c r="S3" s="210">
-        <v>417.53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="52.8">
-      <c r="A4" s="242">
+    </row>
+    <row r="4" spans="1:9" ht="52.8">
+      <c r="A4" s="241">
         <v>2</v>
       </c>
-      <c r="B4" s="243" t="s">
-        <v>141</v>
-      </c>
-      <c r="C4" s="270">
+      <c r="B4" s="242" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" s="269">
         <f>Lead!D8</f>
         <v>30</v>
       </c>
-      <c r="D4" s="245">
+      <c r="D4" s="244">
         <v>417.53</v>
       </c>
-      <c r="E4" s="246">
+      <c r="E4" s="245">
         <v>81.8</v>
       </c>
-      <c r="F4" s="247">
+      <c r="F4" s="246">
         <v>30</v>
       </c>
-      <c r="G4" s="244">
+      <c r="G4" s="243">
         <v>5.95</v>
       </c>
-      <c r="H4" s="245">
+      <c r="H4" s="244">
         <f>G4*F4</f>
         <v>178.5</v>
       </c>
-      <c r="I4" s="248">
+      <c r="I4" s="247">
         <f>D4+E4+H4</f>
         <v>677.82999999999993</v>
       </c>
-      <c r="L4" s="210" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="40.5" customHeight="1">
-      <c r="A5" s="242">
+    </row>
+    <row r="5" spans="1:9" ht="40.5" customHeight="1">
+      <c r="A5" s="241">
         <v>3</v>
       </c>
-      <c r="B5" s="243" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="270">
+      <c r="B5" s="242" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" s="269">
         <f>Lead!D11</f>
         <v>5</v>
       </c>
-      <c r="D5" s="245">
+      <c r="D5" s="244">
         <v>90</v>
       </c>
-      <c r="E5" s="249">
+      <c r="E5" s="248">
         <v>81.8</v>
       </c>
-      <c r="F5" s="245">
+      <c r="F5" s="244">
         <v>5</v>
       </c>
-      <c r="G5" s="250">
+      <c r="G5" s="249">
         <v>0</v>
       </c>
-      <c r="H5" s="245">
+      <c r="H5" s="244">
         <f>TRUNC((G5*F5),2)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="248">
+      <c r="I5" s="247">
         <f>D5+E5+H5</f>
         <v>171.8</v>
       </c>
-      <c r="L5" s="210" t="s">
-        <v>130</v>
-      </c>
-      <c r="M5" s="210" t="s">
-        <v>131</v>
-      </c>
-      <c r="R5" s="210" t="s">
-        <v>128</v>
-      </c>
-      <c r="S5" s="210">
-        <v>81.8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="14.25" customHeight="1">
-      <c r="A6" s="251"/>
-      <c r="B6" s="252"/>
-      <c r="C6" s="170"/>
-      <c r="D6" s="253"/>
-      <c r="E6" s="254"/>
-      <c r="F6" s="253"/>
-      <c r="G6" s="255"/>
-      <c r="H6" s="253"/>
-      <c r="I6" s="256"/>
-      <c r="L6" s="210" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="14.25" customHeight="1">
-      <c r="A7" s="257"/>
-      <c r="B7" s="252"/>
-      <c r="C7" s="258"/>
-      <c r="D7" s="204"/>
-      <c r="E7" s="259" t="s">
+    </row>
+    <row r="6" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A6" s="250"/>
+      <c r="B6" s="251"/>
+      <c r="C6" s="169"/>
+      <c r="D6" s="252"/>
+      <c r="E6" s="253"/>
+      <c r="F6" s="252"/>
+      <c r="G6" s="254"/>
+      <c r="H6" s="252"/>
+      <c r="I6" s="255"/>
+    </row>
+    <row r="7" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A7" s="256"/>
+      <c r="B7" s="251"/>
+      <c r="C7" s="257"/>
+      <c r="D7" s="203"/>
+      <c r="E7" s="258" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="253"/>
-      <c r="G7" s="255"/>
-      <c r="H7" s="407" t="s">
-        <v>65</v>
-      </c>
-      <c r="I7" s="408"/>
-      <c r="L7" s="210" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="14.25" customHeight="1">
-      <c r="A8" s="409" t="s">
+      <c r="F7" s="252"/>
+      <c r="G7" s="254"/>
+      <c r="H7" s="405" t="s">
+        <v>63</v>
+      </c>
+      <c r="I7" s="406"/>
+    </row>
+    <row r="8" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A8" s="407" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="410"/>
-      <c r="C8" s="410"/>
-      <c r="D8" s="410"/>
-      <c r="E8" s="260">
+      <c r="B8" s="408"/>
+      <c r="C8" s="408"/>
+      <c r="D8" s="408"/>
+      <c r="E8" s="259">
         <v>6.5</v>
       </c>
-      <c r="F8" s="253"/>
-      <c r="G8" s="255"/>
-      <c r="H8" s="260">
+      <c r="F8" s="252"/>
+      <c r="G8" s="254"/>
+      <c r="H8" s="259">
         <v>5.85</v>
       </c>
-      <c r="I8" s="261"/>
-      <c r="L8" s="210" t="s">
-        <v>134</v>
-      </c>
-      <c r="M8" s="210" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="14.25" customHeight="1">
-      <c r="A9" s="405" t="s">
+      <c r="I8" s="260"/>
+    </row>
+    <row r="9" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A9" s="403" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="406"/>
-      <c r="C9" s="406"/>
-      <c r="D9" s="406"/>
-      <c r="E9" s="260">
+      <c r="B9" s="404"/>
+      <c r="C9" s="404"/>
+      <c r="D9" s="404"/>
+      <c r="E9" s="259">
         <v>5.86</v>
       </c>
-      <c r="F9" s="253"/>
-      <c r="G9" s="255"/>
-      <c r="H9" s="260">
+      <c r="F9" s="252"/>
+      <c r="G9" s="254"/>
+      <c r="H9" s="259">
         <v>5.27</v>
       </c>
-      <c r="I9" s="261"/>
-      <c r="M9" s="210">
+      <c r="I9" s="260"/>
+    </row>
+    <row r="10" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A10" s="403" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="404"/>
+      <c r="C10" s="404"/>
+      <c r="D10" s="404"/>
+      <c r="E10" s="259">
+        <v>5.41</v>
+      </c>
+      <c r="F10" s="258"/>
+      <c r="G10" s="258"/>
+      <c r="H10" s="259">
+        <v>4.87</v>
+      </c>
+      <c r="I10" s="260"/>
+    </row>
+    <row r="11" spans="1:9" ht="12.75" customHeight="1">
+      <c r="A11" s="403" t="s">
         <v>55</v>
       </c>
-      <c r="N9" s="210" t="s">
-        <v>136</v>
-      </c>
-      <c r="O9" s="210">
-        <v>5</v>
-      </c>
-      <c r="P9" s="210" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q9" s="210">
-        <f>M9-O9</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="14.25" customHeight="1">
-      <c r="A10" s="405" t="s">
-        <v>54</v>
-      </c>
-      <c r="B10" s="406"/>
-      <c r="C10" s="406"/>
-      <c r="D10" s="406"/>
-      <c r="E10" s="260">
-        <v>5.41</v>
-      </c>
-      <c r="F10" s="259"/>
-      <c r="G10" s="259"/>
-      <c r="H10" s="260">
-        <v>4.87</v>
-      </c>
-      <c r="I10" s="261"/>
-      <c r="M10" s="210">
-        <v>50</v>
-      </c>
-      <c r="N10" s="210" t="s">
-        <v>137</v>
-      </c>
-      <c r="O10" s="210">
-        <v>5.95</v>
-      </c>
-      <c r="P10" s="210" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q10" s="210">
-        <f>M10*O10</f>
-        <v>297.5</v>
-      </c>
-      <c r="R10" s="210" t="s">
-        <v>128</v>
-      </c>
-      <c r="S10" s="210">
-        <f>Q10</f>
-        <v>297.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="12.75" customHeight="1">
-      <c r="A11" s="405" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" s="406"/>
-      <c r="C11" s="406"/>
-      <c r="D11" s="406"/>
-      <c r="E11" s="260">
+      <c r="B11" s="404"/>
+      <c r="C11" s="404"/>
+      <c r="D11" s="404"/>
+      <c r="E11" s="259">
         <v>5.35</v>
       </c>
-      <c r="F11" s="259"/>
-      <c r="G11" s="259"/>
-      <c r="H11" s="260">
+      <c r="F11" s="258"/>
+      <c r="G11" s="258"/>
+      <c r="H11" s="259">
         <v>4.82</v>
       </c>
-      <c r="I11" s="261"/>
-      <c r="S11" s="210">
-        <f>S10+S5+S3</f>
-        <v>796.82999999999993</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="12.75" customHeight="1">
-      <c r="A12" s="405" t="s">
+      <c r="I11" s="260"/>
+    </row>
+    <row r="12" spans="1:9" ht="12.75" customHeight="1">
+      <c r="A12" s="403" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="406"/>
-      <c r="C12" s="406"/>
-      <c r="D12" s="406"/>
-      <c r="E12" s="260">
+      <c r="B12" s="404"/>
+      <c r="C12" s="404"/>
+      <c r="D12" s="404"/>
+      <c r="E12" s="259">
         <v>5.96</v>
       </c>
-      <c r="F12" s="204"/>
-      <c r="G12" s="204"/>
-      <c r="H12" s="260">
+      <c r="F12" s="203"/>
+      <c r="G12" s="203"/>
+      <c r="H12" s="259">
         <v>5.36</v>
       </c>
-      <c r="I12" s="261"/>
-    </row>
-    <row r="13" spans="1:19" ht="12.75" customHeight="1">
-      <c r="A13" s="262"/>
-      <c r="B13" s="263"/>
-      <c r="C13" s="263"/>
-      <c r="D13" s="263"/>
-      <c r="E13" s="260"/>
-      <c r="F13" s="204"/>
-      <c r="G13" s="204"/>
-      <c r="H13" s="264"/>
-      <c r="I13" s="261"/>
-    </row>
-    <row r="14" spans="1:19" ht="12.75" customHeight="1">
-      <c r="A14" s="262"/>
-      <c r="B14" s="263"/>
-      <c r="C14" s="263"/>
-      <c r="D14" s="263"/>
-      <c r="E14" s="260"/>
-      <c r="F14" s="204"/>
-      <c r="G14" s="204"/>
-      <c r="H14" s="264"/>
-      <c r="I14" s="261"/>
-    </row>
-    <row r="15" spans="1:19" ht="12.75" customHeight="1">
-      <c r="A15" s="262"/>
-      <c r="B15" s="263"/>
-      <c r="C15" s="263"/>
-      <c r="D15" s="263"/>
-      <c r="E15" s="260"/>
-      <c r="F15" s="204"/>
-      <c r="G15" s="204"/>
-      <c r="H15" s="264"/>
-      <c r="I15" s="261"/>
-    </row>
-    <row r="16" spans="1:19">
-      <c r="A16" s="265"/>
-      <c r="B16" s="204"/>
-      <c r="C16" s="204"/>
-      <c r="D16" s="266"/>
-      <c r="E16" s="204"/>
-      <c r="F16" s="204"/>
-      <c r="G16" s="204"/>
-      <c r="H16" s="204"/>
-      <c r="I16" s="208"/>
+      <c r="I12" s="260"/>
+    </row>
+    <row r="13" spans="1:9" ht="12.75" customHeight="1">
+      <c r="A13" s="261"/>
+      <c r="B13" s="262"/>
+      <c r="C13" s="262"/>
+      <c r="D13" s="262"/>
+      <c r="E13" s="259"/>
+      <c r="F13" s="203"/>
+      <c r="G13" s="203"/>
+      <c r="H13" s="263"/>
+      <c r="I13" s="260"/>
+    </row>
+    <row r="14" spans="1:9" ht="12.75" customHeight="1">
+      <c r="A14" s="261"/>
+      <c r="B14" s="262"/>
+      <c r="C14" s="262"/>
+      <c r="D14" s="262"/>
+      <c r="E14" s="259"/>
+      <c r="F14" s="203"/>
+      <c r="G14" s="203"/>
+      <c r="H14" s="263"/>
+      <c r="I14" s="260"/>
+    </row>
+    <row r="15" spans="1:9" ht="12.75" customHeight="1">
+      <c r="A15" s="261"/>
+      <c r="B15" s="262"/>
+      <c r="C15" s="262"/>
+      <c r="D15" s="262"/>
+      <c r="E15" s="259"/>
+      <c r="F15" s="203"/>
+      <c r="G15" s="203"/>
+      <c r="H15" s="263"/>
+      <c r="I15" s="260"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="264"/>
+      <c r="B16" s="203"/>
+      <c r="C16" s="203"/>
+      <c r="D16" s="265"/>
+      <c r="E16" s="203"/>
+      <c r="F16" s="203"/>
+      <c r="G16" s="203"/>
+      <c r="H16" s="203"/>
+      <c r="I16" s="207"/>
     </row>
     <row r="17" spans="1:9" ht="15.6">
-      <c r="A17" s="265"/>
-      <c r="B17" s="403" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" s="403"/>
-      <c r="D17" s="403"/>
-      <c r="E17" s="203"/>
-      <c r="F17" s="203"/>
-      <c r="G17" s="203"/>
-      <c r="H17" s="203"/>
-      <c r="I17" s="208"/>
+      <c r="A17" s="264"/>
+      <c r="B17" s="415" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="415"/>
+      <c r="D17" s="415"/>
+      <c r="E17" s="202"/>
+      <c r="F17" s="202"/>
+      <c r="G17" s="202"/>
+      <c r="H17" s="202"/>
+      <c r="I17" s="207"/>
     </row>
     <row r="18" spans="1:9" ht="15.6">
-      <c r="A18" s="209"/>
-      <c r="B18" s="271" t="s">
-        <v>167</v>
-      </c>
-      <c r="C18" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="D18" s="271"/>
-      <c r="E18" s="203"/>
-      <c r="F18" s="203"/>
-      <c r="G18" s="203"/>
-      <c r="H18" s="203"/>
-      <c r="I18" s="208"/>
+      <c r="A18" s="208"/>
+      <c r="B18" s="270" t="s">
+        <v>142</v>
+      </c>
+      <c r="C18" s="36" t="s">
+        <v>143</v>
+      </c>
+      <c r="D18" s="270"/>
+      <c r="E18" s="202"/>
+      <c r="F18" s="202"/>
+      <c r="G18" s="202"/>
+      <c r="H18" s="202"/>
+      <c r="I18" s="207"/>
     </row>
     <row r="19" spans="1:9" ht="15">
-      <c r="A19" s="209"/>
-      <c r="B19" s="404"/>
-      <c r="C19" s="404"/>
-      <c r="D19" s="404"/>
-      <c r="E19" s="203"/>
-      <c r="F19" s="203"/>
-      <c r="G19" s="203"/>
-      <c r="H19" s="203"/>
-      <c r="I19" s="208"/>
+      <c r="A19" s="208"/>
+      <c r="B19" s="402"/>
+      <c r="C19" s="402"/>
+      <c r="D19" s="402"/>
+      <c r="E19" s="202"/>
+      <c r="F19" s="202"/>
+      <c r="G19" s="202"/>
+      <c r="H19" s="202"/>
+      <c r="I19" s="207"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="209"/>
-      <c r="B20" s="204"/>
-      <c r="C20" s="204"/>
-      <c r="D20" s="204"/>
-      <c r="E20" s="204"/>
-      <c r="F20" s="204"/>
-      <c r="G20" s="204"/>
-      <c r="H20" s="204"/>
-      <c r="I20" s="208"/>
+      <c r="A20" s="208"/>
+      <c r="B20" s="203"/>
+      <c r="C20" s="203"/>
+      <c r="D20" s="203"/>
+      <c r="E20" s="203"/>
+      <c r="F20" s="203"/>
+      <c r="G20" s="203"/>
+      <c r="H20" s="203"/>
+      <c r="I20" s="207"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="209"/>
-      <c r="B21" s="204"/>
-      <c r="C21" s="204"/>
-      <c r="D21" s="204"/>
-      <c r="E21" s="204"/>
-      <c r="F21" s="204"/>
-      <c r="G21" s="204"/>
-      <c r="H21" s="204"/>
-      <c r="I21" s="208"/>
+      <c r="A21" s="208"/>
+      <c r="B21" s="203"/>
+      <c r="C21" s="203"/>
+      <c r="D21" s="203"/>
+      <c r="E21" s="203"/>
+      <c r="F21" s="203"/>
+      <c r="G21" s="203"/>
+      <c r="H21" s="203"/>
+      <c r="I21" s="207"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="209"/>
-      <c r="B22" s="204"/>
-      <c r="C22" s="204"/>
-      <c r="D22" s="204"/>
-      <c r="E22" s="204"/>
-      <c r="F22" s="204"/>
-      <c r="G22" s="204"/>
-      <c r="H22" s="204"/>
-      <c r="I22" s="208"/>
+      <c r="A22" s="208"/>
+      <c r="B22" s="203"/>
+      <c r="C22" s="203"/>
+      <c r="D22" s="203"/>
+      <c r="E22" s="203"/>
+      <c r="F22" s="203"/>
+      <c r="G22" s="203"/>
+      <c r="H22" s="203"/>
+      <c r="I22" s="207"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="209"/>
-      <c r="B23" s="204"/>
-      <c r="C23" s="204"/>
-      <c r="D23" s="204"/>
-      <c r="E23" s="204"/>
-      <c r="F23" s="204"/>
-      <c r="G23" s="204"/>
-      <c r="H23" s="204"/>
-      <c r="I23" s="208"/>
+      <c r="A23" s="208"/>
+      <c r="B23" s="203"/>
+      <c r="C23" s="203"/>
+      <c r="D23" s="203"/>
+      <c r="E23" s="203"/>
+      <c r="F23" s="203"/>
+      <c r="G23" s="203"/>
+      <c r="H23" s="203"/>
+      <c r="I23" s="207"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="209"/>
-      <c r="B24" s="204"/>
-      <c r="C24" s="204"/>
-      <c r="D24" s="204"/>
-      <c r="E24" s="204"/>
-      <c r="F24" s="204"/>
-      <c r="G24" s="204"/>
-      <c r="H24" s="204"/>
-      <c r="I24" s="208"/>
+      <c r="A24" s="208"/>
+      <c r="B24" s="203"/>
+      <c r="C24" s="203"/>
+      <c r="D24" s="203"/>
+      <c r="E24" s="203"/>
+      <c r="F24" s="203"/>
+      <c r="G24" s="203"/>
+      <c r="H24" s="203"/>
+      <c r="I24" s="207"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="209"/>
-      <c r="B25" s="204"/>
-      <c r="C25" s="204"/>
-      <c r="D25" s="204"/>
-      <c r="E25" s="204"/>
-      <c r="F25" s="204"/>
-      <c r="G25" s="204"/>
-      <c r="H25" s="204"/>
-      <c r="I25" s="208"/>
+      <c r="A25" s="208"/>
+      <c r="B25" s="203"/>
+      <c r="C25" s="203"/>
+      <c r="D25" s="203"/>
+      <c r="E25" s="203"/>
+      <c r="F25" s="203"/>
+      <c r="G25" s="203"/>
+      <c r="H25" s="203"/>
+      <c r="I25" s="207"/>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="209"/>
-      <c r="B26" s="204"/>
-      <c r="C26" s="204"/>
-      <c r="D26" s="204"/>
-      <c r="E26" s="204"/>
-      <c r="F26" s="204"/>
-      <c r="G26" s="204"/>
-      <c r="H26" s="204"/>
-      <c r="I26" s="208"/>
+      <c r="A26" s="208"/>
+      <c r="B26" s="203"/>
+      <c r="C26" s="203"/>
+      <c r="D26" s="203"/>
+      <c r="E26" s="203"/>
+      <c r="F26" s="203"/>
+      <c r="G26" s="203"/>
+      <c r="H26" s="203"/>
+      <c r="I26" s="207"/>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="209"/>
-      <c r="B27" s="204"/>
-      <c r="C27" s="204"/>
-      <c r="D27" s="204"/>
-      <c r="E27" s="204"/>
-      <c r="F27" s="204"/>
-      <c r="G27" s="204"/>
-      <c r="H27" s="204"/>
-      <c r="I27" s="208"/>
+      <c r="A27" s="208"/>
+      <c r="B27" s="203"/>
+      <c r="C27" s="203"/>
+      <c r="D27" s="203"/>
+      <c r="E27" s="203"/>
+      <c r="F27" s="203"/>
+      <c r="G27" s="203"/>
+      <c r="H27" s="203"/>
+      <c r="I27" s="207"/>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="209"/>
-      <c r="B28" s="204"/>
-      <c r="C28" s="204"/>
-      <c r="D28" s="204"/>
-      <c r="E28" s="204"/>
-      <c r="F28" s="204"/>
-      <c r="G28" s="204"/>
-      <c r="H28" s="204"/>
-      <c r="I28" s="208"/>
+      <c r="A28" s="208"/>
+      <c r="B28" s="203"/>
+      <c r="C28" s="203"/>
+      <c r="D28" s="203"/>
+      <c r="E28" s="203"/>
+      <c r="F28" s="203"/>
+      <c r="G28" s="203"/>
+      <c r="H28" s="203"/>
+      <c r="I28" s="207"/>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="209"/>
-      <c r="B29" s="204"/>
-      <c r="C29" s="204"/>
-      <c r="D29" s="204"/>
-      <c r="E29" s="204"/>
-      <c r="F29" s="204"/>
-      <c r="G29" s="204"/>
-      <c r="H29" s="204"/>
-      <c r="I29" s="208"/>
+      <c r="A29" s="208"/>
+      <c r="B29" s="203"/>
+      <c r="C29" s="203"/>
+      <c r="D29" s="203"/>
+      <c r="E29" s="203"/>
+      <c r="F29" s="203"/>
+      <c r="G29" s="203"/>
+      <c r="H29" s="203"/>
+      <c r="I29" s="207"/>
     </row>
     <row r="30" spans="1:9" ht="13.8" thickBot="1">
-      <c r="A30" s="267"/>
-      <c r="B30" s="268"/>
-      <c r="C30" s="268"/>
-      <c r="D30" s="268"/>
-      <c r="E30" s="268"/>
-      <c r="F30" s="268"/>
-      <c r="G30" s="268"/>
-      <c r="H30" s="268"/>
-      <c r="I30" s="269"/>
+      <c r="A30" s="266"/>
+      <c r="B30" s="267"/>
+      <c r="C30" s="267"/>
+      <c r="D30" s="267"/>
+      <c r="E30" s="267"/>
+      <c r="F30" s="267"/>
+      <c r="G30" s="267"/>
+      <c r="H30" s="267"/>
+      <c r="I30" s="268"/>
     </row>
   </sheetData>
   <customSheetViews>

--- a/skeleton-cc.xlsx
+++ b/skeleton-cc.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="9552" windowHeight="3408"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="9552" windowHeight="3408" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="FACE SHEET" sheetId="1" r:id="rId1"/>
@@ -1993,12 +1993,124 @@
     <xf numFmtId="2" fontId="30" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="28" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="25" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -2007,143 +2119,59 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="34" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="34" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="34" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="25" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="34" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="28" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="34" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="34" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2152,32 +2180,40 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="34" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="34" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2190,6 +2226,12 @@
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2205,12 +2247,6 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -2231,42 +2267,6 @@
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="2" fontId="32" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -2300,6 +2300,57 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="46" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="36" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2312,24 +2363,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2357,41 +2393,26 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="46" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="30" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="36" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="36" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2413,27 +2434,6 @@
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="30" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3001,17 +3001,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30.75" customHeight="1" thickBot="1">
-      <c r="A1" s="266" t="s">
+      <c r="A1" s="289" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="267"/>
-      <c r="C1" s="267"/>
-      <c r="D1" s="267"/>
-      <c r="E1" s="267"/>
-      <c r="F1" s="267"/>
-      <c r="G1" s="267"/>
-      <c r="H1" s="267"/>
-      <c r="I1" s="268"/>
+      <c r="B1" s="290"/>
+      <c r="C1" s="290"/>
+      <c r="D1" s="290"/>
+      <c r="E1" s="290"/>
+      <c r="F1" s="290"/>
+      <c r="G1" s="290"/>
+      <c r="H1" s="290"/>
+      <c r="I1" s="291"/>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="3"/>
@@ -3025,11 +3025,11 @@
       <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:9" ht="15">
-      <c r="A3" s="262" t="s">
+      <c r="A3" s="264" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="263"/>
-      <c r="C3" s="263"/>
+      <c r="B3" s="265"/>
+      <c r="C3" s="265"/>
       <c r="D3" s="21" t="s">
         <v>133</v>
       </c>
@@ -3056,11 +3056,11 @@
       <c r="I4" s="7"/>
     </row>
     <row r="5" spans="1:9" ht="15">
-      <c r="A5" s="262" t="s">
+      <c r="A5" s="264" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="263"/>
-      <c r="C5" s="263"/>
+      <c r="B5" s="265"/>
+      <c r="C5" s="265"/>
       <c r="D5" s="21" t="s">
         <v>137</v>
       </c>
@@ -3089,11 +3089,11 @@
       <c r="I6" s="7"/>
     </row>
     <row r="7" spans="1:9" ht="15">
-      <c r="A7" s="262" t="s">
+      <c r="A7" s="264" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="263"/>
-      <c r="C7" s="263"/>
+      <c r="B7" s="265"/>
+      <c r="C7" s="265"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -3113,19 +3113,19 @@
       <c r="I8" s="7"/>
     </row>
     <row r="9" spans="1:9" ht="20.399999999999999">
-      <c r="A9" s="262" t="s">
+      <c r="A9" s="264" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="263"/>
-      <c r="C9" s="263"/>
-      <c r="D9" s="264" t="s">
+      <c r="B9" s="265"/>
+      <c r="C9" s="265"/>
+      <c r="D9" s="297" t="s">
         <v>127</v>
       </c>
-      <c r="E9" s="264"/>
-      <c r="F9" s="264"/>
-      <c r="G9" s="264"/>
-      <c r="H9" s="264"/>
-      <c r="I9" s="265"/>
+      <c r="E9" s="297"/>
+      <c r="F9" s="297"/>
+      <c r="G9" s="297"/>
+      <c r="H9" s="297"/>
+      <c r="I9" s="298"/>
     </row>
     <row r="10" spans="1:9" ht="15">
       <c r="A10" s="19"/>
@@ -3139,11 +3139,11 @@
       <c r="I10" s="7"/>
     </row>
     <row r="11" spans="1:9" ht="15">
-      <c r="A11" s="262" t="s">
+      <c r="A11" s="264" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="263"/>
-      <c r="C11" s="263"/>
+      <c r="B11" s="265"/>
+      <c r="C11" s="265"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
@@ -3163,11 +3163,11 @@
       <c r="I12" s="7"/>
     </row>
     <row r="13" spans="1:9" ht="15">
-      <c r="A13" s="262" t="s">
+      <c r="A13" s="264" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="263"/>
-      <c r="C13" s="263"/>
+      <c r="B13" s="265"/>
+      <c r="C13" s="265"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
@@ -3187,11 +3187,11 @@
       <c r="I14" s="7"/>
     </row>
     <row r="15" spans="1:9" ht="15">
-      <c r="A15" s="262" t="s">
+      <c r="A15" s="264" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="263"/>
-      <c r="C15" s="263"/>
+      <c r="B15" s="265"/>
+      <c r="C15" s="265"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
@@ -3211,11 +3211,11 @@
       <c r="I16" s="7"/>
     </row>
     <row r="17" spans="1:53" ht="15">
-      <c r="A17" s="262" t="s">
+      <c r="A17" s="264" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="263"/>
-      <c r="C17" s="263"/>
+      <c r="B17" s="265"/>
+      <c r="C17" s="265"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
@@ -3235,19 +3235,19 @@
       <c r="I18" s="7"/>
     </row>
     <row r="19" spans="1:53" s="32" customFormat="1" ht="15" customHeight="1">
-      <c r="A19" s="269" t="s">
+      <c r="A19" s="275" t="s">
         <v>144</v>
       </c>
-      <c r="B19" s="269"/>
-      <c r="C19" s="269"/>
-      <c r="D19" s="269"/>
-      <c r="E19" s="269"/>
-      <c r="F19" s="269"/>
-      <c r="G19" s="269"/>
-      <c r="H19" s="273" t="s">
+      <c r="B19" s="275"/>
+      <c r="C19" s="275"/>
+      <c r="D19" s="275"/>
+      <c r="E19" s="275"/>
+      <c r="F19" s="275"/>
+      <c r="G19" s="275"/>
+      <c r="H19" s="295" t="s">
         <v>143</v>
       </c>
-      <c r="I19" s="274"/>
+      <c r="I19" s="296"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
@@ -3294,17 +3294,17 @@
       <c r="BA19" s="2"/>
     </row>
     <row r="20" spans="1:53" s="33" customFormat="1" ht="28.8" customHeight="1">
-      <c r="A20" s="269" t="s">
+      <c r="A20" s="275" t="s">
         <v>145</v>
       </c>
-      <c r="B20" s="269"/>
-      <c r="C20" s="269"/>
-      <c r="D20" s="269"/>
-      <c r="E20" s="269"/>
-      <c r="F20" s="269"/>
-      <c r="G20" s="269"/>
-      <c r="H20" s="269"/>
-      <c r="I20" s="270"/>
+      <c r="B20" s="275"/>
+      <c r="C20" s="275"/>
+      <c r="D20" s="275"/>
+      <c r="E20" s="275"/>
+      <c r="F20" s="275"/>
+      <c r="G20" s="275"/>
+      <c r="H20" s="275"/>
+      <c r="I20" s="292"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
@@ -3351,33 +3351,33 @@
       <c r="BA20" s="2"/>
     </row>
     <row r="21" spans="1:53" ht="45" customHeight="1">
-      <c r="A21" s="271" t="s">
+      <c r="A21" s="293" t="s">
         <v>86</v>
       </c>
-      <c r="B21" s="272"/>
-      <c r="C21" s="295" t="s">
+      <c r="B21" s="294"/>
+      <c r="C21" s="273" t="s">
         <v>130</v>
       </c>
-      <c r="D21" s="295"/>
-      <c r="E21" s="295"/>
-      <c r="F21" s="295"/>
-      <c r="G21" s="295"/>
-      <c r="H21" s="295"/>
-      <c r="I21" s="296"/>
+      <c r="D21" s="273"/>
+      <c r="E21" s="273"/>
+      <c r="F21" s="273"/>
+      <c r="G21" s="273"/>
+      <c r="H21" s="273"/>
+      <c r="I21" s="274"/>
     </row>
     <row r="22" spans="1:53" ht="17.25" customHeight="1">
-      <c r="A22" s="288" t="s">
+      <c r="A22" s="266" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="289"/>
-      <c r="C22" s="289"/>
-      <c r="D22" s="289"/>
-      <c r="E22" s="289"/>
-      <c r="F22" s="289"/>
-      <c r="G22" s="297">
+      <c r="B22" s="267"/>
+      <c r="C22" s="267"/>
+      <c r="D22" s="267"/>
+      <c r="E22" s="267"/>
+      <c r="F22" s="267"/>
+      <c r="G22" s="276">
         <v>100000</v>
       </c>
-      <c r="H22" s="297"/>
+      <c r="H22" s="276"/>
       <c r="I22" s="10"/>
     </row>
     <row r="23" spans="1:53" ht="15">
@@ -3444,19 +3444,19 @@
       <c r="I27" s="7"/>
     </row>
     <row r="28" spans="1:53" ht="15">
-      <c r="A28" s="280" t="s">
+      <c r="A28" s="283" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="281"/>
-      <c r="C28" s="281"/>
-      <c r="D28" s="278" t="s">
+      <c r="B28" s="284"/>
+      <c r="C28" s="284"/>
+      <c r="D28" s="281" t="s">
         <v>128</v>
       </c>
-      <c r="E28" s="278"/>
-      <c r="F28" s="278"/>
-      <c r="G28" s="278"/>
-      <c r="H28" s="278"/>
-      <c r="I28" s="279"/>
+      <c r="E28" s="281"/>
+      <c r="F28" s="281"/>
+      <c r="G28" s="281"/>
+      <c r="H28" s="281"/>
+      <c r="I28" s="282"/>
     </row>
     <row r="29" spans="1:53" ht="15">
       <c r="A29" s="25"/>
@@ -3470,20 +3470,20 @@
       <c r="I29" s="7"/>
     </row>
     <row r="30" spans="1:53" ht="15">
-      <c r="A30" s="280" t="s">
+      <c r="A30" s="283" t="s">
         <v>0</v>
       </c>
-      <c r="B30" s="281"/>
-      <c r="C30" s="281"/>
-      <c r="D30" s="278" t="str">
+      <c r="B30" s="284"/>
+      <c r="C30" s="284"/>
+      <c r="D30" s="281" t="str">
         <f>D28</f>
         <v>MR.V.A.THAKOR. A.A.E.</v>
       </c>
-      <c r="E30" s="278"/>
-      <c r="F30" s="278"/>
-      <c r="G30" s="278"/>
-      <c r="H30" s="278"/>
-      <c r="I30" s="279"/>
+      <c r="E30" s="281"/>
+      <c r="F30" s="281"/>
+      <c r="G30" s="281"/>
+      <c r="H30" s="281"/>
+      <c r="I30" s="282"/>
     </row>
     <row r="31" spans="1:53" ht="17.399999999999999" customHeight="1">
       <c r="A31" s="25"/>
@@ -3497,30 +3497,30 @@
       <c r="I31" s="7"/>
     </row>
     <row r="32" spans="1:53" ht="15" customHeight="1">
-      <c r="A32" s="290" t="s">
+      <c r="A32" s="268" t="s">
         <v>18</v>
       </c>
-      <c r="B32" s="291"/>
-      <c r="C32" s="291"/>
-      <c r="D32" s="276"/>
-      <c r="E32" s="276"/>
-      <c r="F32" s="276"/>
-      <c r="G32" s="276"/>
-      <c r="H32" s="276"/>
-      <c r="I32" s="277"/>
+      <c r="B32" s="269"/>
+      <c r="C32" s="269"/>
+      <c r="D32" s="279"/>
+      <c r="E32" s="279"/>
+      <c r="F32" s="279"/>
+      <c r="G32" s="279"/>
+      <c r="H32" s="279"/>
+      <c r="I32" s="280"/>
     </row>
     <row r="33" spans="1:9" ht="25.5" customHeight="1">
-      <c r="A33" s="283" t="s">
+      <c r="A33" s="286" t="s">
         <v>62</v>
       </c>
-      <c r="B33" s="284"/>
-      <c r="C33" s="284"/>
-      <c r="D33" s="284"/>
-      <c r="E33" s="284"/>
-      <c r="F33" s="284"/>
-      <c r="G33" s="284"/>
-      <c r="H33" s="284"/>
-      <c r="I33" s="285"/>
+      <c r="B33" s="287"/>
+      <c r="C33" s="287"/>
+      <c r="D33" s="287"/>
+      <c r="E33" s="287"/>
+      <c r="F33" s="287"/>
+      <c r="G33" s="287"/>
+      <c r="H33" s="287"/>
+      <c r="I33" s="288"/>
     </row>
     <row r="34" spans="1:9" ht="42" customHeight="1">
       <c r="A34" s="27" t="s">
@@ -3529,48 +3529,48 @@
       <c r="B34" s="31">
         <v>6</v>
       </c>
-      <c r="C34" s="286" t="s">
+      <c r="C34" s="262" t="s">
         <v>129</v>
       </c>
-      <c r="D34" s="286"/>
-      <c r="E34" s="286"/>
-      <c r="F34" s="286"/>
-      <c r="G34" s="286"/>
-      <c r="H34" s="286"/>
-      <c r="I34" s="287"/>
+      <c r="D34" s="262"/>
+      <c r="E34" s="262"/>
+      <c r="F34" s="262"/>
+      <c r="G34" s="262"/>
+      <c r="H34" s="262"/>
+      <c r="I34" s="263"/>
     </row>
     <row r="35" spans="1:9" ht="42" customHeight="1">
       <c r="A35" s="27" t="s">
         <v>124</v>
       </c>
-      <c r="B35" s="298" t="s">
+      <c r="B35" s="277" t="s">
         <v>131</v>
       </c>
-      <c r="C35" s="298"/>
-      <c r="D35" s="298"/>
+      <c r="C35" s="277"/>
+      <c r="D35" s="277"/>
       <c r="E35" s="35" t="s">
         <v>125</v>
       </c>
-      <c r="F35" s="286" t="str">
+      <c r="F35" s="262" t="str">
         <f>D9</f>
         <v>ધારા ફંડ વર્ષ ૨૦૨૫-૨૬.</v>
       </c>
-      <c r="G35" s="286"/>
-      <c r="H35" s="286"/>
-      <c r="I35" s="287"/>
+      <c r="G35" s="262"/>
+      <c r="H35" s="262"/>
+      <c r="I35" s="263"/>
     </row>
     <row r="36" spans="1:9" ht="91.5" customHeight="1">
-      <c r="A36" s="292" t="s">
+      <c r="A36" s="270" t="s">
         <v>141</v>
       </c>
-      <c r="B36" s="293"/>
-      <c r="C36" s="293"/>
-      <c r="D36" s="293"/>
-      <c r="E36" s="293"/>
-      <c r="F36" s="293"/>
-      <c r="G36" s="293"/>
-      <c r="H36" s="293"/>
-      <c r="I36" s="294"/>
+      <c r="B36" s="271"/>
+      <c r="C36" s="271"/>
+      <c r="D36" s="271"/>
+      <c r="E36" s="271"/>
+      <c r="F36" s="271"/>
+      <c r="G36" s="271"/>
+      <c r="H36" s="271"/>
+      <c r="I36" s="272"/>
     </row>
     <row r="37" spans="1:9" ht="23.4" customHeight="1">
       <c r="A37" s="11"/>
@@ -3589,11 +3589,11 @@
       <c r="C38" s="4"/>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
-      <c r="F38" s="282" t="s">
+      <c r="F38" s="285" t="s">
         <v>73</v>
       </c>
-      <c r="G38" s="282"/>
-      <c r="H38" s="282"/>
+      <c r="G38" s="285"/>
+      <c r="H38" s="285"/>
       <c r="I38" s="13"/>
     </row>
     <row r="39" spans="1:9" ht="15.6">
@@ -3618,9 +3618,9 @@
       <c r="C40" s="15"/>
       <c r="D40" s="16"/>
       <c r="E40" s="16"/>
-      <c r="F40" s="275"/>
-      <c r="G40" s="275"/>
-      <c r="H40" s="275"/>
+      <c r="F40" s="278"/>
+      <c r="G40" s="278"/>
+      <c r="H40" s="278"/>
       <c r="I40" s="17"/>
     </row>
     <row r="41" spans="1:9">
@@ -3667,25 +3667,6 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="30">
-    <mergeCell ref="C34:I34"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A36:I36"/>
-    <mergeCell ref="C21:I21"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="D32:I32"/>
-    <mergeCell ref="D30:I30"/>
-    <mergeCell ref="D28:I28"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A33:I33"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A20:I20"/>
     <mergeCell ref="A3:C3"/>
@@ -3697,6 +3678,25 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D9:I9"/>
     <mergeCell ref="A11:C11"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="D32:I32"/>
+    <mergeCell ref="D30:I30"/>
+    <mergeCell ref="D28:I28"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="C21:I21"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="C34:I34"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A32:C32"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -3727,28 +3727,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="45" customHeight="1" thickBot="1">
-      <c r="A1" s="299" t="s">
+      <c r="A1" s="313" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="299"/>
-      <c r="C1" s="299"/>
-      <c r="D1" s="299"/>
-      <c r="E1" s="299"/>
-      <c r="F1" s="299"/>
+      <c r="B1" s="313"/>
+      <c r="C1" s="313"/>
+      <c r="D1" s="313"/>
+      <c r="E1" s="313"/>
+      <c r="F1" s="313"/>
     </row>
     <row r="2" spans="1:6" ht="35.4" thickBot="1">
       <c r="A2" s="81" t="str">
         <f>'FACE SHEET'!A21</f>
         <v>કામ નું નામ :</v>
       </c>
-      <c r="B2" s="306" t="str">
+      <c r="B2" s="314" t="str">
         <f>'FACE SHEET'!C21</f>
         <v xml:space="preserve">ગોળજ ગામે ઉનાળીયા ચેરમેનના ઘર થી ખૂટતા સી.સી. રસ્તાનું કામ . </v>
       </c>
-      <c r="C2" s="306"/>
-      <c r="D2" s="306"/>
-      <c r="E2" s="306"/>
-      <c r="F2" s="307"/>
+      <c r="C2" s="314"/>
+      <c r="D2" s="314"/>
+      <c r="E2" s="314"/>
+      <c r="F2" s="315"/>
     </row>
     <row r="3" spans="1:6" s="1" customFormat="1" ht="61.2" customHeight="1">
       <c r="A3" s="82" t="s">
@@ -3771,11 +3771,11 @@
       </c>
     </row>
     <row r="4" spans="1:6" s="37" customFormat="1" ht="70.95" customHeight="1">
-      <c r="A4" s="305">
+      <c r="A4" s="307">
         <f>Measurement!K6</f>
         <v>36</v>
       </c>
-      <c r="B4" s="309" t="s">
+      <c r="B4" s="300" t="s">
         <v>74</v>
       </c>
       <c r="C4" s="85" t="str">
@@ -3789,14 +3789,14 @@
         <f>B4</f>
         <v>Cmt</v>
       </c>
-      <c r="F4" s="304">
+      <c r="F4" s="299">
         <f>A4*D5</f>
         <v>5692.32</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="37" customFormat="1">
-      <c r="A5" s="305"/>
-      <c r="B5" s="309"/>
+      <c r="A5" s="307"/>
+      <c r="B5" s="300"/>
       <c r="C5" s="87" t="s">
         <v>123</v>
       </c>
@@ -3805,14 +3805,14 @@
         <v>158.12</v>
       </c>
       <c r="E5" s="308"/>
-      <c r="F5" s="304"/>
+      <c r="F5" s="299"/>
     </row>
     <row r="6" spans="1:6" s="37" customFormat="1" ht="48.6" customHeight="1">
-      <c r="A6" s="305">
+      <c r="A6" s="307">
         <f>Measurement!K11</f>
         <v>16.559999999999999</v>
       </c>
-      <c r="B6" s="309" t="str">
+      <c r="B6" s="300" t="str">
         <f>Measurement!L11</f>
         <v>Cmt</v>
       </c>
@@ -3828,14 +3828,14 @@
         <f>B6</f>
         <v>Cmt</v>
       </c>
-      <c r="F6" s="304">
+      <c r="F6" s="299">
         <f>A6*D7</f>
         <v>11336.975999999999</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="37" customFormat="1">
-      <c r="A7" s="305"/>
-      <c r="B7" s="309"/>
+      <c r="A7" s="307"/>
+      <c r="B7" s="300"/>
       <c r="C7" s="87" t="s">
         <v>66</v>
       </c>
@@ -3844,14 +3844,14 @@
         <v>684.6</v>
       </c>
       <c r="E7" s="308"/>
-      <c r="F7" s="304"/>
+      <c r="F7" s="299"/>
     </row>
     <row r="8" spans="1:6" s="37" customFormat="1" ht="48" customHeight="1">
-      <c r="A8" s="305">
+      <c r="A8" s="307">
         <f>Measurement!K14</f>
         <v>4.1399999999999997</v>
       </c>
-      <c r="B8" s="309" t="s">
+      <c r="B8" s="300" t="s">
         <v>74</v>
       </c>
       <c r="C8" s="85" t="str">
@@ -3866,14 +3866,14 @@
         <f>B8</f>
         <v>Cmt</v>
       </c>
-      <c r="F8" s="304">
+      <c r="F8" s="299">
         <f>A8*D9</f>
         <v>718.33139999999992</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="37" customFormat="1">
-      <c r="A9" s="305"/>
-      <c r="B9" s="309"/>
+      <c r="A9" s="307"/>
+      <c r="B9" s="300"/>
       <c r="C9" s="87" t="s">
         <v>67</v>
       </c>
@@ -3882,14 +3882,14 @@
         <v>173.51</v>
       </c>
       <c r="E9" s="308"/>
-      <c r="F9" s="304"/>
+      <c r="F9" s="299"/>
     </row>
     <row r="10" spans="1:6" s="37" customFormat="1" ht="78.599999999999994" customHeight="1">
-      <c r="A10" s="305">
+      <c r="A10" s="307">
         <f>Measurement!K17</f>
         <v>16.559999999999999</v>
       </c>
-      <c r="B10" s="309" t="s">
+      <c r="B10" s="300" t="s">
         <v>74</v>
       </c>
       <c r="C10" s="85" t="str">
@@ -3903,14 +3903,14 @@
         <f>B10</f>
         <v>Cmt</v>
       </c>
-      <c r="F10" s="304">
+      <c r="F10" s="299">
         <f>A10*D11</f>
         <v>4135.8599999999997</v>
       </c>
     </row>
     <row r="11" spans="1:6" s="37" customFormat="1">
-      <c r="A11" s="305"/>
-      <c r="B11" s="309"/>
+      <c r="A11" s="307"/>
+      <c r="B11" s="300"/>
       <c r="C11" s="87" t="s">
         <v>120</v>
       </c>
@@ -3919,14 +3919,14 @@
         <v>249.75</v>
       </c>
       <c r="E11" s="308"/>
-      <c r="F11" s="304"/>
+      <c r="F11" s="299"/>
     </row>
     <row r="12" spans="1:6" s="37" customFormat="1" ht="49.95" customHeight="1">
-      <c r="A12" s="305">
+      <c r="A12" s="307">
         <f>Measurement!K20</f>
         <v>4.1399999999999997</v>
       </c>
-      <c r="B12" s="309" t="s">
+      <c r="B12" s="300" t="s">
         <v>74</v>
       </c>
       <c r="C12" s="85" t="str">
@@ -3940,14 +3940,14 @@
         <f>B12</f>
         <v>Cmt</v>
       </c>
-      <c r="F12" s="304">
+      <c r="F12" s="299">
         <f>A12*D13</f>
         <v>610.5258</v>
       </c>
     </row>
     <row r="13" spans="1:6" s="37" customFormat="1">
-      <c r="A13" s="305"/>
-      <c r="B13" s="309"/>
+      <c r="A13" s="307"/>
+      <c r="B13" s="300"/>
       <c r="C13" s="87" t="s">
         <v>121</v>
       </c>
@@ -3956,13 +3956,13 @@
         <v>147.47</v>
       </c>
       <c r="E13" s="308"/>
-      <c r="F13" s="304"/>
+      <c r="F13" s="299"/>
     </row>
     <row r="14" spans="1:6" s="37" customFormat="1" ht="96.6" hidden="1" customHeight="1">
-      <c r="A14" s="305">
+      <c r="A14" s="307">
         <v>0</v>
       </c>
-      <c r="B14" s="309" t="s">
+      <c r="B14" s="300" t="s">
         <v>47</v>
       </c>
       <c r="C14" s="85" t="str">
@@ -3976,14 +3976,14 @@
         <f>B14</f>
         <v>Smt</v>
       </c>
-      <c r="F14" s="304">
+      <c r="F14" s="299">
         <f>A14*D15</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" s="37" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1">
-      <c r="A15" s="305"/>
-      <c r="B15" s="309"/>
+      <c r="A15" s="307"/>
+      <c r="B15" s="300"/>
       <c r="C15" s="87" t="s">
         <v>71</v>
       </c>
@@ -3992,14 +3992,14 @@
         <v>17.920000000000002</v>
       </c>
       <c r="E15" s="308"/>
-      <c r="F15" s="304"/>
+      <c r="F15" s="299"/>
     </row>
     <row r="16" spans="1:6" s="37" customFormat="1" ht="64.2" customHeight="1">
-      <c r="A16" s="305">
+      <c r="A16" s="307">
         <f>Measurement!K26</f>
         <v>12</v>
       </c>
-      <c r="B16" s="309" t="s">
+      <c r="B16" s="300" t="s">
         <v>74</v>
       </c>
       <c r="C16" s="85" t="str">
@@ -4014,14 +4014,14 @@
         <f>B16</f>
         <v>Cmt</v>
       </c>
-      <c r="F16" s="304">
+      <c r="F16" s="299">
         <f>A16*D17</f>
         <v>58980.12</v>
       </c>
     </row>
     <row r="17" spans="1:6" s="37" customFormat="1">
-      <c r="A17" s="305"/>
-      <c r="B17" s="309"/>
+      <c r="A17" s="307"/>
+      <c r="B17" s="300"/>
       <c r="C17" s="87" t="s">
         <v>90</v>
       </c>
@@ -4030,13 +4030,13 @@
         <v>4915.01</v>
       </c>
       <c r="E17" s="308"/>
-      <c r="F17" s="304"/>
+      <c r="F17" s="299"/>
     </row>
     <row r="18" spans="1:6" s="37" customFormat="1" ht="45">
-      <c r="A18" s="305">
+      <c r="A18" s="307">
         <v>1</v>
       </c>
-      <c r="B18" s="309" t="s">
+      <c r="B18" s="300" t="s">
         <v>50</v>
       </c>
       <c r="C18" s="85" t="s">
@@ -4050,27 +4050,27 @@
         <f>B18</f>
         <v>No</v>
       </c>
-      <c r="F18" s="304">
+      <c r="F18" s="299">
         <f>A18*D18</f>
         <v>2656</v>
       </c>
     </row>
     <row r="19" spans="1:6" s="37" customFormat="1">
-      <c r="A19" s="305"/>
-      <c r="B19" s="309"/>
+      <c r="A19" s="307"/>
+      <c r="B19" s="300"/>
       <c r="C19" s="87" t="s">
         <v>115</v>
       </c>
       <c r="D19" s="86"/>
       <c r="E19" s="308"/>
-      <c r="F19" s="304"/>
+      <c r="F19" s="299"/>
     </row>
     <row r="20" spans="1:6" s="37" customFormat="1" ht="51" customHeight="1">
-      <c r="A20" s="305">
+      <c r="A20" s="307">
         <f>Measurement!K29</f>
         <v>1</v>
       </c>
-      <c r="B20" s="309" t="s">
+      <c r="B20" s="300" t="s">
         <v>50</v>
       </c>
       <c r="C20" s="85" t="str">
@@ -4084,14 +4084,14 @@
         <f>B20</f>
         <v>No</v>
       </c>
-      <c r="F20" s="304">
+      <c r="F20" s="299">
         <f>A20*D21</f>
         <v>306.14</v>
       </c>
     </row>
     <row r="21" spans="1:6" s="37" customFormat="1">
-      <c r="A21" s="305"/>
-      <c r="B21" s="309"/>
+      <c r="A21" s="307"/>
+      <c r="B21" s="300"/>
       <c r="C21" s="87" t="s">
         <v>122</v>
       </c>
@@ -4100,76 +4100,76 @@
         <v>306.14</v>
       </c>
       <c r="E21" s="308"/>
-      <c r="F21" s="304"/>
+      <c r="F21" s="299"/>
     </row>
     <row r="22" spans="1:6" s="38" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A22" s="302" t="s">
+      <c r="A22" s="305" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="303"/>
-      <c r="C22" s="303"/>
-      <c r="D22" s="303"/>
-      <c r="E22" s="303"/>
+      <c r="B22" s="306"/>
+      <c r="C22" s="306"/>
+      <c r="D22" s="306"/>
+      <c r="E22" s="306"/>
       <c r="F22" s="88">
         <f>SUM(F4:F21)</f>
         <v>84436.273199999996</v>
       </c>
     </row>
     <row r="23" spans="1:6" s="38" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A23" s="310" t="s">
+      <c r="A23" s="303" t="s">
         <v>126</v>
       </c>
-      <c r="B23" s="311"/>
-      <c r="C23" s="311"/>
-      <c r="D23" s="311"/>
-      <c r="E23" s="311"/>
+      <c r="B23" s="304"/>
+      <c r="C23" s="304"/>
+      <c r="D23" s="304"/>
+      <c r="E23" s="304"/>
       <c r="F23" s="89">
         <f>F22*18%</f>
         <v>15198.529175999998</v>
       </c>
     </row>
     <row r="24" spans="1:6" s="38" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A24" s="302" t="s">
+      <c r="A24" s="305" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="303"/>
-      <c r="C24" s="303"/>
-      <c r="D24" s="303"/>
-      <c r="E24" s="303"/>
+      <c r="B24" s="306"/>
+      <c r="C24" s="306"/>
+      <c r="D24" s="306"/>
+      <c r="E24" s="306"/>
       <c r="F24" s="88">
         <f>F22+F23</f>
         <v>99634.802375999992</v>
       </c>
     </row>
     <row r="25" spans="1:6" s="41" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A25" s="310" t="s">
+      <c r="A25" s="303" t="s">
         <v>65</v>
       </c>
-      <c r="B25" s="311"/>
-      <c r="C25" s="311"/>
-      <c r="D25" s="311"/>
-      <c r="E25" s="311"/>
+      <c r="B25" s="304"/>
+      <c r="C25" s="304"/>
+      <c r="D25" s="304"/>
+      <c r="E25" s="304"/>
       <c r="F25" s="89">
         <f>'FACE SHEET'!G22</f>
         <v>100000</v>
       </c>
     </row>
     <row r="26" spans="1:6" s="41" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A26" s="300"/>
-      <c r="B26" s="301"/>
-      <c r="C26" s="301"/>
-      <c r="D26" s="301"/>
-      <c r="E26" s="301"/>
+      <c r="A26" s="309"/>
+      <c r="B26" s="310"/>
+      <c r="C26" s="310"/>
+      <c r="D26" s="310"/>
+      <c r="E26" s="310"/>
       <c r="F26" s="42" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:6" s="41" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A27" s="300"/>
-      <c r="B27" s="301"/>
-      <c r="C27" s="301"/>
-      <c r="D27" s="301"/>
-      <c r="E27" s="301"/>
+      <c r="A27" s="309"/>
+      <c r="B27" s="310"/>
+      <c r="C27" s="310"/>
+      <c r="D27" s="310"/>
+      <c r="E27" s="310"/>
       <c r="F27" s="40"/>
     </row>
     <row r="28" spans="1:6" s="41" customFormat="1" ht="19.5" customHeight="1">
@@ -4209,10 +4209,10 @@
       <c r="F31" s="52"/>
     </row>
     <row r="32" spans="1:6" s="50" customFormat="1">
-      <c r="A32" s="312" t="s">
+      <c r="A32" s="311" t="s">
         <v>84</v>
       </c>
-      <c r="B32" s="313"/>
+      <c r="B32" s="312"/>
       <c r="C32" s="53"/>
       <c r="D32" s="51"/>
       <c r="E32" s="51"/>
@@ -4246,9 +4246,9 @@
       <c r="A36" s="63"/>
       <c r="B36" s="64"/>
       <c r="C36" s="65"/>
-      <c r="D36" s="314"/>
-      <c r="E36" s="314"/>
-      <c r="F36" s="315"/>
+      <c r="D36" s="301"/>
+      <c r="E36" s="301"/>
+      <c r="F36" s="302"/>
     </row>
     <row r="37" spans="1:6" s="50" customFormat="1">
       <c r="A37" s="66"/>
@@ -5164,6 +5164,36 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="46">
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="E20:E21"/>
     <mergeCell ref="F14:F15"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="B6:B7"/>
@@ -5180,36 +5210,6 @@
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="E6:E7"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -5243,47 +5243,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="47.25" customHeight="1" thickBot="1">
-      <c r="A1" s="335" t="str">
+      <c r="A1" s="320" t="str">
         <f>'FACE SHEET'!A21</f>
         <v>કામ નું નામ :</v>
       </c>
-      <c r="B1" s="336"/>
-      <c r="C1" s="333" t="str">
+      <c r="B1" s="321"/>
+      <c r="C1" s="318" t="str">
         <f>Abstract!B2</f>
         <v xml:space="preserve">ગોળજ ગામે ઉનાળીયા ચેરમેનના ઘર થી ખૂટતા સી.સી. રસ્તાનું કામ . </v>
       </c>
-      <c r="D1" s="306"/>
-      <c r="E1" s="306"/>
-      <c r="F1" s="306"/>
-      <c r="G1" s="306"/>
-      <c r="H1" s="306"/>
-      <c r="I1" s="306"/>
-      <c r="J1" s="306"/>
-      <c r="K1" s="306"/>
-      <c r="L1" s="334"/>
+      <c r="D1" s="314"/>
+      <c r="E1" s="314"/>
+      <c r="F1" s="314"/>
+      <c r="G1" s="314"/>
+      <c r="H1" s="314"/>
+      <c r="I1" s="314"/>
+      <c r="J1" s="314"/>
+      <c r="K1" s="314"/>
+      <c r="L1" s="319"/>
     </row>
     <row r="2" spans="1:14" ht="27" customHeight="1" thickBot="1">
-      <c r="A2" s="337" t="s">
+      <c r="A2" s="322" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="338"/>
-      <c r="C2" s="338"/>
-      <c r="D2" s="338"/>
-      <c r="E2" s="338"/>
-      <c r="F2" s="338"/>
-      <c r="G2" s="338"/>
-      <c r="H2" s="338"/>
-      <c r="I2" s="338"/>
-      <c r="J2" s="338"/>
-      <c r="K2" s="338"/>
-      <c r="L2" s="339"/>
+      <c r="B2" s="323"/>
+      <c r="C2" s="323"/>
+      <c r="D2" s="323"/>
+      <c r="E2" s="323"/>
+      <c r="F2" s="323"/>
+      <c r="G2" s="323"/>
+      <c r="H2" s="323"/>
+      <c r="I2" s="323"/>
+      <c r="J2" s="323"/>
+      <c r="K2" s="323"/>
+      <c r="L2" s="324"/>
       <c r="N2" s="92"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="331" t="s">
+      <c r="A3" s="316" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="332"/>
+      <c r="B3" s="317"/>
       <c r="C3" s="30">
         <v>40</v>
       </c>
@@ -5315,10 +5315,10 @@
       <c r="N3" s="92"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="331" t="s">
+      <c r="A4" s="316" t="s">
         <v>87</v>
       </c>
-      <c r="B4" s="332"/>
+      <c r="B4" s="317"/>
       <c r="C4" s="30">
         <v>3</v>
       </c>
@@ -5328,11 +5328,11 @@
       <c r="E4" s="139"/>
       <c r="F4" s="95"/>
       <c r="G4" s="94"/>
-      <c r="H4" s="332" t="s">
+      <c r="H4" s="317" t="s">
         <v>85</v>
       </c>
-      <c r="I4" s="332"/>
-      <c r="J4" s="332"/>
+      <c r="I4" s="317"/>
+      <c r="J4" s="317"/>
       <c r="K4" s="30">
         <f>C3*C4</f>
         <v>120</v>
@@ -5343,20 +5343,20 @@
       <c r="M4" s="92"/>
     </row>
     <row r="5" spans="1:14" ht="55.5" customHeight="1">
-      <c r="A5" s="316" t="s">
+      <c r="A5" s="327" t="s">
         <v>77</v>
       </c>
-      <c r="B5" s="317"/>
-      <c r="C5" s="317"/>
-      <c r="D5" s="317"/>
-      <c r="E5" s="317"/>
-      <c r="F5" s="317"/>
-      <c r="G5" s="317"/>
-      <c r="H5" s="317"/>
-      <c r="I5" s="317"/>
-      <c r="J5" s="317"/>
-      <c r="K5" s="317"/>
-      <c r="L5" s="318"/>
+      <c r="B5" s="328"/>
+      <c r="C5" s="328"/>
+      <c r="D5" s="328"/>
+      <c r="E5" s="328"/>
+      <c r="F5" s="328"/>
+      <c r="G5" s="328"/>
+      <c r="H5" s="328"/>
+      <c r="I5" s="328"/>
+      <c r="J5" s="328"/>
+      <c r="K5" s="328"/>
+      <c r="L5" s="329"/>
       <c r="N5" s="92"/>
     </row>
     <row r="6" spans="1:14" ht="19.5" customHeight="1">
@@ -5402,32 +5402,32 @@
       <c r="F7" s="95"/>
       <c r="G7" s="93"/>
       <c r="H7" s="101"/>
-      <c r="I7" s="341"/>
-      <c r="J7" s="341"/>
+      <c r="I7" s="326"/>
+      <c r="J7" s="326"/>
       <c r="K7" s="105"/>
       <c r="L7" s="7"/>
     </row>
     <row r="8" spans="1:14" s="108" customFormat="1" ht="41.25" customHeight="1">
-      <c r="A8" s="316" t="s">
+      <c r="A8" s="327" t="s">
         <v>116</v>
       </c>
-      <c r="B8" s="317"/>
-      <c r="C8" s="317"/>
-      <c r="D8" s="317"/>
-      <c r="E8" s="317"/>
-      <c r="F8" s="317"/>
-      <c r="G8" s="317"/>
-      <c r="H8" s="317"/>
-      <c r="I8" s="317"/>
-      <c r="J8" s="317"/>
-      <c r="K8" s="317"/>
-      <c r="L8" s="318"/>
+      <c r="B8" s="328"/>
+      <c r="C8" s="328"/>
+      <c r="D8" s="328"/>
+      <c r="E8" s="328"/>
+      <c r="F8" s="328"/>
+      <c r="G8" s="328"/>
+      <c r="H8" s="328"/>
+      <c r="I8" s="328"/>
+      <c r="J8" s="328"/>
+      <c r="K8" s="328"/>
+      <c r="L8" s="329"/>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="324" t="s">
+      <c r="A9" s="330" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="325"/>
+      <c r="B9" s="331"/>
       <c r="C9" s="148">
         <v>1</v>
       </c>
@@ -5461,12 +5461,12 @@
       <c r="L9" s="7"/>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="324" t="s">
+      <c r="A10" s="330" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="325"/>
-      <c r="C10" s="325"/>
-      <c r="D10" s="325"/>
+      <c r="B10" s="331"/>
+      <c r="C10" s="331"/>
+      <c r="D10" s="331"/>
       <c r="E10" s="149">
         <f>K9</f>
         <v>14.399999999999999</v>
@@ -5495,10 +5495,10 @@
       <c r="F11" s="95"/>
       <c r="G11" s="93"/>
       <c r="H11" s="101"/>
-      <c r="I11" s="340" t="s">
+      <c r="I11" s="325" t="s">
         <v>43</v>
       </c>
-      <c r="J11" s="340"/>
+      <c r="J11" s="325"/>
       <c r="K11" s="151">
         <f>SUM(K9:K10)</f>
         <v>16.559999999999999</v>
@@ -5522,26 +5522,26 @@
       <c r="L12" s="103"/>
     </row>
     <row r="13" spans="1:14" s="111" customFormat="1" ht="42.75" customHeight="1">
-      <c r="A13" s="316" t="s">
+      <c r="A13" s="327" t="s">
         <v>117</v>
       </c>
-      <c r="B13" s="317"/>
-      <c r="C13" s="317"/>
-      <c r="D13" s="317"/>
-      <c r="E13" s="317"/>
-      <c r="F13" s="317"/>
-      <c r="G13" s="317"/>
-      <c r="H13" s="317"/>
-      <c r="I13" s="317"/>
-      <c r="J13" s="317"/>
-      <c r="K13" s="317"/>
-      <c r="L13" s="318"/>
+      <c r="B13" s="328"/>
+      <c r="C13" s="328"/>
+      <c r="D13" s="328"/>
+      <c r="E13" s="328"/>
+      <c r="F13" s="328"/>
+      <c r="G13" s="328"/>
+      <c r="H13" s="328"/>
+      <c r="I13" s="328"/>
+      <c r="J13" s="328"/>
+      <c r="K13" s="328"/>
+      <c r="L13" s="329"/>
     </row>
     <row r="14" spans="1:14" s="111" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A14" s="319" t="s">
+      <c r="A14" s="332" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="320"/>
+      <c r="B14" s="333"/>
       <c r="C14" s="145" t="s">
         <v>68</v>
       </c>
@@ -5584,33 +5584,33 @@
       <c r="L15" s="116"/>
     </row>
     <row r="16" spans="1:14" s="111" customFormat="1" ht="54.75" customHeight="1">
-      <c r="A16" s="316" t="s">
+      <c r="A16" s="327" t="s">
         <v>80</v>
       </c>
-      <c r="B16" s="317"/>
-      <c r="C16" s="317"/>
-      <c r="D16" s="317"/>
-      <c r="E16" s="317"/>
-      <c r="F16" s="317"/>
-      <c r="G16" s="317"/>
-      <c r="H16" s="317"/>
-      <c r="I16" s="317"/>
-      <c r="J16" s="317"/>
-      <c r="K16" s="317"/>
-      <c r="L16" s="318"/>
+      <c r="B16" s="328"/>
+      <c r="C16" s="328"/>
+      <c r="D16" s="328"/>
+      <c r="E16" s="328"/>
+      <c r="F16" s="328"/>
+      <c r="G16" s="328"/>
+      <c r="H16" s="328"/>
+      <c r="I16" s="328"/>
+      <c r="J16" s="328"/>
+      <c r="K16" s="328"/>
+      <c r="L16" s="329"/>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="321" t="s">
+      <c r="A17" s="334" t="s">
         <v>75</v>
       </c>
-      <c r="B17" s="322"/>
-      <c r="C17" s="322"/>
-      <c r="D17" s="322"/>
-      <c r="E17" s="322"/>
-      <c r="F17" s="322"/>
-      <c r="G17" s="322"/>
-      <c r="H17" s="322"/>
-      <c r="I17" s="322"/>
+      <c r="B17" s="335"/>
+      <c r="C17" s="335"/>
+      <c r="D17" s="335"/>
+      <c r="E17" s="335"/>
+      <c r="F17" s="335"/>
+      <c r="G17" s="335"/>
+      <c r="H17" s="335"/>
+      <c r="I17" s="335"/>
       <c r="J17" s="120" t="s">
         <v>69</v>
       </c>
@@ -5637,33 +5637,33 @@
       <c r="L18" s="103"/>
     </row>
     <row r="19" spans="1:12" s="111" customFormat="1" ht="33" customHeight="1">
-      <c r="A19" s="316" t="s">
+      <c r="A19" s="327" t="s">
         <v>70</v>
       </c>
-      <c r="B19" s="317"/>
-      <c r="C19" s="317"/>
-      <c r="D19" s="317"/>
-      <c r="E19" s="317"/>
-      <c r="F19" s="317"/>
-      <c r="G19" s="317"/>
-      <c r="H19" s="317"/>
-      <c r="I19" s="317"/>
-      <c r="J19" s="317"/>
-      <c r="K19" s="317"/>
-      <c r="L19" s="318"/>
+      <c r="B19" s="328"/>
+      <c r="C19" s="328"/>
+      <c r="D19" s="328"/>
+      <c r="E19" s="328"/>
+      <c r="F19" s="328"/>
+      <c r="G19" s="328"/>
+      <c r="H19" s="328"/>
+      <c r="I19" s="328"/>
+      <c r="J19" s="328"/>
+      <c r="K19" s="328"/>
+      <c r="L19" s="329"/>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="321" t="s">
+      <c r="A20" s="334" t="s">
         <v>76</v>
       </c>
-      <c r="B20" s="322"/>
-      <c r="C20" s="322"/>
-      <c r="D20" s="322"/>
-      <c r="E20" s="322"/>
-      <c r="F20" s="322"/>
-      <c r="G20" s="322"/>
-      <c r="H20" s="322"/>
-      <c r="I20" s="322"/>
+      <c r="B20" s="335"/>
+      <c r="C20" s="335"/>
+      <c r="D20" s="335"/>
+      <c r="E20" s="335"/>
+      <c r="F20" s="335"/>
+      <c r="G20" s="335"/>
+      <c r="H20" s="335"/>
+      <c r="I20" s="335"/>
       <c r="J20" s="120" t="s">
         <v>69</v>
       </c>
@@ -5690,27 +5690,27 @@
       <c r="L21" s="103"/>
     </row>
     <row r="22" spans="1:12" s="111" customFormat="1" ht="64.2" hidden="1" customHeight="1">
-      <c r="A22" s="328" t="s">
+      <c r="A22" s="339" t="s">
         <v>72</v>
       </c>
-      <c r="B22" s="329"/>
-      <c r="C22" s="329"/>
-      <c r="D22" s="329"/>
-      <c r="E22" s="329"/>
-      <c r="F22" s="329"/>
-      <c r="G22" s="329"/>
-      <c r="H22" s="329"/>
-      <c r="I22" s="329"/>
-      <c r="J22" s="329"/>
-      <c r="K22" s="329"/>
-      <c r="L22" s="330"/>
+      <c r="B22" s="340"/>
+      <c r="C22" s="340"/>
+      <c r="D22" s="340"/>
+      <c r="E22" s="340"/>
+      <c r="F22" s="340"/>
+      <c r="G22" s="340"/>
+      <c r="H22" s="340"/>
+      <c r="I22" s="340"/>
+      <c r="J22" s="340"/>
+      <c r="K22" s="340"/>
+      <c r="L22" s="341"/>
     </row>
     <row r="23" spans="1:12" hidden="1">
-      <c r="A23" s="326" t="s">
+      <c r="A23" s="337" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="327"/>
-      <c r="C23" s="327"/>
+      <c r="B23" s="338"/>
+      <c r="C23" s="338"/>
       <c r="D23" s="105"/>
       <c r="E23" s="105">
         <f>C3</f>
@@ -5751,26 +5751,26 @@
       <c r="L24" s="103"/>
     </row>
     <row r="25" spans="1:12" s="111" customFormat="1" ht="51.75" customHeight="1">
-      <c r="A25" s="316" t="s">
+      <c r="A25" s="327" t="s">
         <v>89</v>
       </c>
-      <c r="B25" s="317"/>
-      <c r="C25" s="317"/>
-      <c r="D25" s="317"/>
-      <c r="E25" s="317"/>
-      <c r="F25" s="317"/>
-      <c r="G25" s="317"/>
-      <c r="H25" s="317"/>
-      <c r="I25" s="317"/>
-      <c r="J25" s="317"/>
-      <c r="K25" s="317"/>
-      <c r="L25" s="318"/>
+      <c r="B25" s="328"/>
+      <c r="C25" s="328"/>
+      <c r="D25" s="328"/>
+      <c r="E25" s="328"/>
+      <c r="F25" s="328"/>
+      <c r="G25" s="328"/>
+      <c r="H25" s="328"/>
+      <c r="I25" s="328"/>
+      <c r="J25" s="328"/>
+      <c r="K25" s="328"/>
+      <c r="L25" s="329"/>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="324" t="s">
+      <c r="A26" s="330" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="325"/>
+      <c r="B26" s="331"/>
       <c r="C26" s="99"/>
       <c r="D26" s="100"/>
       <c r="E26" s="149">
@@ -5816,20 +5816,20 @@
       <c r="L27" s="103"/>
     </row>
     <row r="28" spans="1:12" s="111" customFormat="1" ht="38.4" customHeight="1">
-      <c r="A28" s="316" t="s">
+      <c r="A28" s="327" t="s">
         <v>146</v>
       </c>
-      <c r="B28" s="317"/>
-      <c r="C28" s="317"/>
-      <c r="D28" s="317"/>
-      <c r="E28" s="317"/>
-      <c r="F28" s="317"/>
-      <c r="G28" s="317"/>
-      <c r="H28" s="317"/>
-      <c r="I28" s="317"/>
-      <c r="J28" s="317"/>
-      <c r="K28" s="317"/>
-      <c r="L28" s="318"/>
+      <c r="B28" s="328"/>
+      <c r="C28" s="328"/>
+      <c r="D28" s="328"/>
+      <c r="E28" s="328"/>
+      <c r="F28" s="328"/>
+      <c r="G28" s="328"/>
+      <c r="H28" s="328"/>
+      <c r="I28" s="328"/>
+      <c r="J28" s="328"/>
+      <c r="K28" s="328"/>
+      <c r="L28" s="329"/>
     </row>
     <row r="29" spans="1:12" ht="16.2" thickBot="1">
       <c r="A29" s="126"/>
@@ -5870,9 +5870,9 @@
       <c r="F31" s="134"/>
       <c r="G31" s="133"/>
       <c r="H31" s="132"/>
-      <c r="I31" s="323"/>
-      <c r="J31" s="323"/>
-      <c r="K31" s="323"/>
+      <c r="I31" s="336"/>
+      <c r="J31" s="336"/>
+      <c r="K31" s="336"/>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="132"/>
@@ -5883,9 +5883,9 @@
       <c r="F32" s="134"/>
       <c r="G32" s="133"/>
       <c r="H32" s="132"/>
-      <c r="I32" s="323"/>
-      <c r="J32" s="323"/>
-      <c r="K32" s="323"/>
+      <c r="I32" s="336"/>
+      <c r="J32" s="336"/>
+      <c r="K32" s="336"/>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="132"/>
@@ -5896,9 +5896,9 @@
       <c r="F33" s="134"/>
       <c r="G33" s="133"/>
       <c r="H33" s="132"/>
-      <c r="I33" s="323"/>
-      <c r="J33" s="323"/>
-      <c r="K33" s="323"/>
+      <c r="I33" s="336"/>
+      <c r="J33" s="336"/>
+      <c r="K33" s="336"/>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="132"/>
@@ -6051,18 +6051,6 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="26">
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C1:L1"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="A5:L5"/>
-    <mergeCell ref="A8:L8"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A9:B9"/>
     <mergeCell ref="A19:L19"/>
     <mergeCell ref="A13:L13"/>
     <mergeCell ref="A14:B14"/>
@@ -6077,6 +6065,18 @@
     <mergeCell ref="I31:K31"/>
     <mergeCell ref="A22:L22"/>
     <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C1:L1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A8:L8"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A9:B9"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -6108,16 +6108,16 @@
         <v>કામ નું નામ :</v>
       </c>
       <c r="B1" s="346"/>
-      <c r="C1" s="333" t="str">
+      <c r="C1" s="318" t="str">
         <f>Abstract!B2</f>
         <v xml:space="preserve">ગોળજ ગામે ઉનાળીયા ચેરમેનના ઘર થી ખૂટતા સી.સી. રસ્તાનું કામ . </v>
       </c>
-      <c r="D1" s="306"/>
-      <c r="E1" s="306"/>
-      <c r="F1" s="306"/>
-      <c r="G1" s="306"/>
-      <c r="H1" s="306"/>
-      <c r="I1" s="334"/>
+      <c r="D1" s="314"/>
+      <c r="E1" s="314"/>
+      <c r="F1" s="314"/>
+      <c r="G1" s="314"/>
+      <c r="H1" s="314"/>
+      <c r="I1" s="319"/>
     </row>
     <row r="2" spans="1:9" ht="21.6" thickBot="1">
       <c r="A2" s="347" t="s">
@@ -6133,18 +6133,18 @@
       <c r="I2" s="349"/>
     </row>
     <row r="3" spans="1:9" ht="68.400000000000006" customHeight="1">
-      <c r="A3" s="316" t="str">
+      <c r="A3" s="327" t="str">
         <f>Measurement!A25</f>
         <v xml:space="preserve">Item No. :- 6 Providing and Laying Ordinary Ciment Concrete 1:2:4 exposed work with  Curing etc. Complete including compacting with surface mechanical vibrator,mechanical loater, channaling, from work, grooving, excluding cost of reinforcement for R.C.C work  . </v>
       </c>
-      <c r="B3" s="317"/>
-      <c r="C3" s="317"/>
-      <c r="D3" s="317"/>
-      <c r="E3" s="317"/>
-      <c r="F3" s="317"/>
-      <c r="G3" s="317"/>
-      <c r="H3" s="317"/>
-      <c r="I3" s="318"/>
+      <c r="B3" s="328"/>
+      <c r="C3" s="328"/>
+      <c r="D3" s="328"/>
+      <c r="E3" s="328"/>
+      <c r="F3" s="328"/>
+      <c r="G3" s="328"/>
+      <c r="H3" s="328"/>
+      <c r="I3" s="329"/>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1">
       <c r="A4" s="170" t="s">
@@ -6821,7 +6821,7 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup scale="89" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="86" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
@@ -6848,50 +6848,50 @@
         <f>Abstract!A2</f>
         <v>કામ નું નામ :</v>
       </c>
-      <c r="B1" s="353" t="str">
+      <c r="B1" s="370" t="str">
         <f>Abstract!B2</f>
         <v xml:space="preserve">ગોળજ ગામે ઉનાળીયા ચેરમેનના ઘર થી ખૂટતા સી.સી. રસ્તાનું કામ . </v>
       </c>
-      <c r="C1" s="354"/>
-      <c r="D1" s="354"/>
-      <c r="E1" s="354"/>
-      <c r="F1" s="354"/>
-      <c r="G1" s="354"/>
-      <c r="H1" s="355"/>
+      <c r="C1" s="371"/>
+      <c r="D1" s="371"/>
+      <c r="E1" s="371"/>
+      <c r="F1" s="371"/>
+      <c r="G1" s="371"/>
+      <c r="H1" s="372"/>
     </row>
     <row r="2" spans="1:8" ht="33" customHeight="1" thickBot="1">
-      <c r="A2" s="365" t="s">
+      <c r="A2" s="377" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="366"/>
-      <c r="C2" s="366"/>
-      <c r="D2" s="366"/>
-      <c r="E2" s="366"/>
-      <c r="F2" s="366"/>
-      <c r="G2" s="366"/>
-      <c r="H2" s="367"/>
+      <c r="B2" s="378"/>
+      <c r="C2" s="378"/>
+      <c r="D2" s="378"/>
+      <c r="E2" s="378"/>
+      <c r="F2" s="378"/>
+      <c r="G2" s="378"/>
+      <c r="H2" s="379"/>
     </row>
     <row r="3" spans="1:8" ht="15">
-      <c r="A3" s="368"/>
-      <c r="B3" s="369"/>
-      <c r="C3" s="369"/>
-      <c r="D3" s="369"/>
-      <c r="E3" s="369"/>
-      <c r="F3" s="369"/>
-      <c r="G3" s="369"/>
-      <c r="H3" s="370"/>
+      <c r="A3" s="380"/>
+      <c r="B3" s="381"/>
+      <c r="C3" s="381"/>
+      <c r="D3" s="381"/>
+      <c r="E3" s="381"/>
+      <c r="F3" s="381"/>
+      <c r="G3" s="381"/>
+      <c r="H3" s="382"/>
     </row>
     <row r="4" spans="1:8" s="203" customFormat="1" ht="15" customHeight="1">
-      <c r="A4" s="362" t="s">
+      <c r="A4" s="374" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="363"/>
-      <c r="C4" s="363"/>
-      <c r="D4" s="363"/>
-      <c r="E4" s="363"/>
-      <c r="F4" s="363"/>
-      <c r="G4" s="363"/>
-      <c r="H4" s="364"/>
+      <c r="B4" s="375"/>
+      <c r="C4" s="375"/>
+      <c r="D4" s="375"/>
+      <c r="E4" s="375"/>
+      <c r="F4" s="375"/>
+      <c r="G4" s="375"/>
+      <c r="H4" s="376"/>
     </row>
     <row r="5" spans="1:8" s="203" customFormat="1" ht="22.2" customHeight="1">
       <c r="A5" s="217" t="s">
@@ -6907,12 +6907,12 @@
       <c r="D5" s="214">
         <v>15</v>
       </c>
-      <c r="E5" s="360" t="s">
+      <c r="E5" s="359" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="360"/>
-      <c r="G5" s="360"/>
-      <c r="H5" s="361"/>
+      <c r="F5" s="359"/>
+      <c r="G5" s="359"/>
+      <c r="H5" s="360"/>
     </row>
     <row r="6" spans="1:8" s="203" customFormat="1" ht="22.2" customHeight="1">
       <c r="A6" s="213" t="str">
@@ -6928,46 +6928,46 @@
       <c r="D6" s="214">
         <v>15</v>
       </c>
-      <c r="E6" s="360" t="s">
+      <c r="E6" s="359" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="360"/>
-      <c r="G6" s="360"/>
-      <c r="H6" s="361"/>
+      <c r="F6" s="359"/>
+      <c r="G6" s="359"/>
+      <c r="H6" s="360"/>
     </row>
     <row r="7" spans="1:8" s="203" customFormat="1" ht="22.2" customHeight="1">
-      <c r="A7" s="371" t="s">
+      <c r="A7" s="366" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="372"/>
-      <c r="C7" s="372"/>
+      <c r="B7" s="367"/>
+      <c r="C7" s="367"/>
       <c r="D7" s="214">
         <f>D5+D6</f>
         <v>30</v>
       </c>
-      <c r="E7" s="360" t="s">
+      <c r="E7" s="359" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="360"/>
-      <c r="G7" s="360"/>
-      <c r="H7" s="361"/>
+      <c r="F7" s="359"/>
+      <c r="G7" s="359"/>
+      <c r="H7" s="360"/>
     </row>
     <row r="8" spans="1:8" s="203" customFormat="1" ht="22.2" customHeight="1">
-      <c r="A8" s="371" t="s">
+      <c r="A8" s="366" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="372"/>
-      <c r="C8" s="372"/>
+      <c r="B8" s="367"/>
+      <c r="C8" s="367"/>
       <c r="D8" s="214">
         <f>TRUNC(D7,0)</f>
         <v>30</v>
       </c>
-      <c r="E8" s="360" t="s">
+      <c r="E8" s="359" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="360"/>
-      <c r="G8" s="360"/>
-      <c r="H8" s="361"/>
+      <c r="F8" s="359"/>
+      <c r="G8" s="359"/>
+      <c r="H8" s="360"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="356"/>
@@ -6980,32 +6980,32 @@
       <c r="H9" s="358"/>
     </row>
     <row r="10" spans="1:8" s="203" customFormat="1" ht="15" customHeight="1">
-      <c r="A10" s="362" t="s">
+      <c r="A10" s="374" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="363"/>
-      <c r="C10" s="363"/>
-      <c r="D10" s="363"/>
-      <c r="E10" s="363"/>
-      <c r="F10" s="363"/>
-      <c r="G10" s="363"/>
-      <c r="H10" s="364"/>
+      <c r="B10" s="375"/>
+      <c r="C10" s="375"/>
+      <c r="D10" s="375"/>
+      <c r="E10" s="375"/>
+      <c r="F10" s="375"/>
+      <c r="G10" s="375"/>
+      <c r="H10" s="376"/>
     </row>
     <row r="11" spans="1:8" s="203" customFormat="1" ht="25.2" customHeight="1">
-      <c r="A11" s="359" t="s">
+      <c r="A11" s="373" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="360"/>
-      <c r="C11" s="360"/>
+      <c r="B11" s="359"/>
+      <c r="C11" s="359"/>
       <c r="D11" s="214">
         <v>5</v>
       </c>
-      <c r="E11" s="360" t="s">
+      <c r="E11" s="359" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="360"/>
-      <c r="G11" s="360"/>
-      <c r="H11" s="361"/>
+      <c r="F11" s="359"/>
+      <c r="G11" s="359"/>
+      <c r="H11" s="360"/>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
       <c r="A12" s="356"/>
@@ -7018,16 +7018,16 @@
       <c r="H12" s="358"/>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1">
-      <c r="A13" s="373" t="s">
+      <c r="A13" s="353" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="374"/>
-      <c r="C13" s="374"/>
-      <c r="D13" s="374"/>
-      <c r="E13" s="374"/>
-      <c r="F13" s="374"/>
-      <c r="G13" s="374"/>
-      <c r="H13" s="375"/>
+      <c r="B13" s="354"/>
+      <c r="C13" s="354"/>
+      <c r="D13" s="354"/>
+      <c r="E13" s="354"/>
+      <c r="F13" s="354"/>
+      <c r="G13" s="354"/>
+      <c r="H13" s="355"/>
     </row>
     <row r="14" spans="1:8" ht="15">
       <c r="A14" s="199"/>
@@ -7052,10 +7052,10 @@
     <row r="16" spans="1:8" ht="15">
       <c r="A16" s="220"/>
       <c r="B16" s="221"/>
-      <c r="C16" s="380" t="s">
+      <c r="C16" s="365" t="s">
         <v>57</v>
       </c>
-      <c r="D16" s="380"/>
+      <c r="D16" s="365"/>
       <c r="E16" s="221"/>
       <c r="F16" s="221"/>
       <c r="G16" s="219"/>
@@ -7077,10 +7077,10 @@
       <c r="C18" s="223"/>
       <c r="D18" s="223"/>
       <c r="E18" s="223"/>
-      <c r="F18" s="382" t="s">
+      <c r="F18" s="369" t="s">
         <v>58</v>
       </c>
-      <c r="G18" s="382"/>
+      <c r="G18" s="369"/>
       <c r="H18" s="224"/>
     </row>
     <row r="19" spans="1:8" s="205" customFormat="1" ht="15.6">
@@ -7097,10 +7097,10 @@
       <c r="A20" s="222"/>
       <c r="B20" s="223"/>
       <c r="C20" s="223"/>
-      <c r="D20" s="379" t="s">
+      <c r="D20" s="364" t="s">
         <v>59</v>
       </c>
-      <c r="E20" s="379"/>
+      <c r="E20" s="364"/>
       <c r="F20" s="223"/>
       <c r="G20" s="138"/>
       <c r="H20" s="224"/>
@@ -7109,10 +7109,10 @@
       <c r="A21" s="225"/>
       <c r="B21" s="226"/>
       <c r="C21" s="226"/>
-      <c r="D21" s="376" t="s">
+      <c r="D21" s="361" t="s">
         <v>60</v>
       </c>
-      <c r="E21" s="376"/>
+      <c r="E21" s="361"/>
       <c r="F21" s="226"/>
       <c r="G21" s="219"/>
       <c r="H21" s="198"/>
@@ -7133,10 +7133,10 @@
       <c r="C23" s="226"/>
       <c r="D23" s="226"/>
       <c r="E23" s="226"/>
-      <c r="F23" s="381" t="s">
+      <c r="F23" s="368" t="s">
         <v>61</v>
       </c>
-      <c r="G23" s="381"/>
+      <c r="G23" s="368"/>
       <c r="H23" s="198"/>
     </row>
     <row r="24" spans="1:8" ht="15">
@@ -7270,10 +7270,10 @@
       <c r="H36" s="198"/>
     </row>
     <row r="37" spans="1:8" ht="15.6">
-      <c r="A37" s="377" t="s">
+      <c r="A37" s="362" t="s">
         <v>73</v>
       </c>
-      <c r="B37" s="378"/>
+      <c r="B37" s="363"/>
       <c r="C37" s="226"/>
       <c r="D37" s="226"/>
       <c r="E37" s="226"/>
@@ -7346,6 +7346,17 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="22">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="A8:C8"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="E5:H5"/>
@@ -7357,17 +7368,6 @@
     <mergeCell ref="E7:H7"/>
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="F18:G18"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="A8:C8"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -7396,34 +7396,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="64.2" customHeight="1" thickBot="1">
-      <c r="A1" s="390" t="str">
+      <c r="A1" s="383" t="str">
         <f>Abstract!A2</f>
         <v>કામ નું નામ :</v>
       </c>
-      <c r="B1" s="391"/>
-      <c r="C1" s="353" t="str">
+      <c r="B1" s="384"/>
+      <c r="C1" s="370" t="str">
         <f>Abstract!B2</f>
         <v xml:space="preserve">ગોળજ ગામે ઉનાળીયા ચેરમેનના ઘર થી ખૂટતા સી.સી. રસ્તાનું કામ . </v>
       </c>
-      <c r="D1" s="354"/>
-      <c r="E1" s="354"/>
-      <c r="F1" s="354"/>
-      <c r="G1" s="354"/>
-      <c r="H1" s="354"/>
-      <c r="I1" s="355"/>
+      <c r="D1" s="371"/>
+      <c r="E1" s="371"/>
+      <c r="F1" s="371"/>
+      <c r="G1" s="371"/>
+      <c r="H1" s="371"/>
+      <c r="I1" s="372"/>
     </row>
     <row r="2" spans="1:9" ht="49.2" customHeight="1" thickBot="1">
-      <c r="A2" s="392" t="s">
+      <c r="A2" s="385" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="393"/>
-      <c r="C2" s="393"/>
-      <c r="D2" s="393"/>
-      <c r="E2" s="393"/>
-      <c r="F2" s="393"/>
-      <c r="G2" s="393"/>
-      <c r="H2" s="393"/>
-      <c r="I2" s="394"/>
+      <c r="B2" s="386"/>
+      <c r="C2" s="386"/>
+      <c r="D2" s="386"/>
+      <c r="E2" s="386"/>
+      <c r="F2" s="386"/>
+      <c r="G2" s="386"/>
+      <c r="H2" s="386"/>
+      <c r="I2" s="387"/>
     </row>
     <row r="3" spans="1:9" ht="34.5" customHeight="1">
       <c r="A3" s="228" t="s">
@@ -7441,11 +7441,11 @@
       <c r="E3" s="230" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="395" t="s">
+      <c r="F3" s="388" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="395"/>
-      <c r="H3" s="395"/>
+      <c r="G3" s="388"/>
+      <c r="H3" s="388"/>
       <c r="I3" s="231" t="s">
         <v>23</v>
       </c>
@@ -7535,18 +7535,18 @@
       </c>
       <c r="F7" s="243"/>
       <c r="G7" s="245"/>
-      <c r="H7" s="386" t="s">
+      <c r="H7" s="393" t="s">
         <v>63</v>
       </c>
-      <c r="I7" s="387"/>
+      <c r="I7" s="394"/>
     </row>
     <row r="8" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A8" s="388" t="s">
+      <c r="A8" s="395" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="389"/>
-      <c r="C8" s="389"/>
-      <c r="D8" s="389"/>
+      <c r="B8" s="396"/>
+      <c r="C8" s="396"/>
+      <c r="D8" s="396"/>
       <c r="E8" s="250">
         <v>6.5</v>
       </c>
@@ -7558,12 +7558,12 @@
       <c r="I8" s="251"/>
     </row>
     <row r="9" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A9" s="384" t="s">
+      <c r="A9" s="391" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="385"/>
-      <c r="C9" s="385"/>
-      <c r="D9" s="385"/>
+      <c r="B9" s="392"/>
+      <c r="C9" s="392"/>
+      <c r="D9" s="392"/>
       <c r="E9" s="250">
         <v>5.86</v>
       </c>
@@ -7575,12 +7575,12 @@
       <c r="I9" s="251"/>
     </row>
     <row r="10" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A10" s="384" t="s">
+      <c r="A10" s="391" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="385"/>
-      <c r="C10" s="385"/>
-      <c r="D10" s="385"/>
+      <c r="B10" s="392"/>
+      <c r="C10" s="392"/>
+      <c r="D10" s="392"/>
       <c r="E10" s="250">
         <v>5.41</v>
       </c>
@@ -7592,12 +7592,12 @@
       <c r="I10" s="251"/>
     </row>
     <row r="11" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A11" s="384" t="s">
+      <c r="A11" s="391" t="s">
         <v>55</v>
       </c>
-      <c r="B11" s="385"/>
-      <c r="C11" s="385"/>
-      <c r="D11" s="385"/>
+      <c r="B11" s="392"/>
+      <c r="C11" s="392"/>
+      <c r="D11" s="392"/>
       <c r="E11" s="250">
         <v>5.35</v>
       </c>
@@ -7609,12 +7609,12 @@
       <c r="I11" s="251"/>
     </row>
     <row r="12" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A12" s="384" t="s">
+      <c r="A12" s="391" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="385"/>
-      <c r="C12" s="385"/>
-      <c r="D12" s="385"/>
+      <c r="B12" s="392"/>
+      <c r="C12" s="392"/>
+      <c r="D12" s="392"/>
       <c r="E12" s="250">
         <v>5.96</v>
       </c>
@@ -7671,11 +7671,11 @@
     </row>
     <row r="17" spans="1:9" ht="15.6">
       <c r="A17" s="255"/>
-      <c r="B17" s="396" t="s">
+      <c r="B17" s="389" t="s">
         <v>73</v>
       </c>
-      <c r="C17" s="396"/>
-      <c r="D17" s="396"/>
+      <c r="C17" s="389"/>
+      <c r="D17" s="389"/>
       <c r="E17" s="193"/>
       <c r="F17" s="193"/>
       <c r="G17" s="193"/>
@@ -7699,9 +7699,9 @@
     </row>
     <row r="19" spans="1:9" ht="15">
       <c r="A19" s="199"/>
-      <c r="B19" s="383"/>
-      <c r="C19" s="383"/>
-      <c r="D19" s="383"/>
+      <c r="B19" s="390"/>
+      <c r="C19" s="390"/>
+      <c r="D19" s="390"/>
       <c r="E19" s="193"/>
       <c r="F19" s="193"/>
       <c r="G19" s="193"/>
@@ -7840,11 +7840,6 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="12">
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="B17:D17"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
@@ -7852,11 +7847,16 @@
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A10:D10"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="B17:D17"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.59055118110236227" bottom="0.39370078740157483" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
--- a/skeleton-cc.xlsx
+++ b/skeleton-cc.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\VANRAJSINH\Personal\sample\1.grok\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\VANRAJSINH\Personal\sample\source code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED02D61A-2426-4DCD-A494-321CFEE30CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3B1008-DAF4-45D0-9FA6-BD0F88831365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,19 +25,19 @@
   </externalReferences>
   <definedNames>
     <definedName name="_nmw1">[1]lead!$B$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Abstract!$A$1:$F$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Abstract!$A$1:$F$34</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'FACE SHEET'!$A$1:$I$40</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">Lead!$A$1:$H$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Measurement!$A$1:$L$30</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">RA!$A$1:$I$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">Schedule!$A$1:$I$30</definedName>
-    <definedName name="Z_D6DF09BD_97F5_4B8B_B461_A7BC9875A0D8_.wvu.PrintArea" localSheetId="1" hidden="1">Abstract!$A$1:$F$36</definedName>
+    <definedName name="Z_D6DF09BD_97F5_4B8B_B461_A7BC9875A0D8_.wvu.PrintArea" localSheetId="1" hidden="1">Abstract!$A$1:$F$34</definedName>
     <definedName name="Z_D6DF09BD_97F5_4B8B_B461_A7BC9875A0D8_.wvu.PrintArea" localSheetId="0" hidden="1">'FACE SHEET'!$A$1:$I$40</definedName>
     <definedName name="Z_D6DF09BD_97F5_4B8B_B461_A7BC9875A0D8_.wvu.PrintArea" localSheetId="4" hidden="1">Lead!$A$1:$H$42</definedName>
     <definedName name="Z_D6DF09BD_97F5_4B8B_B461_A7BC9875A0D8_.wvu.PrintArea" localSheetId="2" hidden="1">Measurement!$A$1:$L$30</definedName>
     <definedName name="Z_D6DF09BD_97F5_4B8B_B461_A7BC9875A0D8_.wvu.PrintArea" localSheetId="3" hidden="1">RA!$A$1:$I$39</definedName>
     <definedName name="Z_D6DF09BD_97F5_4B8B_B461_A7BC9875A0D8_.wvu.PrintArea" localSheetId="5" hidden="1">Schedule!$A$1:$I$30</definedName>
-    <definedName name="Z_D6DF09BD_97F5_4B8B_B461_A7BC9875A0D8_.wvu.Rows" localSheetId="1" hidden="1">Abstract!$14:$15</definedName>
+    <definedName name="Z_D6DF09BD_97F5_4B8B_B461_A7BC9875A0D8_.wvu.Rows" localSheetId="1" hidden="1">Abstract!#REF!</definedName>
     <definedName name="Z_D6DF09BD_97F5_4B8B_B461_A7BC9875A0D8_.wvu.Rows" localSheetId="0" hidden="1">'FACE SHEET'!$20:$20</definedName>
     <definedName name="Z_D6DF09BD_97F5_4B8B_B461_A7BC9875A0D8_.wvu.Rows" localSheetId="2" hidden="1">Measurement!$20:$22</definedName>
   </definedNames>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="145">
   <si>
     <t xml:space="preserve">Estimate checked by:  </t>
   </si>
@@ -268,9 +268,6 @@
   </si>
   <si>
     <t>Item No. 5 :-  Spreading blindage or road crust filling the  gaps in metal and levelling to gradient  and camber as directed (i) Murrum</t>
-  </si>
-  <si>
-    <t>R &amp; B SOR 21-22 ITEM NO. 26.76 ITEM CODE 26021</t>
   </si>
   <si>
     <t xml:space="preserve">Item No. 6 :- Rolling and consolidation water bound macadam (Except laterite and kankar) including watering not excceding 150 mm thickness ( main layer including binding  matenals) including filling in  depressions which occurs during the process (B) With power roller excceding 8 tonne and not excecding 12 tonne. </t>
@@ -1248,7 +1245,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="383">
+  <cellXfs count="386">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2448,6 +2445,15 @@
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3040,7 +3046,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="30.75" customHeight="1" thickBot="1">
       <c r="A1" s="290" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B1" s="291"/>
       <c r="C1" s="291"/>
@@ -3062,17 +3068,17 @@
       <c r="B3" s="264"/>
       <c r="C3" s="264"/>
       <c r="D3" s="22" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E3" s="23"/>
       <c r="F3" s="30" t="s">
+        <v>128</v>
+      </c>
+      <c r="G3" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="G3" s="30" t="s">
+      <c r="H3" s="22" t="s">
         <v>130</v>
-      </c>
-      <c r="H3" s="22" t="s">
-        <v>131</v>
       </c>
       <c r="J3" s="300"/>
       <c r="K3" s="300"/>
@@ -3099,17 +3105,17 @@
       <c r="B5" s="264"/>
       <c r="C5" s="264"/>
       <c r="D5" s="22" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E5" s="23"/>
       <c r="F5" s="30" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I5" s="30" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J5" s="298"/>
       <c r="K5" s="298"/>
@@ -3123,7 +3129,7 @@
       <c r="B6" s="21"/>
       <c r="C6" s="21"/>
       <c r="D6" s="22" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="6"/>
@@ -3162,7 +3168,7 @@
       <c r="B9" s="264"/>
       <c r="C9" s="264"/>
       <c r="D9" s="302" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E9" s="302"/>
       <c r="F9" s="302"/>
@@ -3280,7 +3286,7 @@
     </row>
     <row r="19" spans="1:19" s="32" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="274" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B19" s="274"/>
       <c r="C19" s="274"/>
@@ -3289,7 +3295,7 @@
       <c r="F19" s="274"/>
       <c r="G19" s="274"/>
       <c r="H19" s="296" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I19" s="297"/>
       <c r="J19" s="276"/>
@@ -3304,7 +3310,7 @@
     </row>
     <row r="20" spans="1:19" s="33" customFormat="1" ht="28.8" customHeight="1">
       <c r="A20" s="274" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B20" s="274"/>
       <c r="C20" s="274"/>
@@ -3326,11 +3332,11 @@
     </row>
     <row r="21" spans="1:19" ht="45" customHeight="1">
       <c r="A21" s="294" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B21" s="295"/>
       <c r="C21" s="272" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D21" s="272"/>
       <c r="E21" s="272"/>
@@ -3424,7 +3430,7 @@
       <c r="B28" s="285"/>
       <c r="C28" s="285"/>
       <c r="D28" s="282" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E28" s="282"/>
       <c r="F28" s="282"/>
@@ -3525,13 +3531,13 @@
     </row>
     <row r="34" spans="1:19" ht="42" customHeight="1">
       <c r="A34" s="28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B34" s="31">
         <v>6</v>
       </c>
       <c r="C34" s="261" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D34" s="261"/>
       <c r="E34" s="261"/>
@@ -3551,15 +3557,15 @@
     </row>
     <row r="35" spans="1:19" ht="42" customHeight="1">
       <c r="A35" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B35" s="278" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C35" s="278"/>
       <c r="D35" s="278"/>
       <c r="E35" s="35" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F35" s="261" t="str">
         <f>D9</f>
@@ -3580,7 +3586,7 @@
     </row>
     <row r="36" spans="1:19" ht="91.5" customHeight="1">
       <c r="A36" s="269" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B36" s="270"/>
       <c r="C36" s="270"/>
@@ -3616,7 +3622,7 @@
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
       <c r="F38" s="286" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G38" s="286"/>
       <c r="H38" s="286"/>
@@ -3627,7 +3633,7 @@
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="29" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G39" s="29"/>
       <c r="H39" s="34" t="str">
@@ -3740,7 +3746,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:I167"/>
+  <dimension ref="A1:I165"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="14.6640625" style="77" bestFit="1" customWidth="1"/>
@@ -3811,7 +3817,7 @@
         <v>36</v>
       </c>
       <c r="B4" s="242" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C4" s="87" t="str">
         <f>Measurement!A3</f>
@@ -3834,7 +3840,7 @@
       <c r="A5" s="249"/>
       <c r="B5" s="242"/>
       <c r="C5" s="89" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D5" s="88">
         <f>TRUNC((D4*1.01),2)</f>
@@ -3895,7 +3901,7 @@
         <v>4.1399999999999997</v>
       </c>
       <c r="B8" s="242" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C8" s="87" t="str">
         <f>Measurement!A11</f>
@@ -3935,7 +3941,7 @@
         <v>16.559999999999999</v>
       </c>
       <c r="B10" s="242" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C10" s="87" t="str">
         <f>Measurement!A14</f>
@@ -3958,7 +3964,7 @@
       <c r="A11" s="249"/>
       <c r="B11" s="242"/>
       <c r="C11" s="89" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D11" s="88">
         <f>TRUNC((D10*1.01),2)</f>
@@ -3967,13 +3973,13 @@
       <c r="E11" s="250"/>
       <c r="F11" s="241"/>
     </row>
-    <row r="12" spans="1:9" s="38" customFormat="1" ht="49.95" customHeight="1">
+    <row r="12" spans="1:9" s="38" customFormat="1" ht="45">
       <c r="A12" s="249">
         <f>Measurement!K18</f>
         <v>4.1399999999999997</v>
       </c>
       <c r="B12" s="242" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C12" s="87" t="str">
         <f>Measurement!A17</f>
@@ -3995,7 +4001,7 @@
       <c r="A13" s="249"/>
       <c r="B13" s="242"/>
       <c r="C13" s="89" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" s="88">
         <f>TRUNC((D12*1.01),2)</f>
@@ -4004,148 +4010,139 @@
       <c r="E13" s="250"/>
       <c r="F13" s="241"/>
     </row>
-    <row r="14" spans="1:9" s="38" customFormat="1" ht="96.6" hidden="1" customHeight="1">
+    <row r="14" spans="1:9" s="38" customFormat="1" ht="90">
       <c r="A14" s="249">
-        <v>0</v>
+        <f>Measurement!K24</f>
+        <v>12</v>
       </c>
       <c r="B14" s="242" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="C14" s="87" t="str">
-        <f>Measurement!A20</f>
-        <v xml:space="preserve">Item No. 6 :- Rolling and consolidation water bound macadam (Except laterite and kankar) including watering not excceding 150 mm thickness ( main layer including binding  matenals) including filling in  depressions which occurs during the process (B) With power roller excceding 8 tonne and not excecding 12 tonne. </v>
+        <f>Measurement!A23</f>
+        <v xml:space="preserve">Item No. :- 6 Providing and Laying Ordinary Ciment Concrete 1:2:4 exposed work with  Curing etc. Complete including compacting with surface mechanical vibrator,mechanical loater, channaling, from work, grooving, excluding cost of reinforcement for R.C.C work  . </v>
       </c>
       <c r="D14" s="88">
-        <v>17.75</v>
+        <f>RA!G14</f>
+        <v>4866.3500000000004</v>
       </c>
       <c r="E14" s="250" t="str">
         <f>B14</f>
-        <v>Smt</v>
+        <v>Cmt</v>
       </c>
       <c r="F14" s="241">
         <f>A14*D15</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" s="38" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1">
+        <v>58980.12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" s="38" customFormat="1">
       <c r="A15" s="249"/>
       <c r="B15" s="242"/>
       <c r="C15" s="89" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="D15" s="88">
         <f>TRUNC((D14*1.01),2)</f>
-        <v>17.920000000000002</v>
+        <v>4915.01</v>
       </c>
       <c r="E15" s="250"/>
       <c r="F15" s="241"/>
     </row>
-    <row r="16" spans="1:9" s="38" customFormat="1" ht="64.2" customHeight="1">
+    <row r="16" spans="1:9" s="38" customFormat="1" ht="45">
       <c r="A16" s="249">
-        <f>Measurement!K24</f>
-        <v>12</v>
+        <f>Measurement!K27</f>
+        <v>1</v>
       </c>
       <c r="B16" s="242" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="87" t="str">
-        <f>Measurement!A23</f>
-        <v xml:space="preserve">Item No. :- 6 Providing and Laying Ordinary Ciment Concrete 1:2:4 exposed work with  Curing etc. Complete including compacting with surface mechanical vibrator,mechanical loater, channaling, from work, grooving, excluding cost of reinforcement for R.C.C work  . </v>
+        <v>48</v>
+      </c>
+      <c r="C16" s="87" t="s">
+        <v>108</v>
       </c>
       <c r="D16" s="88">
-        <f>RA!G14</f>
-        <v>4866.3500000000004</v>
+        <f>RA!G28</f>
+        <v>2656</v>
       </c>
       <c r="E16" s="250" t="str">
         <f>B16</f>
-        <v>Cmt</v>
+        <v>No</v>
       </c>
       <c r="F16" s="241">
-        <f>A16*D17</f>
-        <v>58980.12</v>
+        <f>A16*D16</f>
+        <v>2656</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="38" customFormat="1">
       <c r="A17" s="249"/>
       <c r="B17" s="242"/>
       <c r="C17" s="89" t="s">
-        <v>85</v>
-      </c>
-      <c r="D17" s="88">
-        <f>TRUNC((D16*1.01),2)</f>
-        <v>4915.01</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="D17" s="88"/>
       <c r="E17" s="250"/>
       <c r="F17" s="241"/>
     </row>
-    <row r="18" spans="1:8" s="38" customFormat="1" ht="45">
+    <row r="18" spans="1:8" s="38" customFormat="1" ht="51" customHeight="1">
       <c r="A18" s="249">
+        <f>Measurement!K30</f>
         <v>1</v>
       </c>
       <c r="B18" s="242" t="s">
         <v>48</v>
       </c>
       <c r="C18" s="87" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="D18" s="88">
-        <f>RA!G28</f>
-        <v>2656</v>
+        <v>303.11</v>
       </c>
       <c r="E18" s="250" t="str">
         <f>B18</f>
         <v>No</v>
       </c>
       <c r="F18" s="241">
-        <f>A18*D18</f>
-        <v>2656</v>
+        <f>A18*D19</f>
+        <v>306.14</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="38" customFormat="1">
       <c r="A19" s="249"/>
       <c r="B19" s="242"/>
       <c r="C19" s="89" t="s">
-        <v>110</v>
-      </c>
-      <c r="D19" s="88"/>
+        <v>116</v>
+      </c>
+      <c r="D19" s="88">
+        <f>TRUNC((D18*1.01),2)</f>
+        <v>306.14</v>
+      </c>
       <c r="E19" s="250"/>
       <c r="F19" s="241"/>
     </row>
-    <row r="20" spans="1:8" s="38" customFormat="1" ht="51" customHeight="1">
-      <c r="A20" s="249">
-        <f>Measurement!K27</f>
-        <v>1</v>
-      </c>
-      <c r="B20" s="242" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" s="87" t="s">
-        <v>145</v>
-      </c>
-      <c r="D20" s="88">
-        <v>303.11</v>
-      </c>
-      <c r="E20" s="250" t="str">
-        <f>B20</f>
-        <v>No</v>
-      </c>
-      <c r="F20" s="241">
-        <f>A20*D21</f>
-        <v>306.14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" s="38" customFormat="1">
-      <c r="A21" s="249"/>
-      <c r="B21" s="242"/>
-      <c r="C21" s="89" t="s">
-        <v>117</v>
-      </c>
-      <c r="D21" s="88">
-        <f>TRUNC((D20*1.01),2)</f>
-        <v>306.14</v>
-      </c>
-      <c r="E21" s="250"/>
-      <c r="F21" s="241"/>
+    <row r="20" spans="1:8" s="40" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A20" s="247" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="248"/>
+      <c r="C20" s="248"/>
+      <c r="D20" s="248"/>
+      <c r="E20" s="248"/>
+      <c r="F20" s="90">
+        <f>SUM(F4:F19)</f>
+        <v>84436.273199999996</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" s="40" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A21" s="245" t="s">
+        <v>120</v>
+      </c>
+      <c r="B21" s="246"/>
+      <c r="C21" s="246"/>
+      <c r="D21" s="246"/>
+      <c r="E21" s="246"/>
+      <c r="F21" s="91">
+        <f>F20*18%</f>
+        <v>15198.529175999998</v>
+      </c>
     </row>
     <row r="22" spans="1:8" s="40" customFormat="1" ht="19.5" customHeight="1">
       <c r="A22" s="247" t="s">
@@ -4156,154 +4153,144 @@
       <c r="D22" s="248"/>
       <c r="E22" s="248"/>
       <c r="F22" s="90">
-        <f>SUM(F4:F21)</f>
-        <v>84436.273199999996</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" s="40" customFormat="1" ht="19.5" customHeight="1">
+        <f>F20+F21</f>
+        <v>99634.802375999992</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" s="43" customFormat="1" ht="19.5" customHeight="1">
       <c r="A23" s="245" t="s">
-        <v>121</v>
+        <v>63</v>
       </c>
       <c r="B23" s="246"/>
       <c r="C23" s="246"/>
       <c r="D23" s="246"/>
       <c r="E23" s="246"/>
       <c r="F23" s="91">
-        <f>F22*18%</f>
-        <v>15198.529175999998</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" s="40" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A24" s="247" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" s="248"/>
-      <c r="C24" s="248"/>
-      <c r="D24" s="248"/>
-      <c r="E24" s="248"/>
-      <c r="F24" s="90">
-        <f>F22+F23</f>
-        <v>99634.802375999992</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" s="43" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A25" s="245" t="s">
-        <v>63</v>
-      </c>
-      <c r="B25" s="246"/>
-      <c r="C25" s="246"/>
-      <c r="D25" s="246"/>
-      <c r="E25" s="246"/>
-      <c r="F25" s="91">
         <f>'FACE SHEET'!G22</f>
         <v>100000</v>
       </c>
     </row>
+    <row r="24" spans="1:8" s="43" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A24" s="252"/>
+      <c r="B24" s="253"/>
+      <c r="C24" s="253"/>
+      <c r="D24" s="253"/>
+      <c r="E24" s="253"/>
+      <c r="F24" s="44" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" s="43" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A25" s="252"/>
+      <c r="B25" s="253"/>
+      <c r="C25" s="253"/>
+      <c r="D25" s="253"/>
+      <c r="E25" s="253"/>
+      <c r="F25" s="42"/>
+    </row>
     <row r="26" spans="1:8" s="43" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A26" s="252"/>
-      <c r="B26" s="253"/>
-      <c r="C26" s="253"/>
-      <c r="D26" s="253"/>
-      <c r="E26" s="253"/>
-      <c r="F26" s="44" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" s="43" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A27" s="252"/>
-      <c r="B27" s="253"/>
-      <c r="C27" s="253"/>
-      <c r="D27" s="253"/>
-      <c r="E27" s="253"/>
-      <c r="F27" s="42"/>
-    </row>
-    <row r="28" spans="1:8" s="43" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A28" s="45"/>
-      <c r="B28" s="41"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="42"/>
+      <c r="A26" s="45"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="42"/>
+    </row>
+    <row r="27" spans="1:8" s="52" customFormat="1">
+      <c r="A27" s="46"/>
+      <c r="B27" s="47"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="49"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="51"/>
+    </row>
+    <row r="28" spans="1:8" s="52" customFormat="1">
+      <c r="A28" s="92" t="s">
+        <v>79</v>
+      </c>
+      <c r="B28" s="81"/>
+      <c r="C28" s="82"/>
+      <c r="D28" s="53"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="55"/>
+      <c r="H28" s="55"/>
     </row>
     <row r="29" spans="1:8" s="52" customFormat="1">
-      <c r="A29" s="46"/>
-      <c r="B29" s="47"/>
-      <c r="C29" s="48"/>
-      <c r="D29" s="49"/>
-      <c r="E29" s="50"/>
-      <c r="F29" s="51"/>
+      <c r="A29" s="93" t="s">
+        <v>80</v>
+      </c>
+      <c r="B29" s="81"/>
+      <c r="C29" s="82"/>
+      <c r="D29" s="53"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="251"/>
+      <c r="H29" s="251"/>
     </row>
     <row r="30" spans="1:8" s="52" customFormat="1">
-      <c r="A30" s="92" t="s">
-        <v>80</v>
-      </c>
-      <c r="B30" s="81"/>
-      <c r="C30" s="82"/>
+      <c r="A30" s="254" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" s="255"/>
+      <c r="C30" s="56"/>
       <c r="D30" s="53"/>
       <c r="E30" s="53"/>
       <c r="F30" s="54"/>
-      <c r="G30" s="55"/>
-      <c r="H30" s="55"/>
-    </row>
-    <row r="31" spans="1:8" s="52" customFormat="1">
-      <c r="A31" s="93" t="s">
-        <v>81</v>
-      </c>
-      <c r="B31" s="81"/>
-      <c r="C31" s="82"/>
-      <c r="D31" s="53"/>
-      <c r="E31" s="53"/>
-      <c r="F31" s="54"/>
-      <c r="G31" s="251"/>
-      <c r="H31" s="251"/>
+      <c r="G30" s="251"/>
+      <c r="H30" s="251"/>
+    </row>
+    <row r="31" spans="1:8" s="52" customFormat="1" ht="17.399999999999999">
+      <c r="A31" s="57"/>
+      <c r="B31" s="58"/>
+      <c r="C31" s="59"/>
+      <c r="D31" s="60"/>
+      <c r="E31" s="59"/>
+      <c r="F31" s="61"/>
+      <c r="G31" s="62"/>
+      <c r="H31" s="37"/>
     </row>
     <row r="32" spans="1:8" s="52" customFormat="1">
-      <c r="A32" s="254" t="s">
-        <v>82</v>
-      </c>
-      <c r="B32" s="255"/>
-      <c r="C32" s="56"/>
-      <c r="D32" s="53"/>
-      <c r="E32" s="53"/>
-      <c r="F32" s="54"/>
-      <c r="G32" s="251"/>
-      <c r="H32" s="251"/>
-    </row>
-    <row r="33" spans="1:8" s="52" customFormat="1" ht="17.399999999999999">
+      <c r="A32" s="57"/>
+      <c r="B32" s="58"/>
+      <c r="C32" s="63"/>
+      <c r="D32" s="64"/>
+      <c r="E32" s="65"/>
+      <c r="F32" s="66"/>
+    </row>
+    <row r="33" spans="1:6" s="52" customFormat="1">
       <c r="A33" s="57"/>
       <c r="B33" s="58"/>
-      <c r="C33" s="59"/>
-      <c r="D33" s="60"/>
-      <c r="E33" s="59"/>
-      <c r="F33" s="61"/>
-      <c r="G33" s="62"/>
-      <c r="H33" s="37"/>
-    </row>
-    <row r="34" spans="1:8" s="52" customFormat="1">
-      <c r="A34" s="57"/>
-      <c r="B34" s="58"/>
-      <c r="C34" s="63"/>
-      <c r="D34" s="64"/>
-      <c r="E34" s="65"/>
-      <c r="F34" s="66"/>
-    </row>
-    <row r="35" spans="1:8" s="52" customFormat="1">
-      <c r="A35" s="57"/>
-      <c r="B35" s="58"/>
+      <c r="C33" s="63"/>
+      <c r="D33" s="64"/>
+      <c r="E33" s="65"/>
+      <c r="F33" s="66"/>
+    </row>
+    <row r="34" spans="1:6" s="52" customFormat="1">
+      <c r="A34" s="67"/>
+      <c r="B34" s="68"/>
+      <c r="C34" s="69"/>
+      <c r="D34" s="243"/>
+      <c r="E34" s="243"/>
+      <c r="F34" s="244"/>
+    </row>
+    <row r="35" spans="1:6" s="52" customFormat="1">
+      <c r="A35" s="70"/>
+      <c r="B35" s="70"/>
       <c r="C35" s="63"/>
-      <c r="D35" s="64"/>
-      <c r="E35" s="65"/>
-      <c r="F35" s="66"/>
-    </row>
-    <row r="36" spans="1:8" s="52" customFormat="1">
-      <c r="A36" s="67"/>
-      <c r="B36" s="68"/>
-      <c r="C36" s="69"/>
-      <c r="D36" s="243"/>
-      <c r="E36" s="243"/>
-      <c r="F36" s="244"/>
-    </row>
-    <row r="37" spans="1:8" s="52" customFormat="1">
+      <c r="D35" s="71"/>
+      <c r="E35" s="72"/>
+      <c r="F35" s="71"/>
+    </row>
+    <row r="36" spans="1:6" s="52" customFormat="1">
+      <c r="A36" s="70"/>
+      <c r="B36" s="70"/>
+      <c r="C36" s="63"/>
+      <c r="D36" s="71"/>
+      <c r="E36" s="72"/>
+      <c r="F36" s="71"/>
+    </row>
+    <row r="37" spans="1:6" s="52" customFormat="1">
       <c r="A37" s="70"/>
       <c r="B37" s="70"/>
       <c r="C37" s="63"/>
@@ -4311,7 +4298,7 @@
       <c r="E37" s="72"/>
       <c r="F37" s="71"/>
     </row>
-    <row r="38" spans="1:8" s="52" customFormat="1">
+    <row r="38" spans="1:6" s="52" customFormat="1">
       <c r="A38" s="70"/>
       <c r="B38" s="70"/>
       <c r="C38" s="63"/>
@@ -4319,7 +4306,7 @@
       <c r="E38" s="72"/>
       <c r="F38" s="71"/>
     </row>
-    <row r="39" spans="1:8" s="52" customFormat="1">
+    <row r="39" spans="1:6" s="52" customFormat="1">
       <c r="A39" s="70"/>
       <c r="B39" s="70"/>
       <c r="C39" s="63"/>
@@ -4327,7 +4314,7 @@
       <c r="E39" s="72"/>
       <c r="F39" s="71"/>
     </row>
-    <row r="40" spans="1:8" s="52" customFormat="1">
+    <row r="40" spans="1:6" s="52" customFormat="1">
       <c r="A40" s="70"/>
       <c r="B40" s="70"/>
       <c r="C40" s="63"/>
@@ -4335,7 +4322,7 @@
       <c r="E40" s="72"/>
       <c r="F40" s="71"/>
     </row>
-    <row r="41" spans="1:8" s="52" customFormat="1">
+    <row r="41" spans="1:6" s="52" customFormat="1">
       <c r="A41" s="70"/>
       <c r="B41" s="70"/>
       <c r="C41" s="63"/>
@@ -4343,7 +4330,7 @@
       <c r="E41" s="72"/>
       <c r="F41" s="71"/>
     </row>
-    <row r="42" spans="1:8" s="52" customFormat="1">
+    <row r="42" spans="1:6" s="52" customFormat="1">
       <c r="A42" s="70"/>
       <c r="B42" s="70"/>
       <c r="C42" s="63"/>
@@ -4351,7 +4338,7 @@
       <c r="E42" s="72"/>
       <c r="F42" s="71"/>
     </row>
-    <row r="43" spans="1:8" s="52" customFormat="1">
+    <row r="43" spans="1:6" s="52" customFormat="1">
       <c r="A43" s="70"/>
       <c r="B43" s="70"/>
       <c r="C43" s="63"/>
@@ -4359,7 +4346,7 @@
       <c r="E43" s="72"/>
       <c r="F43" s="71"/>
     </row>
-    <row r="44" spans="1:8" s="52" customFormat="1">
+    <row r="44" spans="1:6" s="52" customFormat="1">
       <c r="A44" s="70"/>
       <c r="B44" s="70"/>
       <c r="C44" s="63"/>
@@ -4367,23 +4354,23 @@
       <c r="E44" s="72"/>
       <c r="F44" s="71"/>
     </row>
-    <row r="45" spans="1:8" s="52" customFormat="1">
-      <c r="A45" s="70"/>
-      <c r="B45" s="70"/>
-      <c r="C45" s="63"/>
-      <c r="D45" s="71"/>
-      <c r="E45" s="72"/>
-      <c r="F45" s="71"/>
-    </row>
-    <row r="46" spans="1:8" s="52" customFormat="1">
-      <c r="A46" s="70"/>
-      <c r="B46" s="70"/>
-      <c r="C46" s="63"/>
-      <c r="D46" s="71"/>
-      <c r="E46" s="72"/>
-      <c r="F46" s="71"/>
-    </row>
-    <row r="47" spans="1:8">
+    <row r="45" spans="1:6">
+      <c r="A45" s="73"/>
+      <c r="B45" s="73"/>
+      <c r="C45" s="59"/>
+      <c r="D45" s="74"/>
+      <c r="E45" s="75"/>
+      <c r="F45" s="74"/>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="73"/>
+      <c r="B46" s="73"/>
+      <c r="C46" s="59"/>
+      <c r="D46" s="74"/>
+      <c r="E46" s="75"/>
+      <c r="F46" s="74"/>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47" s="73"/>
       <c r="B47" s="73"/>
       <c r="C47" s="59"/>
@@ -4391,7 +4378,7 @@
       <c r="E47" s="75"/>
       <c r="F47" s="74"/>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:6">
       <c r="A48" s="73"/>
       <c r="B48" s="73"/>
       <c r="C48" s="59"/>
@@ -4416,20 +4403,18 @@
       <c r="F50" s="74"/>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="73"/>
-      <c r="B51" s="73"/>
-      <c r="C51" s="59"/>
-      <c r="D51" s="74"/>
-      <c r="E51" s="75"/>
-      <c r="F51" s="74"/>
+      <c r="A51" s="76"/>
+      <c r="B51" s="76"/>
+      <c r="D51" s="77"/>
+      <c r="E51" s="78"/>
+      <c r="F51" s="77"/>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="73"/>
-      <c r="B52" s="73"/>
-      <c r="C52" s="59"/>
-      <c r="D52" s="74"/>
-      <c r="E52" s="75"/>
-      <c r="F52" s="74"/>
+      <c r="A52" s="76"/>
+      <c r="B52" s="76"/>
+      <c r="D52" s="77"/>
+      <c r="E52" s="78"/>
+      <c r="F52" s="77"/>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="76"/>
@@ -4594,14 +4579,14 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="76"/>
-      <c r="B76" s="76"/>
+      <c r="B76" s="79"/>
       <c r="D76" s="77"/>
       <c r="E76" s="78"/>
       <c r="F76" s="77"/>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="76"/>
-      <c r="B77" s="76"/>
+      <c r="B77" s="79"/>
       <c r="D77" s="77"/>
       <c r="E77" s="78"/>
       <c r="F77" s="77"/>
@@ -5148,16 +5133,10 @@
     <row r="155" spans="1:6">
       <c r="A155" s="76"/>
       <c r="B155" s="79"/>
-      <c r="D155" s="77"/>
-      <c r="E155" s="78"/>
-      <c r="F155" s="77"/>
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="76"/>
       <c r="B156" s="79"/>
-      <c r="D156" s="77"/>
-      <c r="E156" s="78"/>
-      <c r="F156" s="77"/>
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="76"/>
@@ -5194,14 +5173,6 @@
     <row r="165" spans="1:2">
       <c r="A165" s="76"/>
       <c r="B165" s="79"/>
-    </row>
-    <row r="166" spans="1:2">
-      <c r="A166" s="76"/>
-      <c r="B166" s="79"/>
-    </row>
-    <row r="167" spans="1:2">
-      <c r="A167" s="76"/>
-      <c r="B167" s="79"/>
     </row>
   </sheetData>
   <customSheetViews>
@@ -5216,10 +5187,10 @@
       <headerFooter scaleWithDoc="0" alignWithMargins="0"/>
     </customSheetView>
   </customSheetViews>
-  <mergeCells count="48">
+  <mergeCells count="44">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A20:E20"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A4:A5"/>
@@ -5231,40 +5202,36 @@
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A18:A19"/>
     <mergeCell ref="E6:E7"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="E10:E11"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="G29:H29"/>
     <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="A16:A17"/>
     <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="E12:E13"/>
     <mergeCell ref="E18:E19"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B14:B15"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="F14:F15"/>
     <mergeCell ref="F16:F17"/>
-    <mergeCell ref="F18:F19"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A14:A15"/>
     <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A14:A15"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -5339,7 +5306,7 @@
     </row>
     <row r="3" spans="1:14" ht="55.5" customHeight="1">
       <c r="A3" s="313" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B3" s="314"/>
       <c r="C3" s="314"/>
@@ -5386,7 +5353,7 @@
         <v>36</v>
       </c>
       <c r="L4" s="129" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -5404,7 +5371,7 @@
     </row>
     <row r="6" spans="1:14" s="108" customFormat="1" ht="41.25" customHeight="1">
       <c r="A6" s="313" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B6" s="314"/>
       <c r="C6" s="314"/>
@@ -5498,7 +5465,7 @@
         <v>16.559999999999999</v>
       </c>
       <c r="L9" s="129" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -5516,7 +5483,7 @@
     </row>
     <row r="11" spans="1:14" s="111" customFormat="1" ht="42.75" customHeight="1">
       <c r="A11" s="313" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B11" s="314"/>
       <c r="C11" s="314"/>
@@ -5559,7 +5526,7 @@
         <v>4.1399999999999997</v>
       </c>
       <c r="L12" s="130" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:14" s="111" customFormat="1">
@@ -5578,7 +5545,7 @@
     </row>
     <row r="14" spans="1:14" s="111" customFormat="1" ht="54.75" customHeight="1">
       <c r="A14" s="313" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B14" s="314"/>
       <c r="C14" s="314"/>
@@ -5594,7 +5561,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="320" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B15" s="321"/>
       <c r="C15" s="321"/>
@@ -5612,7 +5579,7 @@
         <v>16.559999999999999</v>
       </c>
       <c r="L15" s="129" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -5647,7 +5614,7 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="320" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B18" s="321"/>
       <c r="C18" s="321"/>
@@ -5665,7 +5632,7 @@
         <v>4.1399999999999997</v>
       </c>
       <c r="L18" s="129" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -5684,7 +5651,7 @@
     </row>
     <row r="20" spans="1:12" s="111" customFormat="1" ht="64.2" hidden="1" customHeight="1">
       <c r="A20" s="325" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B20" s="326"/>
       <c r="C20" s="326"/>
@@ -5743,7 +5710,7 @@
     </row>
     <row r="23" spans="1:12" s="111" customFormat="1" ht="51.75" customHeight="1">
       <c r="A23" s="313" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B23" s="314"/>
       <c r="C23" s="314"/>
@@ -5789,7 +5756,7 @@
         <v>12</v>
       </c>
       <c r="L24" s="129" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -5808,7 +5775,7 @@
     </row>
     <row r="26" spans="1:12" s="111" customFormat="1" ht="38.4" customHeight="1">
       <c r="A26" s="313" t="str">
-        <f>Abstract!C18</f>
+        <f>Abstract!C16</f>
         <v>Item No :- 7 Testing charges for Kapchi,Metal,Sand,Cement,C.C. Cube as per schedule of testing</v>
       </c>
       <c r="B26" s="314"/>
@@ -5823,7 +5790,7 @@
       <c r="K26" s="314"/>
       <c r="L26" s="315"/>
     </row>
-    <row r="27" spans="1:12" s="111" customFormat="1" ht="16.2" thickBot="1">
+    <row r="27" spans="1:12" s="111" customFormat="1">
       <c r="A27" s="238"/>
       <c r="B27" s="239"/>
       <c r="C27" s="239"/>
@@ -5833,13 +5800,13 @@
       <c r="G27" s="239"/>
       <c r="H27" s="239"/>
       <c r="I27" s="239"/>
-      <c r="J27" s="150" t="s">
+      <c r="J27" s="383" t="s">
         <v>67</v>
       </c>
-      <c r="K27" s="149">
+      <c r="K27" s="384">
         <v>1</v>
       </c>
-      <c r="L27" s="131" t="s">
+      <c r="L27" s="385" t="s">
         <v>48</v>
       </c>
     </row>
@@ -5859,7 +5826,7 @@
     </row>
     <row r="29" spans="1:12" s="111" customFormat="1" ht="38.4" customHeight="1">
       <c r="A29" s="313" t="str">
-        <f>Abstract!C20</f>
+        <f>Abstract!C18</f>
         <v xml:space="preserve">Item No :- 8 Providing and fixing number plate of marble stone of required size set in C. M. 1 : 4 including finishing and engraving letters etc. complete.                </v>
       </c>
       <c r="B29" s="314"/>
@@ -6188,7 +6155,7 @@
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1">
       <c r="A4" s="155" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B4" s="156"/>
       <c r="C4" s="156"/>
@@ -6201,7 +6168,7 @@
         <v>3616.35</v>
       </c>
       <c r="H4" s="159" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I4" s="160" t="s">
         <v>38</v>
@@ -6209,7 +6176,7 @@
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1">
       <c r="A5" s="161" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B5" s="156"/>
       <c r="C5" s="156"/>
@@ -6222,7 +6189,7 @@
     </row>
     <row r="6" spans="1:10" ht="35.25" customHeight="1">
       <c r="A6" s="337" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B6" s="338"/>
       <c r="C6" s="338"/>
@@ -6246,7 +6213,7 @@
     </row>
     <row r="8" spans="1:10" ht="33.75" customHeight="1">
       <c r="A8" s="162" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B8" s="156"/>
       <c r="C8" s="156"/>
@@ -6259,7 +6226,7 @@
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1">
       <c r="A9" s="162" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B9" s="156"/>
       <c r="C9" s="156"/>
@@ -6272,14 +6239,14 @@
     </row>
     <row r="10" spans="1:10" ht="15">
       <c r="A10" s="162" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B10" s="156"/>
       <c r="C10" s="163">
         <v>10</v>
       </c>
       <c r="D10" s="164" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E10" s="163">
         <v>125</v>
@@ -6292,7 +6259,7 @@
         <v>1250</v>
       </c>
       <c r="H10" s="159" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I10" s="160" t="s">
         <v>39</v>
@@ -6305,14 +6272,14 @@
       <c r="D11" s="156"/>
       <c r="E11" s="156"/>
       <c r="F11" s="159" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G11" s="166">
         <f>SUM(G4:G10)</f>
         <v>4866.3500000000004</v>
       </c>
       <c r="H11" s="167" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I11" s="160"/>
     </row>
@@ -6340,7 +6307,7 @@
     </row>
     <row r="14" spans="1:10" ht="15.6">
       <c r="A14" s="168" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B14" s="156"/>
       <c r="C14" s="156"/>
@@ -6352,7 +6319,7 @@
         <v>4866.3500000000004</v>
       </c>
       <c r="H14" s="167" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I14" s="160"/>
     </row>
@@ -6369,7 +6336,7 @@
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1">
       <c r="A16" s="330" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B16" s="330"/>
       <c r="C16" s="330"/>
@@ -6382,17 +6349,17 @@
     </row>
     <row r="17" spans="1:14" ht="39.6">
       <c r="A17" s="170" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" s="170" t="s">
         <v>95</v>
       </c>
-      <c r="B17" s="170" t="s">
+      <c r="C17" s="171" t="s">
         <v>96</v>
-      </c>
-      <c r="C17" s="171" t="s">
-        <v>97</v>
       </c>
       <c r="D17" s="170"/>
       <c r="E17" s="170" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F17" s="170"/>
       <c r="G17" s="170" t="s">
@@ -6406,7 +6373,7 @@
         <v>1</v>
       </c>
       <c r="B18" s="170" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C18" s="173">
         <v>0</v>
@@ -6434,7 +6401,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="170" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C19" s="173">
         <v>1</v>
@@ -6461,7 +6428,7 @@
         <v>3</v>
       </c>
       <c r="B20" s="170" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C20" s="173">
         <v>1</v>
@@ -6488,7 +6455,7 @@
         <v>4</v>
       </c>
       <c r="B21" s="170" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C21" s="173">
         <v>1</v>
@@ -6515,7 +6482,7 @@
         <v>5</v>
       </c>
       <c r="B22" s="170" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C22" s="173">
         <v>1</v>
@@ -6542,7 +6509,7 @@
         <v>6</v>
       </c>
       <c r="B23" s="170" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C23" s="173">
         <v>1</v>
@@ -6569,7 +6536,7 @@
         <v>7</v>
       </c>
       <c r="B24" s="170" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C24" s="173">
         <v>0</v>
@@ -6595,7 +6562,7 @@
         <v>8</v>
       </c>
       <c r="B25" s="170" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C25" s="173">
         <v>0</v>
@@ -6621,7 +6588,7 @@
         <v>9</v>
       </c>
       <c r="B26" s="170" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C26" s="173">
         <v>0</v>
@@ -6647,7 +6614,7 @@
         <v>10</v>
       </c>
       <c r="B27" s="170" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C27" s="173">
         <v>0</v>
@@ -6773,7 +6740,7 @@
     <row r="37" spans="1:9" ht="15.6">
       <c r="A37" s="176"/>
       <c r="B37" s="329" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C37" s="329"/>
       <c r="D37" s="329"/>
@@ -6786,11 +6753,11 @@
     <row r="38" spans="1:9" ht="15.6">
       <c r="A38" s="176"/>
       <c r="B38" s="180" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C38" s="181"/>
       <c r="D38" s="34" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E38" s="176"/>
       <c r="F38" s="176"/>
@@ -6943,10 +6910,10 @@
     </row>
     <row r="5" spans="1:8" s="182" customFormat="1" ht="22.2" customHeight="1">
       <c r="A5" s="195" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B5" s="196" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C5" s="190" t="str">
         <f>'FACE SHEET'!H39</f>
@@ -6968,10 +6935,10 @@
         <v>Thasra</v>
       </c>
       <c r="B6" s="196" t="s">
+        <v>141</v>
+      </c>
+      <c r="C6" s="196" t="s">
         <v>142</v>
-      </c>
-      <c r="C6" s="196" t="s">
-        <v>143</v>
       </c>
       <c r="D6" s="192">
         <v>15</v>
@@ -7319,7 +7286,7 @@
     </row>
     <row r="37" spans="1:8" ht="15.6">
       <c r="A37" s="349" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B37" s="350"/>
       <c r="C37" s="204"/>
@@ -7331,10 +7298,10 @@
     </row>
     <row r="38" spans="1:8" ht="15.6">
       <c r="A38" s="205" t="s">
+        <v>136</v>
+      </c>
+      <c r="B38" s="193" t="s">
         <v>137</v>
-      </c>
-      <c r="B38" s="193" t="s">
-        <v>138</v>
       </c>
       <c r="C38" s="204"/>
       <c r="D38" s="204"/>
@@ -7485,7 +7452,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="211" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C4" s="237">
         <f>Lead!D8</f>
@@ -7517,7 +7484,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="211" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C5" s="237">
         <f>Lead!D11</f>
@@ -7687,7 +7654,7 @@
     <row r="17" spans="1:9" ht="15.6">
       <c r="A17" s="232"/>
       <c r="B17" s="329" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C17" s="329"/>
       <c r="D17" s="329"/>
@@ -7700,10 +7667,10 @@
     <row r="18" spans="1:9" ht="15.6">
       <c r="A18" s="179"/>
       <c r="B18" s="180" t="s">
+        <v>136</v>
+      </c>
+      <c r="C18" s="34" t="s">
         <v>137</v>
-      </c>
-      <c r="C18" s="34" t="s">
-        <v>138</v>
       </c>
       <c r="D18" s="180"/>
       <c r="E18" s="175"/>
